--- a/Doo-Doc/Nueva Version Victus/Modelos de Dominio Enriquecidos/Modelo De Dominio Enriquecido Residentes.xlsx
+++ b/Doo-Doc/Nueva Version Victus/Modelos de Dominio Enriquecidos/Modelo De Dominio Enriquecido Residentes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andre\Documents\DOO 2024 BD\DOO\victus-doc\Doo-Doc\Nueva Version Victus\Modelos de Dominio Enriquecidos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DB36B92-521F-4F14-B89E-5C9909EC606C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BB5121B-42CE-451F-8C22-FE101CBDE1A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" firstSheet="1" activeTab="4" xr2:uid="{007C2ECE-7E90-4717-B1E7-3A143C146FF0}"/>
+    <workbookView xWindow="20355" yWindow="2415" windowWidth="16605" windowHeight="15345" firstSheet="2" activeTab="3" xr2:uid="{007C2ECE-7E90-4717-B1E7-3A143C146FF0}"/>
   </bookViews>
   <sheets>
     <sheet name="Valores" sheetId="1" r:id="rId1"/>
@@ -2189,209 +2189,209 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="34" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="25" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="34" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="25" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="34" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="25" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="26" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="27" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="30" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="31" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="33" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="8" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="26" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="27" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="30" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="31" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="33" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="34" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="25" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="34" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="25" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="34" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="25" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -2995,73 +2995,73 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A1" s="88" t="s">
+      <c r="A1" s="124" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="88"/>
-      <c r="C1" s="88"/>
-      <c r="D1" s="88"/>
-      <c r="E1" s="88"/>
-      <c r="F1" s="88"/>
-      <c r="G1" s="88"/>
-      <c r="H1" s="88"/>
-      <c r="I1" s="88"/>
-      <c r="J1" s="88"/>
-      <c r="K1" s="88"/>
-      <c r="L1" s="88"/>
-      <c r="M1" s="88"/>
-      <c r="N1" s="88"/>
-      <c r="O1" s="88"/>
-      <c r="P1" s="88"/>
-      <c r="Q1" s="88"/>
+      <c r="B1" s="124"/>
+      <c r="C1" s="124"/>
+      <c r="D1" s="124"/>
+      <c r="E1" s="124"/>
+      <c r="F1" s="124"/>
+      <c r="G1" s="124"/>
+      <c r="H1" s="124"/>
+      <c r="I1" s="124"/>
+      <c r="J1" s="124"/>
+      <c r="K1" s="124"/>
+      <c r="L1" s="124"/>
+      <c r="M1" s="124"/>
+      <c r="N1" s="124"/>
+      <c r="O1" s="124"/>
+      <c r="P1" s="124"/>
+      <c r="Q1" s="124"/>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A2" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="B2" s="89" t="str">
+      <c r="B2" s="125" t="str">
         <f>'Listado Objetos de Dominio'!A3</f>
         <v>Residente</v>
       </c>
-      <c r="C2" s="89"/>
-      <c r="D2" s="89"/>
-      <c r="E2" s="89"/>
-      <c r="F2" s="89"/>
-      <c r="G2" s="89"/>
-      <c r="H2" s="89"/>
-      <c r="I2" s="89"/>
-      <c r="J2" s="89"/>
-      <c r="K2" s="89"/>
-      <c r="L2" s="89"/>
-      <c r="M2" s="89"/>
-      <c r="N2" s="89"/>
-      <c r="O2" s="89"/>
-      <c r="P2" s="89"/>
-      <c r="Q2" s="89"/>
+      <c r="C2" s="125"/>
+      <c r="D2" s="125"/>
+      <c r="E2" s="125"/>
+      <c r="F2" s="125"/>
+      <c r="G2" s="125"/>
+      <c r="H2" s="125"/>
+      <c r="I2" s="125"/>
+      <c r="J2" s="125"/>
+      <c r="K2" s="125"/>
+      <c r="L2" s="125"/>
+      <c r="M2" s="125"/>
+      <c r="N2" s="125"/>
+      <c r="O2" s="125"/>
+      <c r="P2" s="125"/>
+      <c r="Q2" s="125"/>
     </row>
     <row r="3" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="B3" s="90" t="str">
+      <c r="B3" s="126" t="str">
         <f>'Listado Objetos de Dominio'!B3</f>
         <v>Objeto de dominio que representa a un residente que vive dentro de un inmueble en un conjunto residencial</v>
       </c>
-      <c r="C3" s="90"/>
-      <c r="D3" s="90"/>
-      <c r="E3" s="90"/>
-      <c r="F3" s="90"/>
-      <c r="G3" s="90"/>
-      <c r="H3" s="90"/>
-      <c r="I3" s="90"/>
-      <c r="J3" s="90"/>
-      <c r="K3" s="90"/>
-      <c r="L3" s="90"/>
-      <c r="M3" s="90"/>
-      <c r="N3" s="90"/>
-      <c r="O3" s="90"/>
-      <c r="P3" s="90"/>
-      <c r="Q3" s="90"/>
+      <c r="C3" s="126"/>
+      <c r="D3" s="126"/>
+      <c r="E3" s="126"/>
+      <c r="F3" s="126"/>
+      <c r="G3" s="126"/>
+      <c r="H3" s="126"/>
+      <c r="I3" s="126"/>
+      <c r="J3" s="126"/>
+      <c r="K3" s="126"/>
+      <c r="L3" s="126"/>
+      <c r="M3" s="126"/>
+      <c r="N3" s="126"/>
+      <c r="O3" s="126"/>
+      <c r="P3" s="126"/>
+      <c r="Q3" s="126"/>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A4" s="15" t="s">
@@ -3360,8 +3360,12 @@
       <c r="D9" s="19"/>
       <c r="E9" s="19"/>
       <c r="F9" s="19"/>
-      <c r="G9" s="19"/>
-      <c r="H9" s="19"/>
+      <c r="G9" s="19">
+        <v>1</v>
+      </c>
+      <c r="H9" s="19">
+        <v>100000000000</v>
+      </c>
       <c r="I9" s="20" t="s">
         <v>45</v>
       </c>
@@ -3458,8 +3462,12 @@
       <c r="D11" s="19"/>
       <c r="E11" s="19"/>
       <c r="F11" s="19"/>
-      <c r="G11" s="19"/>
-      <c r="H11" s="19"/>
+      <c r="G11" s="19">
+        <v>1</v>
+      </c>
+      <c r="H11" s="19">
+        <v>10000000</v>
+      </c>
       <c r="I11" s="20" t="s">
         <v>45</v>
       </c>
@@ -3658,21 +3666,21 @@
       </c>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A16" s="74" t="s">
+      <c r="A16" s="127" t="s">
         <v>93</v>
       </c>
-      <c r="B16" s="74"/>
-      <c r="C16" s="74"/>
-      <c r="E16" s="74" t="s">
+      <c r="B16" s="127"/>
+      <c r="C16" s="127"/>
+      <c r="E16" s="127" t="s">
         <v>95</v>
       </c>
-      <c r="F16" s="74"/>
-      <c r="G16" s="74"/>
-      <c r="I16" s="74" t="s">
+      <c r="F16" s="127"/>
+      <c r="G16" s="127"/>
+      <c r="I16" s="127" t="s">
         <v>47</v>
       </c>
-      <c r="J16" s="74"/>
-      <c r="K16" s="74"/>
+      <c r="J16" s="127"/>
+      <c r="K16" s="127"/>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A17" s="26" t="s">
@@ -3704,113 +3712,113 @@
       </c>
     </row>
     <row r="18" spans="1:19" ht="25.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="75" t="s">
+      <c r="A18" s="138" t="s">
         <v>50</v>
       </c>
-      <c r="B18" s="76" t="s">
+      <c r="B18" s="139" t="s">
         <v>94</v>
       </c>
-      <c r="C18" s="73" t="s">
+      <c r="C18" s="140" t="s">
         <v>71</v>
       </c>
-      <c r="E18" s="76" t="s">
+      <c r="E18" s="139" t="s">
         <v>99</v>
       </c>
-      <c r="F18" s="76" t="s">
+      <c r="F18" s="139" t="s">
         <v>96</v>
       </c>
-      <c r="G18" s="73" t="s">
+      <c r="G18" s="140" t="s">
         <v>83</v>
       </c>
       <c r="H18" s="39"/>
-      <c r="I18" s="75" t="s">
+      <c r="I18" s="138" t="s">
         <v>100</v>
       </c>
-      <c r="J18" s="76" t="s">
+      <c r="J18" s="139" t="s">
         <v>97</v>
       </c>
-      <c r="K18" s="73" t="s">
+      <c r="K18" s="140" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="19" spans="1:19" ht="25.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="75"/>
-      <c r="B19" s="76"/>
-      <c r="C19" s="73"/>
-      <c r="E19" s="76"/>
-      <c r="F19" s="76"/>
-      <c r="G19" s="73"/>
+      <c r="A19" s="138"/>
+      <c r="B19" s="139"/>
+      <c r="C19" s="140"/>
+      <c r="E19" s="139"/>
+      <c r="F19" s="139"/>
+      <c r="G19" s="140"/>
       <c r="H19" s="39"/>
-      <c r="I19" s="75"/>
-      <c r="J19" s="76"/>
-      <c r="K19" s="73"/>
+      <c r="I19" s="138"/>
+      <c r="J19" s="139"/>
+      <c r="K19" s="140"/>
     </row>
     <row r="20" spans="1:19" ht="25.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="75"/>
-      <c r="B20" s="76"/>
-      <c r="C20" s="73" t="s">
+      <c r="A20" s="138"/>
+      <c r="B20" s="139"/>
+      <c r="C20" s="140" t="s">
         <v>82</v>
       </c>
-      <c r="E20" s="76"/>
-      <c r="F20" s="76"/>
-      <c r="G20" s="73"/>
-      <c r="I20" s="75"/>
-      <c r="J20" s="76"/>
-      <c r="K20" s="73"/>
+      <c r="E20" s="139"/>
+      <c r="F20" s="139"/>
+      <c r="G20" s="140"/>
+      <c r="I20" s="138"/>
+      <c r="J20" s="139"/>
+      <c r="K20" s="140"/>
     </row>
     <row r="21" spans="1:19" ht="25.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="75"/>
-      <c r="B21" s="76"/>
-      <c r="C21" s="73"/>
-      <c r="E21" s="76"/>
-      <c r="F21" s="76"/>
-      <c r="G21" s="73"/>
-      <c r="I21" s="75"/>
-      <c r="J21" s="76"/>
-      <c r="K21" s="73"/>
+      <c r="A21" s="138"/>
+      <c r="B21" s="139"/>
+      <c r="C21" s="140"/>
+      <c r="E21" s="139"/>
+      <c r="F21" s="139"/>
+      <c r="G21" s="140"/>
+      <c r="I21" s="138"/>
+      <c r="J21" s="139"/>
+      <c r="K21" s="140"/>
     </row>
     <row r="22" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="23" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A23" s="91" t="s">
+      <c r="A23" s="128" t="s">
         <v>51</v>
       </c>
-      <c r="B23" s="92"/>
-      <c r="C23" s="95" t="s">
+      <c r="B23" s="129"/>
+      <c r="C23" s="132" t="s">
         <v>2</v>
       </c>
-      <c r="D23" s="96"/>
-      <c r="E23" s="96"/>
-      <c r="F23" s="96"/>
-      <c r="G23" s="92"/>
-      <c r="H23" s="83" t="s">
+      <c r="D23" s="133"/>
+      <c r="E23" s="133"/>
+      <c r="F23" s="133"/>
+      <c r="G23" s="129"/>
+      <c r="H23" s="119" t="s">
         <v>52</v>
       </c>
-      <c r="I23" s="99"/>
-      <c r="J23" s="100"/>
-      <c r="K23" s="83" t="s">
+      <c r="I23" s="136"/>
+      <c r="J23" s="137"/>
+      <c r="K23" s="119" t="s">
         <v>53</v>
       </c>
-      <c r="L23" s="99"/>
-      <c r="M23" s="99"/>
-      <c r="N23" s="99"/>
-      <c r="O23" s="100"/>
-      <c r="P23" s="83" t="s">
+      <c r="L23" s="136"/>
+      <c r="M23" s="136"/>
+      <c r="N23" s="136"/>
+      <c r="O23" s="137"/>
+      <c r="P23" s="119" t="s">
         <v>54</v>
       </c>
-      <c r="Q23" s="100"/>
-      <c r="R23" s="83" t="s">
+      <c r="Q23" s="137"/>
+      <c r="R23" s="119" t="s">
         <v>55</v>
       </c>
-      <c r="S23" s="84"/>
+      <c r="S23" s="120"/>
     </row>
     <row r="24" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A24" s="93"/>
-      <c r="B24" s="94"/>
-      <c r="C24" s="97"/>
-      <c r="D24" s="98"/>
-      <c r="E24" s="98"/>
-      <c r="F24" s="98"/>
-      <c r="G24" s="94"/>
+      <c r="A24" s="130"/>
+      <c r="B24" s="131"/>
+      <c r="C24" s="134"/>
+      <c r="D24" s="135"/>
+      <c r="E24" s="135"/>
+      <c r="F24" s="135"/>
+      <c r="G24" s="131"/>
       <c r="H24" s="47" t="s">
         <v>56</v>
       </c>
@@ -3823,12 +3831,12 @@
       <c r="K24" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="L24" s="85" t="s">
+      <c r="L24" s="121" t="s">
         <v>2</v>
       </c>
-      <c r="M24" s="86"/>
-      <c r="N24" s="86"/>
-      <c r="O24" s="87"/>
+      <c r="M24" s="122"/>
+      <c r="N24" s="122"/>
+      <c r="O24" s="123"/>
       <c r="P24" s="27" t="s">
         <v>58</v>
       </c>
@@ -3843,34 +3851,34 @@
       </c>
     </row>
     <row r="25" spans="1:19" ht="45" x14ac:dyDescent="0.25">
-      <c r="A25" s="101" t="s">
+      <c r="A25" s="97" t="s">
         <v>106</v>
       </c>
-      <c r="B25" s="102"/>
-      <c r="C25" s="105" t="s">
+      <c r="B25" s="98"/>
+      <c r="C25" s="101" t="s">
         <v>144</v>
       </c>
-      <c r="D25" s="106"/>
-      <c r="E25" s="106"/>
-      <c r="F25" s="106"/>
-      <c r="G25" s="107"/>
-      <c r="H25" s="111" t="str">
+      <c r="D25" s="102"/>
+      <c r="E25" s="102"/>
+      <c r="F25" s="102"/>
+      <c r="G25" s="103"/>
+      <c r="H25" s="107" t="str">
         <f>_xlfn.CONCAT("datos",B2)</f>
         <v>datosResidente</v>
       </c>
-      <c r="I25" s="113" t="str">
+      <c r="I25" s="109" t="str">
         <f>B2</f>
         <v>Residente</v>
       </c>
-      <c r="J25" s="115" t="str">
+      <c r="J25" s="111" t="str">
         <f>_xlfn.CONCAT("Corresponde al objeto que internamente contiene los datos necesarios para crear un nuevo ",B2,)</f>
         <v>Corresponde al objeto que internamente contiene los datos necesarios para crear un nuevo Residente</v>
       </c>
       <c r="K25" s="48"/>
-      <c r="L25" s="77"/>
-      <c r="M25" s="78"/>
-      <c r="N25" s="78"/>
-      <c r="O25" s="79"/>
+      <c r="L25" s="113"/>
+      <c r="M25" s="114"/>
+      <c r="N25" s="114"/>
+      <c r="O25" s="115"/>
       <c r="P25" s="13" t="s">
         <v>150</v>
       </c>
@@ -3885,21 +3893,21 @@
       </c>
     </row>
     <row r="26" spans="1:19" ht="30" x14ac:dyDescent="0.25">
-      <c r="A26" s="103"/>
-      <c r="B26" s="104"/>
-      <c r="C26" s="108"/>
-      <c r="D26" s="109"/>
-      <c r="E26" s="109"/>
-      <c r="F26" s="109"/>
-      <c r="G26" s="110"/>
-      <c r="H26" s="112"/>
-      <c r="I26" s="114"/>
-      <c r="J26" s="116"/>
+      <c r="A26" s="99"/>
+      <c r="B26" s="100"/>
+      <c r="C26" s="104"/>
+      <c r="D26" s="105"/>
+      <c r="E26" s="105"/>
+      <c r="F26" s="105"/>
+      <c r="G26" s="106"/>
+      <c r="H26" s="108"/>
+      <c r="I26" s="110"/>
+      <c r="J26" s="112"/>
       <c r="K26" s="57"/>
-      <c r="L26" s="80"/>
-      <c r="M26" s="81"/>
-      <c r="N26" s="81"/>
-      <c r="O26" s="82"/>
+      <c r="L26" s="116"/>
+      <c r="M26" s="117"/>
+      <c r="N26" s="117"/>
+      <c r="O26" s="118"/>
       <c r="P26" s="13" t="s">
         <v>151</v>
       </c>
@@ -3914,21 +3922,21 @@
       </c>
     </row>
     <row r="27" spans="1:19" ht="30" x14ac:dyDescent="0.25">
-      <c r="A27" s="103"/>
-      <c r="B27" s="104"/>
-      <c r="C27" s="108"/>
-      <c r="D27" s="109"/>
-      <c r="E27" s="109"/>
-      <c r="F27" s="109"/>
-      <c r="G27" s="110"/>
-      <c r="H27" s="112"/>
-      <c r="I27" s="114"/>
-      <c r="J27" s="116"/>
+      <c r="A27" s="99"/>
+      <c r="B27" s="100"/>
+      <c r="C27" s="104"/>
+      <c r="D27" s="105"/>
+      <c r="E27" s="105"/>
+      <c r="F27" s="105"/>
+      <c r="G27" s="106"/>
+      <c r="H27" s="108"/>
+      <c r="I27" s="110"/>
+      <c r="J27" s="112"/>
       <c r="K27" s="57"/>
-      <c r="L27" s="80"/>
-      <c r="M27" s="81"/>
-      <c r="N27" s="81"/>
-      <c r="O27" s="82"/>
+      <c r="L27" s="116"/>
+      <c r="M27" s="117"/>
+      <c r="N27" s="117"/>
+      <c r="O27" s="118"/>
       <c r="P27" s="13" t="s">
         <v>152</v>
       </c>
@@ -3943,21 +3951,21 @@
       </c>
     </row>
     <row r="28" spans="1:19" ht="45" x14ac:dyDescent="0.25">
-      <c r="A28" s="103"/>
-      <c r="B28" s="104"/>
-      <c r="C28" s="108"/>
-      <c r="D28" s="109"/>
-      <c r="E28" s="109"/>
-      <c r="F28" s="109"/>
-      <c r="G28" s="110"/>
-      <c r="H28" s="112"/>
-      <c r="I28" s="114"/>
-      <c r="J28" s="116"/>
+      <c r="A28" s="99"/>
+      <c r="B28" s="100"/>
+      <c r="C28" s="104"/>
+      <c r="D28" s="105"/>
+      <c r="E28" s="105"/>
+      <c r="F28" s="105"/>
+      <c r="G28" s="106"/>
+      <c r="H28" s="108"/>
+      <c r="I28" s="110"/>
+      <c r="J28" s="112"/>
       <c r="K28" s="57"/>
-      <c r="L28" s="80"/>
-      <c r="M28" s="81"/>
-      <c r="N28" s="81"/>
-      <c r="O28" s="82"/>
+      <c r="L28" s="116"/>
+      <c r="M28" s="117"/>
+      <c r="N28" s="117"/>
+      <c r="O28" s="118"/>
       <c r="P28" s="13" t="s">
         <v>153</v>
       </c>
@@ -4001,17 +4009,17 @@
       </c>
     </row>
     <row r="30" spans="1:19" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="125" t="s">
+      <c r="A30" s="81" t="s">
         <v>131</v>
       </c>
-      <c r="B30" s="126"/>
-      <c r="C30" s="127" t="s">
+      <c r="B30" s="82"/>
+      <c r="C30" s="83" t="s">
         <v>145</v>
       </c>
-      <c r="D30" s="128"/>
-      <c r="E30" s="128"/>
-      <c r="F30" s="128"/>
-      <c r="G30" s="129"/>
+      <c r="D30" s="84"/>
+      <c r="E30" s="84"/>
+      <c r="F30" s="84"/>
+      <c r="G30" s="85"/>
       <c r="H30" s="30" t="str">
         <f>_xlfn.CONCAT("datos",B2)</f>
         <v>datosResidente</v>
@@ -4027,12 +4035,12 @@
       <c r="K30" s="41" t="s">
         <v>149</v>
       </c>
-      <c r="L30" s="130" t="s">
+      <c r="L30" s="86" t="s">
         <v>170</v>
       </c>
-      <c r="M30" s="131"/>
-      <c r="N30" s="131"/>
-      <c r="O30" s="132"/>
+      <c r="M30" s="87"/>
+      <c r="N30" s="87"/>
+      <c r="O30" s="88"/>
       <c r="P30" s="23" t="s">
         <v>165</v>
       </c>
@@ -4047,17 +4055,17 @@
       </c>
     </row>
     <row r="31" spans="1:19" ht="30" x14ac:dyDescent="0.25">
-      <c r="A31" s="133" t="s">
+      <c r="A31" s="89" t="s">
         <v>136</v>
       </c>
-      <c r="B31" s="134"/>
-      <c r="C31" s="135" t="s">
+      <c r="B31" s="90"/>
+      <c r="C31" s="91" t="s">
         <v>146</v>
       </c>
-      <c r="D31" s="136"/>
-      <c r="E31" s="136"/>
-      <c r="F31" s="136"/>
-      <c r="G31" s="137"/>
+      <c r="D31" s="92"/>
+      <c r="E31" s="92"/>
+      <c r="F31" s="92"/>
+      <c r="G31" s="93"/>
       <c r="H31" s="32" t="str">
         <f>_xlfn.CONCAT("datos",B2)</f>
         <v>datosResidente</v>
@@ -4071,10 +4079,10 @@
         <v>Corresponde a los datos que se van a modificar del Residente</v>
       </c>
       <c r="K31" s="34"/>
-      <c r="L31" s="138"/>
-      <c r="M31" s="139"/>
-      <c r="N31" s="139"/>
-      <c r="O31" s="140"/>
+      <c r="L31" s="94"/>
+      <c r="M31" s="95"/>
+      <c r="N31" s="95"/>
+      <c r="O31" s="96"/>
       <c r="P31" s="62" t="s">
         <v>166</v>
       </c>
@@ -4089,17 +4097,17 @@
       </c>
     </row>
     <row r="32" spans="1:19" ht="30" x14ac:dyDescent="0.25">
-      <c r="A32" s="117" t="s">
+      <c r="A32" s="73" t="s">
         <v>142</v>
       </c>
-      <c r="B32" s="118"/>
-      <c r="C32" s="119" t="s">
+      <c r="B32" s="74"/>
+      <c r="C32" s="75" t="s">
         <v>147</v>
       </c>
-      <c r="D32" s="120"/>
-      <c r="E32" s="120"/>
-      <c r="F32" s="120"/>
-      <c r="G32" s="121"/>
+      <c r="D32" s="76"/>
+      <c r="E32" s="76"/>
+      <c r="F32" s="76"/>
+      <c r="G32" s="77"/>
       <c r="H32" s="35" t="s">
         <v>39</v>
       </c>
@@ -4111,10 +4119,10 @@
         <v>Corresponde al identificador del Residente  que se quiere dar de baja.</v>
       </c>
       <c r="K32" s="36"/>
-      <c r="L32" s="122"/>
-      <c r="M32" s="123"/>
-      <c r="N32" s="123"/>
-      <c r="O32" s="124"/>
+      <c r="L32" s="78"/>
+      <c r="M32" s="79"/>
+      <c r="N32" s="79"/>
+      <c r="O32" s="80"/>
       <c r="P32" s="25" t="s">
         <v>166</v>
       </c>
@@ -4130,20 +4138,14 @@
     </row>
   </sheetData>
   <mergeCells count="38">
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="C32:G32"/>
-    <mergeCell ref="L32:O32"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="C30:G30"/>
-    <mergeCell ref="L30:O30"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="C31:G31"/>
-    <mergeCell ref="L31:O31"/>
-    <mergeCell ref="A25:B28"/>
-    <mergeCell ref="C25:G28"/>
-    <mergeCell ref="H25:H28"/>
-    <mergeCell ref="I25:I28"/>
-    <mergeCell ref="J25:J28"/>
+    <mergeCell ref="C20:C21"/>
+    <mergeCell ref="C18:C19"/>
+    <mergeCell ref="G18:G21"/>
+    <mergeCell ref="I16:K16"/>
+    <mergeCell ref="I18:I21"/>
+    <mergeCell ref="K18:K21"/>
+    <mergeCell ref="F18:F21"/>
+    <mergeCell ref="J18:J21"/>
     <mergeCell ref="L25:O28"/>
     <mergeCell ref="R23:S23"/>
     <mergeCell ref="L24:O24"/>
@@ -4160,14 +4162,20 @@
     <mergeCell ref="B18:B21"/>
     <mergeCell ref="E16:G16"/>
     <mergeCell ref="E18:E21"/>
-    <mergeCell ref="C20:C21"/>
-    <mergeCell ref="C18:C19"/>
-    <mergeCell ref="G18:G21"/>
-    <mergeCell ref="I16:K16"/>
-    <mergeCell ref="I18:I21"/>
-    <mergeCell ref="K18:K21"/>
-    <mergeCell ref="F18:F21"/>
-    <mergeCell ref="J18:J21"/>
+    <mergeCell ref="A25:B28"/>
+    <mergeCell ref="C25:G28"/>
+    <mergeCell ref="H25:H28"/>
+    <mergeCell ref="I25:I28"/>
+    <mergeCell ref="J25:J28"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="C32:G32"/>
+    <mergeCell ref="L32:O32"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="C30:G30"/>
+    <mergeCell ref="L30:O30"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="C31:G31"/>
+    <mergeCell ref="L31:O31"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A1" location="'Objetos de Dominio'!A1" display="Volver al inicio" xr:uid="{475DC609-B6D5-4D2D-A170-5000DA801120}"/>
@@ -4238,73 +4246,73 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A1" s="88" t="s">
+      <c r="A1" s="124" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="88"/>
-      <c r="C1" s="88"/>
-      <c r="D1" s="88"/>
-      <c r="E1" s="88"/>
-      <c r="F1" s="88"/>
-      <c r="G1" s="88"/>
-      <c r="H1" s="88"/>
-      <c r="I1" s="88"/>
-      <c r="J1" s="88"/>
-      <c r="K1" s="88"/>
-      <c r="L1" s="88"/>
-      <c r="M1" s="88"/>
-      <c r="N1" s="88"/>
-      <c r="O1" s="88"/>
-      <c r="P1" s="88"/>
-      <c r="Q1" s="88"/>
+      <c r="B1" s="124"/>
+      <c r="C1" s="124"/>
+      <c r="D1" s="124"/>
+      <c r="E1" s="124"/>
+      <c r="F1" s="124"/>
+      <c r="G1" s="124"/>
+      <c r="H1" s="124"/>
+      <c r="I1" s="124"/>
+      <c r="J1" s="124"/>
+      <c r="K1" s="124"/>
+      <c r="L1" s="124"/>
+      <c r="M1" s="124"/>
+      <c r="N1" s="124"/>
+      <c r="O1" s="124"/>
+      <c r="P1" s="124"/>
+      <c r="Q1" s="124"/>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A2" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="B2" s="89" t="str">
+      <c r="B2" s="125" t="str">
         <f>'Listado Objetos de Dominio'!A4</f>
         <v>Inmueble</v>
       </c>
-      <c r="C2" s="89"/>
-      <c r="D2" s="89"/>
-      <c r="E2" s="89"/>
-      <c r="F2" s="89"/>
-      <c r="G2" s="89"/>
-      <c r="H2" s="89"/>
-      <c r="I2" s="89"/>
-      <c r="J2" s="89"/>
-      <c r="K2" s="89"/>
-      <c r="L2" s="89"/>
-      <c r="M2" s="89"/>
-      <c r="N2" s="89"/>
-      <c r="O2" s="89"/>
-      <c r="P2" s="89"/>
-      <c r="Q2" s="89"/>
+      <c r="C2" s="125"/>
+      <c r="D2" s="125"/>
+      <c r="E2" s="125"/>
+      <c r="F2" s="125"/>
+      <c r="G2" s="125"/>
+      <c r="H2" s="125"/>
+      <c r="I2" s="125"/>
+      <c r="J2" s="125"/>
+      <c r="K2" s="125"/>
+      <c r="L2" s="125"/>
+      <c r="M2" s="125"/>
+      <c r="N2" s="125"/>
+      <c r="O2" s="125"/>
+      <c r="P2" s="125"/>
+      <c r="Q2" s="125"/>
     </row>
     <row r="3" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="B3" s="90" t="str">
+      <c r="B3" s="126" t="str">
         <f>'Listado Objetos de Dominio'!B4</f>
         <v xml:space="preserve">Objeto de dominio que representa el inmueble donde vive el residente del conjunto residencial. </v>
       </c>
-      <c r="C3" s="90"/>
-      <c r="D3" s="90"/>
-      <c r="E3" s="90"/>
-      <c r="F3" s="90"/>
-      <c r="G3" s="90"/>
-      <c r="H3" s="90"/>
-      <c r="I3" s="90"/>
-      <c r="J3" s="90"/>
-      <c r="K3" s="90"/>
-      <c r="L3" s="90"/>
-      <c r="M3" s="90"/>
-      <c r="N3" s="90"/>
-      <c r="O3" s="90"/>
-      <c r="P3" s="90"/>
-      <c r="Q3" s="90"/>
+      <c r="C3" s="126"/>
+      <c r="D3" s="126"/>
+      <c r="E3" s="126"/>
+      <c r="F3" s="126"/>
+      <c r="G3" s="126"/>
+      <c r="H3" s="126"/>
+      <c r="I3" s="126"/>
+      <c r="J3" s="126"/>
+      <c r="K3" s="126"/>
+      <c r="L3" s="126"/>
+      <c r="M3" s="126"/>
+      <c r="N3" s="126"/>
+      <c r="O3" s="126"/>
+      <c r="P3" s="126"/>
+      <c r="Q3" s="126"/>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A4" s="15" t="s">
@@ -4570,11 +4578,11 @@
     </row>
     <row r="9" spans="1:21" ht="23.45" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="10" spans="1:21" ht="51" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="74" t="s">
+      <c r="A10" s="127" t="s">
         <v>47</v>
       </c>
-      <c r="B10" s="74"/>
-      <c r="C10" s="74"/>
+      <c r="B10" s="127"/>
+      <c r="C10" s="127"/>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A11" s="26" t="s">
@@ -4588,77 +4596,77 @@
       </c>
     </row>
     <row r="12" spans="1:21" ht="31.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="76" t="s">
+      <c r="A12" s="139" t="s">
         <v>104</v>
       </c>
-      <c r="B12" s="76" t="s">
+      <c r="B12" s="139" t="s">
         <v>105</v>
       </c>
-      <c r="C12" s="73" t="s">
+      <c r="C12" s="140" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="13" spans="1:21" ht="31.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="76"/>
-      <c r="B13" s="76"/>
-      <c r="C13" s="73"/>
+      <c r="A13" s="139"/>
+      <c r="B13" s="139"/>
+      <c r="C13" s="140"/>
     </row>
     <row r="14" spans="1:21" ht="31.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="76"/>
-      <c r="B14" s="76"/>
+      <c r="A14" s="139"/>
+      <c r="B14" s="139"/>
       <c r="C14" s="38" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="15" spans="1:21" ht="31.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="76"/>
-      <c r="B15" s="76"/>
+      <c r="A15" s="139"/>
+      <c r="B15" s="139"/>
       <c r="C15" s="38" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="16" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="17" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A17" s="91" t="s">
+      <c r="A17" s="128" t="s">
         <v>51</v>
       </c>
-      <c r="B17" s="92"/>
-      <c r="C17" s="95" t="s">
+      <c r="B17" s="129"/>
+      <c r="C17" s="132" t="s">
         <v>2</v>
       </c>
-      <c r="D17" s="96"/>
-      <c r="E17" s="96"/>
-      <c r="F17" s="96"/>
-      <c r="G17" s="92"/>
-      <c r="H17" s="83" t="s">
+      <c r="D17" s="133"/>
+      <c r="E17" s="133"/>
+      <c r="F17" s="133"/>
+      <c r="G17" s="129"/>
+      <c r="H17" s="119" t="s">
         <v>52</v>
       </c>
-      <c r="I17" s="99"/>
-      <c r="J17" s="100"/>
-      <c r="K17" s="83" t="s">
+      <c r="I17" s="136"/>
+      <c r="J17" s="137"/>
+      <c r="K17" s="119" t="s">
         <v>53</v>
       </c>
-      <c r="L17" s="99"/>
-      <c r="M17" s="99"/>
-      <c r="N17" s="99"/>
-      <c r="O17" s="100"/>
-      <c r="P17" s="83" t="s">
+      <c r="L17" s="136"/>
+      <c r="M17" s="136"/>
+      <c r="N17" s="136"/>
+      <c r="O17" s="137"/>
+      <c r="P17" s="119" t="s">
         <v>54</v>
       </c>
-      <c r="Q17" s="100"/>
-      <c r="R17" s="83" t="s">
+      <c r="Q17" s="137"/>
+      <c r="R17" s="119" t="s">
         <v>55</v>
       </c>
-      <c r="S17" s="84"/>
+      <c r="S17" s="120"/>
     </row>
     <row r="18" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A18" s="93"/>
-      <c r="B18" s="94"/>
-      <c r="C18" s="97"/>
-      <c r="D18" s="98"/>
-      <c r="E18" s="98"/>
-      <c r="F18" s="98"/>
-      <c r="G18" s="94"/>
+      <c r="A18" s="130"/>
+      <c r="B18" s="131"/>
+      <c r="C18" s="134"/>
+      <c r="D18" s="135"/>
+      <c r="E18" s="135"/>
+      <c r="F18" s="135"/>
+      <c r="G18" s="131"/>
       <c r="H18" s="47" t="s">
         <v>56</v>
       </c>
@@ -4671,12 +4679,12 @@
       <c r="K18" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="L18" s="85" t="s">
+      <c r="L18" s="121" t="s">
         <v>2</v>
       </c>
-      <c r="M18" s="86"/>
-      <c r="N18" s="86"/>
-      <c r="O18" s="87"/>
+      <c r="M18" s="122"/>
+      <c r="N18" s="122"/>
+      <c r="O18" s="123"/>
       <c r="P18" s="27" t="s">
         <v>58</v>
       </c>
@@ -4691,18 +4699,18 @@
       </c>
     </row>
     <row r="19" spans="1:19" ht="30" x14ac:dyDescent="0.25">
-      <c r="A19" s="101" t="s">
+      <c r="A19" s="97" t="s">
         <v>106</v>
       </c>
-      <c r="B19" s="102"/>
-      <c r="C19" s="105" t="s">
+      <c r="B19" s="98"/>
+      <c r="C19" s="101" t="s">
         <v>114</v>
       </c>
-      <c r="D19" s="106"/>
-      <c r="E19" s="106"/>
-      <c r="F19" s="106"/>
-      <c r="G19" s="107"/>
-      <c r="H19" s="111" t="str">
+      <c r="D19" s="102"/>
+      <c r="E19" s="102"/>
+      <c r="F19" s="102"/>
+      <c r="G19" s="103"/>
+      <c r="H19" s="107" t="str">
         <f>_xlfn.CONCAT("datos",B2)</f>
         <v>datosInmueble</v>
       </c>
@@ -4710,15 +4718,15 @@
         <f>B2</f>
         <v>Inmueble</v>
       </c>
-      <c r="J19" s="115" t="str">
+      <c r="J19" s="111" t="str">
         <f>_xlfn.CONCAT("Corresponde al objeto que internamente contiene los datos necesarios para crear una nueva ",B2,)</f>
         <v>Corresponde al objeto que internamente contiene los datos necesarios para crear una nueva Inmueble</v>
       </c>
       <c r="K19" s="48"/>
-      <c r="L19" s="77"/>
-      <c r="M19" s="78"/>
-      <c r="N19" s="78"/>
-      <c r="O19" s="79"/>
+      <c r="L19" s="113"/>
+      <c r="M19" s="114"/>
+      <c r="N19" s="114"/>
+      <c r="O19" s="115"/>
       <c r="P19" s="13" t="s">
         <v>115</v>
       </c>
@@ -4733,21 +4741,21 @@
       </c>
     </row>
     <row r="20" spans="1:19" ht="45" x14ac:dyDescent="0.25">
-      <c r="A20" s="103"/>
-      <c r="B20" s="104"/>
-      <c r="C20" s="108"/>
-      <c r="D20" s="109"/>
-      <c r="E20" s="109"/>
-      <c r="F20" s="109"/>
-      <c r="G20" s="110"/>
-      <c r="H20" s="112"/>
+      <c r="A20" s="99"/>
+      <c r="B20" s="100"/>
+      <c r="C20" s="104"/>
+      <c r="D20" s="105"/>
+      <c r="E20" s="105"/>
+      <c r="F20" s="105"/>
+      <c r="G20" s="106"/>
+      <c r="H20" s="108"/>
       <c r="I20" s="142"/>
-      <c r="J20" s="116"/>
+      <c r="J20" s="112"/>
       <c r="K20" s="57"/>
-      <c r="L20" s="80"/>
-      <c r="M20" s="81"/>
-      <c r="N20" s="81"/>
-      <c r="O20" s="82"/>
+      <c r="L20" s="116"/>
+      <c r="M20" s="117"/>
+      <c r="N20" s="117"/>
+      <c r="O20" s="118"/>
       <c r="P20" s="13" t="s">
         <v>119</v>
       </c>
@@ -4762,21 +4770,21 @@
       </c>
     </row>
     <row r="21" spans="1:19" ht="30" x14ac:dyDescent="0.25">
-      <c r="A21" s="103"/>
-      <c r="B21" s="104"/>
-      <c r="C21" s="108"/>
-      <c r="D21" s="109"/>
-      <c r="E21" s="109"/>
-      <c r="F21" s="109"/>
-      <c r="G21" s="110"/>
-      <c r="H21" s="112"/>
+      <c r="A21" s="99"/>
+      <c r="B21" s="100"/>
+      <c r="C21" s="104"/>
+      <c r="D21" s="105"/>
+      <c r="E21" s="105"/>
+      <c r="F21" s="105"/>
+      <c r="G21" s="106"/>
+      <c r="H21" s="108"/>
       <c r="I21" s="142"/>
-      <c r="J21" s="116"/>
+      <c r="J21" s="112"/>
       <c r="K21" s="57"/>
-      <c r="L21" s="80"/>
-      <c r="M21" s="81"/>
-      <c r="N21" s="81"/>
-      <c r="O21" s="82"/>
+      <c r="L21" s="116"/>
+      <c r="M21" s="117"/>
+      <c r="N21" s="117"/>
+      <c r="O21" s="118"/>
       <c r="P21" s="13" t="s">
         <v>123</v>
       </c>
@@ -4791,21 +4799,21 @@
       </c>
     </row>
     <row r="22" spans="1:19" ht="45" x14ac:dyDescent="0.25">
-      <c r="A22" s="103"/>
-      <c r="B22" s="104"/>
-      <c r="C22" s="108"/>
-      <c r="D22" s="109"/>
-      <c r="E22" s="109"/>
-      <c r="F22" s="109"/>
-      <c r="G22" s="110"/>
-      <c r="H22" s="112"/>
+      <c r="A22" s="99"/>
+      <c r="B22" s="100"/>
+      <c r="C22" s="104"/>
+      <c r="D22" s="105"/>
+      <c r="E22" s="105"/>
+      <c r="F22" s="105"/>
+      <c r="G22" s="106"/>
+      <c r="H22" s="108"/>
       <c r="I22" s="142"/>
-      <c r="J22" s="116"/>
+      <c r="J22" s="112"/>
       <c r="K22" s="57"/>
-      <c r="L22" s="80"/>
-      <c r="M22" s="81"/>
-      <c r="N22" s="81"/>
-      <c r="O22" s="82"/>
+      <c r="L22" s="116"/>
+      <c r="M22" s="117"/>
+      <c r="N22" s="117"/>
+      <c r="O22" s="118"/>
       <c r="P22" s="13" t="s">
         <v>127</v>
       </c>
@@ -4820,17 +4828,17 @@
       </c>
     </row>
     <row r="23" spans="1:19" ht="71.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="125" t="s">
+      <c r="A23" s="81" t="s">
         <v>131</v>
       </c>
-      <c r="B23" s="126"/>
-      <c r="C23" s="127" t="s">
+      <c r="B23" s="82"/>
+      <c r="C23" s="83" t="s">
         <v>132</v>
       </c>
-      <c r="D23" s="128"/>
-      <c r="E23" s="128"/>
-      <c r="F23" s="128"/>
-      <c r="G23" s="129"/>
+      <c r="D23" s="84"/>
+      <c r="E23" s="84"/>
+      <c r="F23" s="84"/>
+      <c r="G23" s="85"/>
       <c r="H23" s="30" t="str">
         <f>_xlfn.CONCAT("datos",B2)</f>
         <v>datosInmueble</v>
@@ -4846,12 +4854,12 @@
       <c r="K23" s="41" t="s">
         <v>148</v>
       </c>
-      <c r="L23" s="130" t="s">
+      <c r="L23" s="86" t="s">
         <v>133</v>
       </c>
-      <c r="M23" s="131"/>
-      <c r="N23" s="131"/>
-      <c r="O23" s="132"/>
+      <c r="M23" s="87"/>
+      <c r="N23" s="87"/>
+      <c r="O23" s="88"/>
       <c r="P23" s="23" t="s">
         <v>134</v>
       </c>
@@ -4866,17 +4874,17 @@
       </c>
     </row>
     <row r="24" spans="1:19" ht="30" x14ac:dyDescent="0.25">
-      <c r="A24" s="133" t="s">
+      <c r="A24" s="89" t="s">
         <v>136</v>
       </c>
-      <c r="B24" s="134"/>
-      <c r="C24" s="135" t="s">
+      <c r="B24" s="90"/>
+      <c r="C24" s="91" t="s">
         <v>137</v>
       </c>
-      <c r="D24" s="136"/>
-      <c r="E24" s="136"/>
-      <c r="F24" s="136"/>
-      <c r="G24" s="137"/>
+      <c r="D24" s="92"/>
+      <c r="E24" s="92"/>
+      <c r="F24" s="92"/>
+      <c r="G24" s="93"/>
       <c r="H24" s="32" t="str">
         <f>_xlfn.CONCAT("datos",B2)</f>
         <v>datosInmueble</v>
@@ -4890,10 +4898,10 @@
         <v>Corresponde a los datos que se van a modificar de la Inmueble</v>
       </c>
       <c r="K24" s="34"/>
-      <c r="L24" s="138"/>
-      <c r="M24" s="139"/>
-      <c r="N24" s="139"/>
-      <c r="O24" s="140"/>
+      <c r="L24" s="94"/>
+      <c r="M24" s="95"/>
+      <c r="N24" s="95"/>
+      <c r="O24" s="96"/>
       <c r="P24" s="62" t="s">
         <v>138</v>
       </c>
@@ -4908,17 +4916,17 @@
       </c>
     </row>
     <row r="25" spans="1:19" ht="30" x14ac:dyDescent="0.25">
-      <c r="A25" s="117" t="s">
+      <c r="A25" s="73" t="s">
         <v>142</v>
       </c>
-      <c r="B25" s="118"/>
-      <c r="C25" s="119" t="s">
+      <c r="B25" s="74"/>
+      <c r="C25" s="75" t="s">
         <v>143</v>
       </c>
-      <c r="D25" s="120"/>
-      <c r="E25" s="120"/>
-      <c r="F25" s="120"/>
-      <c r="G25" s="121"/>
+      <c r="D25" s="76"/>
+      <c r="E25" s="76"/>
+      <c r="F25" s="76"/>
+      <c r="G25" s="77"/>
       <c r="H25" s="35" t="s">
         <v>39</v>
       </c>
@@ -4930,10 +4938,10 @@
         <v>Corresponde al identificador de la Inmueble  que se quiere dar de baja.</v>
       </c>
       <c r="K25" s="36"/>
-      <c r="L25" s="122"/>
-      <c r="M25" s="123"/>
-      <c r="N25" s="123"/>
-      <c r="O25" s="124"/>
+      <c r="L25" s="78"/>
+      <c r="M25" s="79"/>
+      <c r="N25" s="79"/>
+      <c r="O25" s="80"/>
       <c r="P25" s="25" t="s">
         <v>138</v>
       </c>
@@ -4949,6 +4957,26 @@
     </row>
   </sheetData>
   <mergeCells count="29">
+    <mergeCell ref="L19:O22"/>
+    <mergeCell ref="A19:B22"/>
+    <mergeCell ref="C19:G22"/>
+    <mergeCell ref="H19:H22"/>
+    <mergeCell ref="I19:I22"/>
+    <mergeCell ref="J19:J22"/>
+    <mergeCell ref="P17:Q17"/>
+    <mergeCell ref="R17:S17"/>
+    <mergeCell ref="L18:O18"/>
+    <mergeCell ref="A17:B18"/>
+    <mergeCell ref="C17:G18"/>
+    <mergeCell ref="H17:J17"/>
+    <mergeCell ref="K17:O17"/>
+    <mergeCell ref="A1:Q1"/>
+    <mergeCell ref="B2:Q2"/>
+    <mergeCell ref="B3:Q3"/>
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="B12:B15"/>
+    <mergeCell ref="C12:C13"/>
     <mergeCell ref="A25:B25"/>
     <mergeCell ref="C25:G25"/>
     <mergeCell ref="L25:O25"/>
@@ -4958,26 +4986,6 @@
     <mergeCell ref="A24:B24"/>
     <mergeCell ref="C24:G24"/>
     <mergeCell ref="L24:O24"/>
-    <mergeCell ref="A1:Q1"/>
-    <mergeCell ref="B2:Q2"/>
-    <mergeCell ref="B3:Q3"/>
-    <mergeCell ref="A10:C10"/>
-    <mergeCell ref="A12:A15"/>
-    <mergeCell ref="B12:B15"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="P17:Q17"/>
-    <mergeCell ref="R17:S17"/>
-    <mergeCell ref="L18:O18"/>
-    <mergeCell ref="A17:B18"/>
-    <mergeCell ref="C17:G18"/>
-    <mergeCell ref="H17:J17"/>
-    <mergeCell ref="K17:O17"/>
-    <mergeCell ref="L19:O22"/>
-    <mergeCell ref="A19:B22"/>
-    <mergeCell ref="C19:G22"/>
-    <mergeCell ref="H19:H22"/>
-    <mergeCell ref="I19:I22"/>
-    <mergeCell ref="J19:J22"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A1" location="'Objetos de Dominio'!A1" display="Volver al inicio" xr:uid="{4C6EA31D-5DD1-42F9-A469-ED5E8CAE0643}"/>

--- a/Doo-Doc/Nueva Version Victus/Modelos de Dominio Enriquecidos/Modelo De Dominio Enriquecido Residentes.xlsx
+++ b/Doo-Doc/Nueva Version Victus/Modelos de Dominio Enriquecidos/Modelo De Dominio Enriquecido Residentes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andre\Documents\DOO 2024 BD\DOO\victus-doc\Doo-Doc\Nueva Version Victus\Modelos de Dominio Enriquecidos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BB5121B-42CE-451F-8C22-FE101CBDE1A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31D795FA-9C46-48AA-A019-6F77E3828310}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20355" yWindow="2415" windowWidth="16605" windowHeight="15345" firstSheet="2" activeTab="3" xr2:uid="{007C2ECE-7E90-4717-B1E7-3A143C146FF0}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="20985" firstSheet="2" activeTab="3" xr2:uid="{007C2ECE-7E90-4717-B1E7-3A143C146FF0}"/>
   </bookViews>
   <sheets>
     <sheet name="Valores" sheetId="1" r:id="rId1"/>
@@ -898,7 +898,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="396" uniqueCount="171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="491" uniqueCount="185">
   <si>
     <t>Tipo Objeto Dominio</t>
   </si>
@@ -1128,24 +1128,9 @@
     <t>Debe contener al menos una minuscula un carácter especial y un número, No puede contener espacios.</t>
   </si>
   <si>
-    <t>tipoInmueble</t>
-  </si>
-  <si>
-    <t>numeroVivienda</t>
-  </si>
-  <si>
-    <t>ZonaInmueble</t>
-  </si>
-  <si>
-    <t>Casa/Apartamento, dónde cada uno representa el tipo de inmueble que es el inmueble dónde habitan los residentes.</t>
-  </si>
-  <si>
     <t>Entero</t>
   </si>
   <si>
-    <t>Representa la zona dónde se encuentran varios inmuebles.</t>
-  </si>
-  <si>
     <t>numeroDocumento</t>
   </si>
   <si>
@@ -1206,18 +1191,9 @@
     <t>Es un dato que hace que cada inmueble sea único.</t>
   </si>
   <si>
-    <t>Es un dato que representa al nombre de un inmueble Casa, apartamento ETC.</t>
-  </si>
-  <si>
     <t>Este atributo representa el número especifico del inmueble.</t>
   </si>
   <si>
-    <t>Ubicación unica de un inmueble</t>
-  </si>
-  <si>
-    <t>No es posible tener mas de un tipo inmueble que tenga el mismo número de vivienda más la misma zona inmueble.</t>
-  </si>
-  <si>
     <t>Registrar</t>
   </si>
   <si>
@@ -1239,9 +1215,6 @@
     <t>No requerido</t>
   </si>
   <si>
-    <t>Filtro {ZonaInmueble.identificador}/Listar {ZonaInmueble.nombre}</t>
-  </si>
-  <si>
     <t>Acción dónde un administrador podrá crear un inmueble.</t>
   </si>
   <si>
@@ -1368,30 +1341,6 @@
     <t>Asegurar que los datos requeridos para registrar la información del nuevo residente sean válidos a nivel de tipo de dato,formato, rango, longitud y obligatoriedad.</t>
   </si>
   <si>
-    <t>Se debe asegurar que no exista otro Residente registrado con el mismo tipo y numero de documento de identidad.</t>
-  </si>
-  <si>
-    <t>Asegurar que el identificador del residente que se desea registrar  no ha haya sido asignado previamente a otro residente.</t>
-  </si>
-  <si>
-    <t>Se debe asegurar que no exista otro residente registrado con el mismo correo electronico.</t>
-  </si>
-  <si>
-    <t>En caso de que la politica no se cumpla, se deberá generar un mensaje de error indicando que se intenta registrar un residente que tiene el mismo tipo y número de documento de un residente ya existente.</t>
-  </si>
-  <si>
-    <t>En caso de que la politica no se cumpla, se deberá generar un mensaje de error indicando que se intenta registrar un residente con el mismo número de contacto que otro residente ya existente.</t>
-  </si>
-  <si>
-    <t>Se debe asegurar que no exista otro Residente registrado con el mismo número de contacto.</t>
-  </si>
-  <si>
-    <t>En caso de que la politica no se cumpla, se deberá generar un mensaje de error indicando que se intenta registrar un residente que esta previamente registrado con el mismo identificador.</t>
-  </si>
-  <si>
-    <t>En caso de que la politica no se cumpla, se deberá generar un mensaje de error indicando que se intenta registrar un residente con el mismo correo electronico que otro residente ya existente.</t>
-  </si>
-  <si>
     <t>Detengo el proceso hasta que se ingresen datos valido para la creación del residente.</t>
   </si>
   <si>
@@ -1411,13 +1360,106 @@
   </si>
   <si>
     <t>Listado de todos los residentes que cumplen con los filtros de consulta: 1. Devuelve vacio cuando no se cumplan parametros de consulta. 2.Devuelve el listado de los residentes que cumplan con el filtro de consulta.</t>
+  </si>
+  <si>
+    <t>identificadorConjuntoResidencial</t>
+  </si>
+  <si>
+    <t>nombreConjuntoResidencial</t>
+  </si>
+  <si>
+    <t>identificadorTipoInmueble</t>
+  </si>
+  <si>
+    <t>nombreTipoInmueble</t>
+  </si>
+  <si>
+    <t>identificadorInmueble</t>
+  </si>
+  <si>
+    <t>numeroViviendaInmueble</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Datos unicos para comunicación </t>
+  </si>
+  <si>
+    <t>No es posible tener otra trasferencia identedica.</t>
+  </si>
+  <si>
+    <t>Es un dato que hace que cada conjunto residencial sea único.</t>
+  </si>
+  <si>
+    <t>Quitar espacios en blanco al inicio, al final, y entre palabras.</t>
+  </si>
+  <si>
+    <t>Es un dato que representa al nombre de un conjunto residencial</t>
+  </si>
+  <si>
+    <t>Es un dato que hace que cada tipo de inmueble sea único.</t>
+  </si>
+  <si>
+    <t>Este atributo representa el número especifico del tipo de inmueble inmueble.</t>
+  </si>
+  <si>
+    <t>identificadorTipoZonaInmueble</t>
+  </si>
+  <si>
+    <t>nombreTipoZonaInmueble</t>
+  </si>
+  <si>
+    <t>identificadorZonaInmueble</t>
+  </si>
+  <si>
+    <t>numeroZonaInmuebleZonaInmueble</t>
+  </si>
+  <si>
+    <t>Es un dato que hace que cada zona imueble sea única.</t>
+  </si>
+  <si>
+    <t>solo números</t>
+  </si>
+  <si>
+    <t>Quitar espacios en blanco al inicio y al final.</t>
+  </si>
+  <si>
+    <t>Es el atributo que representa el numero que pertenece a un tipo de zona inmueble .</t>
+  </si>
+  <si>
+    <t>Residente debe estar asociado a un Inmueble existente en el contexto Conjuntos Residenciales</t>
+  </si>
+  <si>
+    <t>Los datos personales del residente deben ser válidos.</t>
+  </si>
+  <si>
+    <t>En caso de que la politica no se cumpla, se deberá generar un mensaje de error indicando que se intenta registrar un residente que tiene asociado un inmueble que no existe.</t>
+  </si>
+  <si>
+    <t>En caso de que la politica no se cumpla, se deberá generar un mensaje de error indicando que se intenta registrar un residente el cual los datos no son validos.</t>
+  </si>
+  <si>
+    <t>Se debe asegurar que exista.</t>
+  </si>
+  <si>
+    <t>Los datos personales y la referencia al Inmueble deben ser válidos.</t>
+  </si>
+  <si>
+    <t>En caso de que la politica no se cumpla, se deberá generar un mensaje de error indicando que el residenten que intenta modificar no existe</t>
+  </si>
+  <si>
+    <t>Detengo el proceso hasta que se encuenre un residente existente para modificar.</t>
+  </si>
+  <si>
+    <t>En caso de que la politica no se cumpla, se deberá generar un mensaje de error indicando que la referencia del inmueble o los datos personales no son validos.</t>
+  </si>
+  <si>
+    <t>Detengo el preceso hasta que se inserten datos validos .</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1482,6 +1524,12 @@
       <u/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1979,7 +2027,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="143">
+  <cellXfs count="147">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2120,12 +2168,147 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="33" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="8" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="26" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="27" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="30" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="31" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2135,60 +2318,24 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="33" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="33" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="33" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="34" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2261,143 +2408,56 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="26" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="27" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="30" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="31" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="33" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="8" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="33" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="8" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="30" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="31" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="9" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="10" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="33" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="12" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2791,10 +2851,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="67" t="s">
+      <c r="A1" s="56" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="68"/>
+      <c r="B1" s="57"/>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -2904,11 +2964,11 @@
       <c r="A1" s="40" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="69" t="s">
+      <c r="B1" s="58" t="s">
         <v>61</v>
       </c>
-      <c r="C1" s="69"/>
-      <c r="D1" s="70"/>
+      <c r="C1" s="58"/>
+      <c r="D1" s="59"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
@@ -2934,7 +2994,7 @@
       <c r="C3" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="71" t="str">
+      <c r="D3" s="60" t="str">
         <f>$B$1</f>
         <v>Residentes</v>
       </c>
@@ -2950,7 +3010,7 @@
         <f>Valores!$A$4</f>
         <v>Referenciado</v>
       </c>
-      <c r="D4" s="72"/>
+      <c r="D4" s="61"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -2966,7 +3026,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3CD2E3E-2179-4007-8743-BED3F3BF1317}">
-  <dimension ref="A1:U32"/>
+  <dimension ref="A1:U33"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="23.85546875" style="7" bestFit="1" customWidth="1"/>
@@ -2995,73 +3055,73 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A1" s="124" t="s">
+      <c r="A1" s="77" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="124"/>
-      <c r="C1" s="124"/>
-      <c r="D1" s="124"/>
-      <c r="E1" s="124"/>
-      <c r="F1" s="124"/>
-      <c r="G1" s="124"/>
-      <c r="H1" s="124"/>
-      <c r="I1" s="124"/>
-      <c r="J1" s="124"/>
-      <c r="K1" s="124"/>
-      <c r="L1" s="124"/>
-      <c r="M1" s="124"/>
-      <c r="N1" s="124"/>
-      <c r="O1" s="124"/>
-      <c r="P1" s="124"/>
-      <c r="Q1" s="124"/>
+      <c r="B1" s="77"/>
+      <c r="C1" s="77"/>
+      <c r="D1" s="77"/>
+      <c r="E1" s="77"/>
+      <c r="F1" s="77"/>
+      <c r="G1" s="77"/>
+      <c r="H1" s="77"/>
+      <c r="I1" s="77"/>
+      <c r="J1" s="77"/>
+      <c r="K1" s="77"/>
+      <c r="L1" s="77"/>
+      <c r="M1" s="77"/>
+      <c r="N1" s="77"/>
+      <c r="O1" s="77"/>
+      <c r="P1" s="77"/>
+      <c r="Q1" s="77"/>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A2" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="B2" s="125" t="str">
+      <c r="B2" s="78" t="str">
         <f>'Listado Objetos de Dominio'!A3</f>
         <v>Residente</v>
       </c>
-      <c r="C2" s="125"/>
-      <c r="D2" s="125"/>
-      <c r="E2" s="125"/>
-      <c r="F2" s="125"/>
-      <c r="G2" s="125"/>
-      <c r="H2" s="125"/>
-      <c r="I2" s="125"/>
-      <c r="J2" s="125"/>
-      <c r="K2" s="125"/>
-      <c r="L2" s="125"/>
-      <c r="M2" s="125"/>
-      <c r="N2" s="125"/>
-      <c r="O2" s="125"/>
-      <c r="P2" s="125"/>
-      <c r="Q2" s="125"/>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="78"/>
+      <c r="H2" s="78"/>
+      <c r="I2" s="78"/>
+      <c r="J2" s="78"/>
+      <c r="K2" s="78"/>
+      <c r="L2" s="78"/>
+      <c r="M2" s="78"/>
+      <c r="N2" s="78"/>
+      <c r="O2" s="78"/>
+      <c r="P2" s="78"/>
+      <c r="Q2" s="78"/>
     </row>
     <row r="3" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="B3" s="126" t="str">
+      <c r="B3" s="79" t="str">
         <f>'Listado Objetos de Dominio'!B3</f>
         <v>Objeto de dominio que representa a un residente que vive dentro de un inmueble en un conjunto residencial</v>
       </c>
-      <c r="C3" s="126"/>
-      <c r="D3" s="126"/>
-      <c r="E3" s="126"/>
-      <c r="F3" s="126"/>
-      <c r="G3" s="126"/>
-      <c r="H3" s="126"/>
-      <c r="I3" s="126"/>
-      <c r="J3" s="126"/>
-      <c r="K3" s="126"/>
-      <c r="L3" s="126"/>
-      <c r="M3" s="126"/>
-      <c r="N3" s="126"/>
-      <c r="O3" s="126"/>
-      <c r="P3" s="126"/>
-      <c r="Q3" s="126"/>
+      <c r="C3" s="79"/>
+      <c r="D3" s="79"/>
+      <c r="E3" s="79"/>
+      <c r="F3" s="79"/>
+      <c r="G3" s="79"/>
+      <c r="H3" s="79"/>
+      <c r="I3" s="79"/>
+      <c r="J3" s="79"/>
+      <c r="K3" s="79"/>
+      <c r="L3" s="79"/>
+      <c r="M3" s="79"/>
+      <c r="N3" s="79"/>
+      <c r="O3" s="79"/>
+      <c r="P3" s="79"/>
+      <c r="Q3" s="79"/>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A4" s="15" t="s">
@@ -3116,18 +3176,18 @@
         <v>2</v>
       </c>
       <c r="R4" s="42" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="S4" s="43" t="str">
         <f>A30</f>
         <v>Buscar</v>
       </c>
       <c r="T4" s="44" t="str">
+        <f>A28</f>
+        <v>Modificar</v>
+      </c>
+      <c r="U4" s="45" t="str">
         <f>A31</f>
-        <v>Modificar</v>
-      </c>
-      <c r="U4" s="45" t="str">
-        <f>A32</f>
         <v>Eliminar</v>
       </c>
     </row>
@@ -3169,19 +3229,19 @@
         <v>41</v>
       </c>
       <c r="Q5" s="20" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="R5" s="46" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="S5" s="23" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="T5" s="24" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="U5" s="25" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
     </row>
     <row r="6" spans="1:21" ht="40.5" x14ac:dyDescent="0.25">
@@ -3224,19 +3284,19 @@
         <v>42</v>
       </c>
       <c r="Q6" s="20" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="R6" s="46" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="S6" s="23" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="T6" s="24" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="U6" s="25" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
     </row>
     <row r="7" spans="1:21" ht="40.5" x14ac:dyDescent="0.25">
@@ -3279,19 +3339,19 @@
         <v>42</v>
       </c>
       <c r="Q7" s="20" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="R7" s="46" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="S7" s="23" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="T7" s="24" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="U7" s="25" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
     </row>
     <row r="8" spans="1:21" ht="40.5" x14ac:dyDescent="0.25">
@@ -3334,24 +3394,24 @@
         <v>42</v>
       </c>
       <c r="Q8" s="20" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="R8" s="46" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="S8" s="23" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="T8" s="24" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="U8" s="25" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
     </row>
     <row r="9" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A9" s="18" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="B9" s="19" t="s">
         <v>13</v>
@@ -3387,19 +3447,19 @@
         <v>42</v>
       </c>
       <c r="Q9" s="20" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="R9" s="46" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="S9" s="23" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="T9" s="24" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="U9" s="25" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.25">
@@ -3436,24 +3496,24 @@
         <v>42</v>
       </c>
       <c r="Q10" s="20" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="R10" s="46" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="S10" s="23" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="T10" s="24" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="U10" s="25" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
     </row>
     <row r="11" spans="1:21" ht="40.5" x14ac:dyDescent="0.25">
       <c r="A11" s="18" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="B11" s="19" t="s">
         <v>13</v>
@@ -3491,24 +3551,24 @@
         <v>42</v>
       </c>
       <c r="Q11" s="20" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="R11" s="46" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="S11" s="23" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="T11" s="24" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="U11" s="25" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
     </row>
     <row r="12" spans="1:21" ht="40.5" x14ac:dyDescent="0.25">
       <c r="A12" s="18" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="B12" s="19" t="s">
         <v>9</v>
@@ -3546,19 +3606,19 @@
         <v>42</v>
       </c>
       <c r="Q12" s="20" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="R12" s="46" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="S12" s="23" t="s">
-        <v>169</v>
+        <v>152</v>
       </c>
       <c r="T12" s="24" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="U12" s="25" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
     </row>
     <row r="13" spans="1:21" ht="67.5" x14ac:dyDescent="0.25">
@@ -3601,19 +3661,19 @@
         <v>42</v>
       </c>
       <c r="Q13" s="20" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="R13" s="46" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="S13" s="23" t="s">
-        <v>169</v>
+        <v>152</v>
       </c>
       <c r="T13" s="24" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="U13" s="25" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
     </row>
     <row r="14" spans="1:21" ht="30" x14ac:dyDescent="0.25">
@@ -3653,34 +3713,34 @@
         <v>66</v>
       </c>
       <c r="R14" s="46" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="S14" s="31" t="s">
-        <v>168</v>
+        <v>151</v>
       </c>
       <c r="T14" s="24" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="U14" s="25" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A16" s="127" t="s">
-        <v>93</v>
-      </c>
-      <c r="B16" s="127"/>
-      <c r="C16" s="127"/>
-      <c r="E16" s="127" t="s">
-        <v>95</v>
-      </c>
-      <c r="F16" s="127"/>
-      <c r="G16" s="127"/>
-      <c r="I16" s="127" t="s">
+      <c r="A16" s="63" t="s">
+        <v>88</v>
+      </c>
+      <c r="B16" s="63"/>
+      <c r="C16" s="63"/>
+      <c r="E16" s="63" t="s">
+        <v>90</v>
+      </c>
+      <c r="F16" s="63"/>
+      <c r="G16" s="63"/>
+      <c r="I16" s="63" t="s">
         <v>47</v>
       </c>
-      <c r="J16" s="127"/>
-      <c r="K16" s="127"/>
+      <c r="J16" s="63"/>
+      <c r="K16" s="63"/>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A17" s="26" t="s">
@@ -3712,113 +3772,113 @@
       </c>
     </row>
     <row r="18" spans="1:19" ht="25.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="138" t="s">
+      <c r="A18" s="64" t="s">
         <v>50</v>
       </c>
-      <c r="B18" s="139" t="s">
+      <c r="B18" s="65" t="s">
+        <v>89</v>
+      </c>
+      <c r="C18" s="62" t="s">
+        <v>71</v>
+      </c>
+      <c r="E18" s="65" t="s">
         <v>94</v>
       </c>
-      <c r="C18" s="140" t="s">
-        <v>71</v>
-      </c>
-      <c r="E18" s="139" t="s">
-        <v>99</v>
-      </c>
-      <c r="F18" s="139" t="s">
-        <v>96</v>
-      </c>
-      <c r="G18" s="140" t="s">
-        <v>83</v>
+      <c r="F18" s="65" t="s">
+        <v>91</v>
+      </c>
+      <c r="G18" s="62" t="s">
+        <v>78</v>
       </c>
       <c r="H18" s="39"/>
-      <c r="I18" s="138" t="s">
-        <v>100</v>
-      </c>
-      <c r="J18" s="139" t="s">
-        <v>97</v>
-      </c>
-      <c r="K18" s="140" t="s">
-        <v>98</v>
+      <c r="I18" s="64" t="s">
+        <v>95</v>
+      </c>
+      <c r="J18" s="65" t="s">
+        <v>92</v>
+      </c>
+      <c r="K18" s="62" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="19" spans="1:19" ht="25.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="138"/>
-      <c r="B19" s="139"/>
-      <c r="C19" s="140"/>
-      <c r="E19" s="139"/>
-      <c r="F19" s="139"/>
-      <c r="G19" s="140"/>
+      <c r="A19" s="64"/>
+      <c r="B19" s="65"/>
+      <c r="C19" s="62"/>
+      <c r="E19" s="65"/>
+      <c r="F19" s="65"/>
+      <c r="G19" s="62"/>
       <c r="H19" s="39"/>
-      <c r="I19" s="138"/>
-      <c r="J19" s="139"/>
-      <c r="K19" s="140"/>
+      <c r="I19" s="64"/>
+      <c r="J19" s="65"/>
+      <c r="K19" s="62"/>
     </row>
     <row r="20" spans="1:19" ht="25.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="138"/>
-      <c r="B20" s="139"/>
-      <c r="C20" s="140" t="s">
-        <v>82</v>
-      </c>
-      <c r="E20" s="139"/>
-      <c r="F20" s="139"/>
-      <c r="G20" s="140"/>
-      <c r="I20" s="138"/>
-      <c r="J20" s="139"/>
-      <c r="K20" s="140"/>
+      <c r="A20" s="64"/>
+      <c r="B20" s="65"/>
+      <c r="C20" s="62" t="s">
+        <v>77</v>
+      </c>
+      <c r="E20" s="65"/>
+      <c r="F20" s="65"/>
+      <c r="G20" s="62"/>
+      <c r="I20" s="64"/>
+      <c r="J20" s="65"/>
+      <c r="K20" s="62"/>
     </row>
     <row r="21" spans="1:19" ht="25.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="138"/>
-      <c r="B21" s="139"/>
-      <c r="C21" s="140"/>
-      <c r="E21" s="139"/>
-      <c r="F21" s="139"/>
-      <c r="G21" s="140"/>
-      <c r="I21" s="138"/>
-      <c r="J21" s="139"/>
-      <c r="K21" s="140"/>
+      <c r="A21" s="64"/>
+      <c r="B21" s="65"/>
+      <c r="C21" s="62"/>
+      <c r="E21" s="65"/>
+      <c r="F21" s="65"/>
+      <c r="G21" s="62"/>
+      <c r="I21" s="64"/>
+      <c r="J21" s="65"/>
+      <c r="K21" s="62"/>
     </row>
     <row r="22" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="23" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A23" s="128" t="s">
+      <c r="A23" s="80" t="s">
         <v>51</v>
       </c>
-      <c r="B23" s="129"/>
-      <c r="C23" s="132" t="s">
+      <c r="B23" s="81"/>
+      <c r="C23" s="84" t="s">
         <v>2</v>
       </c>
-      <c r="D23" s="133"/>
-      <c r="E23" s="133"/>
-      <c r="F23" s="133"/>
-      <c r="G23" s="129"/>
-      <c r="H23" s="119" t="s">
+      <c r="D23" s="85"/>
+      <c r="E23" s="85"/>
+      <c r="F23" s="85"/>
+      <c r="G23" s="81"/>
+      <c r="H23" s="72" t="s">
         <v>52</v>
       </c>
-      <c r="I23" s="136"/>
-      <c r="J23" s="137"/>
-      <c r="K23" s="119" t="s">
+      <c r="I23" s="88"/>
+      <c r="J23" s="89"/>
+      <c r="K23" s="72" t="s">
         <v>53</v>
       </c>
-      <c r="L23" s="136"/>
-      <c r="M23" s="136"/>
-      <c r="N23" s="136"/>
-      <c r="O23" s="137"/>
-      <c r="P23" s="119" t="s">
+      <c r="L23" s="88"/>
+      <c r="M23" s="88"/>
+      <c r="N23" s="88"/>
+      <c r="O23" s="89"/>
+      <c r="P23" s="72" t="s">
         <v>54</v>
       </c>
-      <c r="Q23" s="137"/>
-      <c r="R23" s="119" t="s">
+      <c r="Q23" s="89"/>
+      <c r="R23" s="72" t="s">
         <v>55</v>
       </c>
-      <c r="S23" s="120"/>
+      <c r="S23" s="73"/>
     </row>
     <row r="24" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A24" s="130"/>
-      <c r="B24" s="131"/>
-      <c r="C24" s="134"/>
-      <c r="D24" s="135"/>
-      <c r="E24" s="135"/>
-      <c r="F24" s="135"/>
-      <c r="G24" s="131"/>
+      <c r="A24" s="82"/>
+      <c r="B24" s="83"/>
+      <c r="C24" s="86"/>
+      <c r="D24" s="87"/>
+      <c r="E24" s="87"/>
+      <c r="F24" s="87"/>
+      <c r="G24" s="83"/>
       <c r="H24" s="47" t="s">
         <v>56</v>
       </c>
@@ -3831,12 +3891,12 @@
       <c r="K24" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="L24" s="121" t="s">
+      <c r="L24" s="74" t="s">
         <v>2</v>
       </c>
-      <c r="M24" s="122"/>
-      <c r="N24" s="122"/>
-      <c r="O24" s="123"/>
+      <c r="M24" s="75"/>
+      <c r="N24" s="75"/>
+      <c r="O24" s="76"/>
       <c r="P24" s="27" t="s">
         <v>58</v>
       </c>
@@ -3851,180 +3911,193 @@
       </c>
     </row>
     <row r="25" spans="1:19" ht="45" x14ac:dyDescent="0.25">
-      <c r="A25" s="97" t="s">
-        <v>106</v>
-      </c>
-      <c r="B25" s="98"/>
-      <c r="C25" s="101" t="s">
-        <v>144</v>
-      </c>
-      <c r="D25" s="102"/>
-      <c r="E25" s="102"/>
-      <c r="F25" s="102"/>
-      <c r="G25" s="103"/>
-      <c r="H25" s="107" t="str">
+      <c r="A25" s="90" t="s">
+        <v>98</v>
+      </c>
+      <c r="B25" s="91"/>
+      <c r="C25" s="94" t="s">
+        <v>135</v>
+      </c>
+      <c r="D25" s="95"/>
+      <c r="E25" s="95"/>
+      <c r="F25" s="95"/>
+      <c r="G25" s="96"/>
+      <c r="H25" s="100" t="str">
         <f>_xlfn.CONCAT("datos",B2)</f>
         <v>datosResidente</v>
       </c>
-      <c r="I25" s="109" t="str">
+      <c r="I25" s="102" t="str">
         <f>B2</f>
         <v>Residente</v>
       </c>
-      <c r="J25" s="111" t="str">
+      <c r="J25" s="104" t="str">
         <f>_xlfn.CONCAT("Corresponde al objeto que internamente contiene los datos necesarios para crear un nuevo ",B2,)</f>
         <v>Corresponde al objeto que internamente contiene los datos necesarios para crear un nuevo Residente</v>
       </c>
       <c r="K25" s="48"/>
-      <c r="L25" s="113"/>
-      <c r="M25" s="114"/>
-      <c r="N25" s="114"/>
-      <c r="O25" s="115"/>
+      <c r="L25" s="66"/>
+      <c r="M25" s="67"/>
+      <c r="N25" s="67"/>
+      <c r="O25" s="68"/>
       <c r="P25" s="13" t="s">
-        <v>150</v>
+        <v>141</v>
       </c>
       <c r="Q25" s="12" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="R25" s="12" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="S25" s="49" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
     </row>
     <row r="26" spans="1:19" ht="30" x14ac:dyDescent="0.25">
-      <c r="A26" s="99"/>
-      <c r="B26" s="100"/>
-      <c r="C26" s="104"/>
-      <c r="D26" s="105"/>
-      <c r="E26" s="105"/>
-      <c r="F26" s="105"/>
-      <c r="G26" s="106"/>
-      <c r="H26" s="108"/>
-      <c r="I26" s="110"/>
-      <c r="J26" s="112"/>
-      <c r="K26" s="57"/>
-      <c r="L26" s="116"/>
-      <c r="M26" s="117"/>
-      <c r="N26" s="117"/>
-      <c r="O26" s="118"/>
+      <c r="A26" s="92"/>
+      <c r="B26" s="93"/>
+      <c r="C26" s="97"/>
+      <c r="D26" s="98"/>
+      <c r="E26" s="98"/>
+      <c r="F26" s="98"/>
+      <c r="G26" s="99"/>
+      <c r="H26" s="101"/>
+      <c r="I26" s="103"/>
+      <c r="J26" s="105"/>
+      <c r="K26" s="50"/>
+      <c r="L26" s="69"/>
+      <c r="M26" s="70"/>
+      <c r="N26" s="70"/>
+      <c r="O26" s="71"/>
       <c r="P26" s="13" t="s">
-        <v>151</v>
+        <v>142</v>
       </c>
       <c r="Q26" s="12" t="s">
-        <v>156</v>
+        <v>175</v>
       </c>
       <c r="R26" s="12" t="s">
-        <v>159</v>
+        <v>177</v>
       </c>
       <c r="S26" s="49" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
     </row>
     <row r="27" spans="1:19" ht="30" x14ac:dyDescent="0.25">
-      <c r="A27" s="99"/>
-      <c r="B27" s="100"/>
-      <c r="C27" s="104"/>
-      <c r="D27" s="105"/>
-      <c r="E27" s="105"/>
-      <c r="F27" s="105"/>
-      <c r="G27" s="106"/>
-      <c r="H27" s="108"/>
-      <c r="I27" s="110"/>
-      <c r="J27" s="112"/>
-      <c r="K27" s="57"/>
-      <c r="L27" s="116"/>
-      <c r="M27" s="117"/>
-      <c r="N27" s="117"/>
-      <c r="O27" s="118"/>
+      <c r="A27" s="92"/>
+      <c r="B27" s="93"/>
+      <c r="C27" s="97"/>
+      <c r="D27" s="98"/>
+      <c r="E27" s="98"/>
+      <c r="F27" s="98"/>
+      <c r="G27" s="99"/>
+      <c r="H27" s="101"/>
+      <c r="I27" s="103"/>
+      <c r="J27" s="105"/>
+      <c r="K27" s="50"/>
+      <c r="L27" s="69"/>
+      <c r="M27" s="70"/>
+      <c r="N27" s="70"/>
+      <c r="O27" s="71"/>
       <c r="P27" s="13" t="s">
-        <v>152</v>
+        <v>143</v>
       </c>
       <c r="Q27" s="12" t="s">
-        <v>161</v>
+        <v>176</v>
       </c>
       <c r="R27" s="12" t="s">
-        <v>160</v>
+        <v>178</v>
       </c>
       <c r="S27" s="49" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="28" spans="1:19" ht="45" x14ac:dyDescent="0.25">
-      <c r="A28" s="99"/>
-      <c r="B28" s="100"/>
-      <c r="C28" s="104"/>
-      <c r="D28" s="105"/>
-      <c r="E28" s="105"/>
-      <c r="F28" s="105"/>
-      <c r="G28" s="106"/>
-      <c r="H28" s="108"/>
-      <c r="I28" s="110"/>
-      <c r="J28" s="112"/>
-      <c r="K28" s="57"/>
-      <c r="L28" s="116"/>
-      <c r="M28" s="117"/>
-      <c r="N28" s="117"/>
-      <c r="O28" s="118"/>
-      <c r="P28" s="13" t="s">
-        <v>153</v>
-      </c>
-      <c r="Q28" s="12" t="s">
-        <v>157</v>
-      </c>
-      <c r="R28" s="12" t="s">
-        <v>162</v>
-      </c>
-      <c r="S28" s="49" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="28" spans="1:19" ht="30" x14ac:dyDescent="0.25">
+      <c r="A28" s="133" t="s">
+        <v>127</v>
+      </c>
+      <c r="B28" s="134"/>
+      <c r="C28" s="137" t="s">
+        <v>137</v>
+      </c>
+      <c r="D28" s="138"/>
+      <c r="E28" s="138"/>
+      <c r="F28" s="138"/>
+      <c r="G28" s="139"/>
+      <c r="H28" s="143" t="str">
+        <f>_xlfn.CONCAT("datos",B2)</f>
+        <v>datosResidente</v>
+      </c>
+      <c r="I28" s="145" t="str">
+        <f>B2</f>
+        <v>Residente</v>
+      </c>
+      <c r="J28" s="143" t="str">
+        <f>_xlfn.CONCAT("Corresponde a los datos que se van a modificar del ",B2)</f>
+        <v>Corresponde a los datos que se van a modificar del Residente</v>
+      </c>
+      <c r="K28" s="34"/>
+      <c r="L28" s="127"/>
+      <c r="M28" s="128"/>
+      <c r="N28" s="128"/>
+      <c r="O28" s="129"/>
+      <c r="P28" s="53" t="s">
+        <v>144</v>
+      </c>
+      <c r="Q28" s="53" t="s">
+        <v>179</v>
+      </c>
+      <c r="R28" s="53" t="s">
+        <v>181</v>
+      </c>
+      <c r="S28" s="53" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="29" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="135"/>
+      <c r="B29" s="136"/>
+      <c r="C29" s="140"/>
+      <c r="D29" s="141"/>
+      <c r="E29" s="141"/>
+      <c r="F29" s="141"/>
+      <c r="G29" s="142"/>
+      <c r="H29" s="144"/>
+      <c r="I29" s="146"/>
+      <c r="J29" s="144"/>
+      <c r="K29" s="34"/>
+      <c r="L29" s="127"/>
+      <c r="M29" s="128"/>
+      <c r="N29" s="128"/>
+      <c r="O29" s="129"/>
+      <c r="P29" s="53" t="s">
+        <v>145</v>
+      </c>
+      <c r="Q29" s="53" t="s">
+        <v>180</v>
+      </c>
+      <c r="R29" s="53" t="s">
+        <v>183</v>
+      </c>
+      <c r="S29" s="54" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="30" spans="1:19" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="114" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="29" spans="1:19" ht="30" x14ac:dyDescent="0.25">
-      <c r="A29" s="50"/>
-      <c r="B29" s="51"/>
-      <c r="C29" s="52"/>
-      <c r="D29" s="53"/>
-      <c r="E29" s="53"/>
-      <c r="F29" s="53"/>
-      <c r="G29" s="54"/>
-      <c r="H29" s="55"/>
-      <c r="I29" s="65"/>
-      <c r="J29" s="56"/>
-      <c r="K29" s="57"/>
-      <c r="L29" s="58"/>
-      <c r="M29" s="59"/>
-      <c r="N29" s="59"/>
-      <c r="O29" s="60"/>
-      <c r="P29" s="13" t="s">
-        <v>154</v>
-      </c>
-      <c r="Q29" s="12" t="s">
-        <v>158</v>
-      </c>
-      <c r="R29" s="12" t="s">
-        <v>163</v>
-      </c>
-      <c r="S29" s="49" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="30" spans="1:19" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="81" t="s">
-        <v>131</v>
-      </c>
-      <c r="B30" s="82"/>
-      <c r="C30" s="83" t="s">
-        <v>145</v>
-      </c>
-      <c r="D30" s="84"/>
-      <c r="E30" s="84"/>
-      <c r="F30" s="84"/>
-      <c r="G30" s="85"/>
+      <c r="B30" s="115"/>
+      <c r="C30" s="116" t="s">
+        <v>136</v>
+      </c>
+      <c r="D30" s="117"/>
+      <c r="E30" s="117"/>
+      <c r="F30" s="117"/>
+      <c r="G30" s="118"/>
       <c r="H30" s="30" t="str">
         <f>_xlfn.CONCAT("datos",B2)</f>
         <v>datosResidente</v>
       </c>
-      <c r="I30" s="66" t="str">
+      <c r="I30" s="55" t="str">
         <f>B2</f>
         <v>Residente</v>
       </c>
@@ -4033,81 +4106,79 @@
         <v>Corresponde a un objeto que contiene los filtros de consulta de un  Residente de un conjunto residencial.</v>
       </c>
       <c r="K30" s="41" t="s">
+        <v>140</v>
+      </c>
+      <c r="L30" s="119" t="s">
+        <v>153</v>
+      </c>
+      <c r="M30" s="120"/>
+      <c r="N30" s="120"/>
+      <c r="O30" s="121"/>
+      <c r="P30" s="23" t="s">
+        <v>148</v>
+      </c>
+      <c r="Q30" s="31" t="s">
+        <v>126</v>
+      </c>
+      <c r="R30" s="31" t="s">
+        <v>108</v>
+      </c>
+      <c r="S30" s="51" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="31" spans="1:19" ht="30" x14ac:dyDescent="0.25">
+      <c r="A31" s="106" t="s">
+        <v>133</v>
+      </c>
+      <c r="B31" s="107"/>
+      <c r="C31" s="108" t="s">
+        <v>138</v>
+      </c>
+      <c r="D31" s="109"/>
+      <c r="E31" s="109"/>
+      <c r="F31" s="109"/>
+      <c r="G31" s="110"/>
+      <c r="H31" s="35" t="s">
+        <v>39</v>
+      </c>
+      <c r="I31" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="J31" s="35" t="str">
+        <f>_xlfn.CONCAT("Corresponde al identificador del ",$B$2,"  que se quiere dar de baja.")</f>
+        <v>Corresponde al identificador del Residente  que se quiere dar de baja.</v>
+      </c>
+      <c r="K31" s="36"/>
+      <c r="L31" s="111"/>
+      <c r="M31" s="112"/>
+      <c r="N31" s="112"/>
+      <c r="O31" s="113"/>
+      <c r="P31" s="25" t="s">
         <v>149</v>
       </c>
-      <c r="L30" s="86" t="s">
-        <v>170</v>
-      </c>
-      <c r="M30" s="87"/>
-      <c r="N30" s="87"/>
-      <c r="O30" s="88"/>
-      <c r="P30" s="23" t="s">
-        <v>165</v>
-      </c>
-      <c r="Q30" s="31" t="s">
-        <v>135</v>
-      </c>
-      <c r="R30" s="31" t="s">
-        <v>117</v>
-      </c>
-      <c r="S30" s="61" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="31" spans="1:19" ht="30" x14ac:dyDescent="0.25">
-      <c r="A31" s="89" t="s">
-        <v>136</v>
-      </c>
-      <c r="B31" s="90"/>
-      <c r="C31" s="91" t="s">
-        <v>146</v>
-      </c>
-      <c r="D31" s="92"/>
-      <c r="E31" s="92"/>
-      <c r="F31" s="92"/>
-      <c r="G31" s="93"/>
-      <c r="H31" s="32" t="str">
-        <f>_xlfn.CONCAT("datos",B2)</f>
-        <v>datosResidente</v>
-      </c>
-      <c r="I31" s="33" t="str">
-        <f>B2</f>
-        <v>Residente</v>
-      </c>
-      <c r="J31" s="32" t="str">
-        <f>_xlfn.CONCAT("Corresponde a los datos que se van a modificar del ",B2)</f>
-        <v>Corresponde a los datos que se van a modificar del Residente</v>
-      </c>
-      <c r="K31" s="34"/>
-      <c r="L31" s="94"/>
-      <c r="M31" s="95"/>
-      <c r="N31" s="95"/>
-      <c r="O31" s="96"/>
-      <c r="P31" s="62" t="s">
-        <v>166</v>
-      </c>
-      <c r="Q31" s="63" t="s">
-        <v>139</v>
-      </c>
-      <c r="R31" s="63" t="s">
-        <v>167</v>
-      </c>
-      <c r="S31" s="64" t="s">
-        <v>141</v>
+      <c r="Q31" s="37" t="s">
+        <v>130</v>
+      </c>
+      <c r="R31" s="37" t="s">
+        <v>150</v>
+      </c>
+      <c r="S31" s="37" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="32" spans="1:19" ht="30" x14ac:dyDescent="0.25">
-      <c r="A32" s="73" t="s">
-        <v>142</v>
-      </c>
-      <c r="B32" s="74"/>
-      <c r="C32" s="75" t="s">
-        <v>147</v>
-      </c>
-      <c r="D32" s="76"/>
-      <c r="E32" s="76"/>
-      <c r="F32" s="76"/>
-      <c r="G32" s="77"/>
+      <c r="A32" s="106" t="s">
+        <v>133</v>
+      </c>
+      <c r="B32" s="107"/>
+      <c r="C32" s="108" t="s">
+        <v>138</v>
+      </c>
+      <c r="D32" s="109"/>
+      <c r="E32" s="109"/>
+      <c r="F32" s="109"/>
+      <c r="G32" s="110"/>
       <c r="H32" s="35" t="s">
         <v>39</v>
       </c>
@@ -4119,34 +4190,90 @@
         <v>Corresponde al identificador del Residente  que se quiere dar de baja.</v>
       </c>
       <c r="K32" s="36"/>
-      <c r="L32" s="78"/>
-      <c r="M32" s="79"/>
-      <c r="N32" s="79"/>
-      <c r="O32" s="80"/>
+      <c r="L32" s="111"/>
+      <c r="M32" s="112"/>
+      <c r="N32" s="112"/>
+      <c r="O32" s="113"/>
       <c r="P32" s="25" t="s">
-        <v>166</v>
+        <v>149</v>
       </c>
       <c r="Q32" s="37" t="s">
-        <v>139</v>
+        <v>130</v>
       </c>
       <c r="R32" s="37" t="s">
-        <v>167</v>
+        <v>150</v>
       </c>
       <c r="S32" s="37" t="s">
-        <v>141</v>
+        <v>132</v>
+      </c>
+    </row>
+    <row r="33" spans="1:19" ht="30" x14ac:dyDescent="0.25">
+      <c r="A33" s="106" t="s">
+        <v>133</v>
+      </c>
+      <c r="B33" s="107"/>
+      <c r="C33" s="108" t="s">
+        <v>138</v>
+      </c>
+      <c r="D33" s="109"/>
+      <c r="E33" s="109"/>
+      <c r="F33" s="109"/>
+      <c r="G33" s="110"/>
+      <c r="H33" s="35" t="s">
+        <v>39</v>
+      </c>
+      <c r="I33" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="J33" s="35" t="str">
+        <f>_xlfn.CONCAT("Corresponde al identificador del ",$B$2,"  que se quiere dar de baja.")</f>
+        <v>Corresponde al identificador del Residente  que se quiere dar de baja.</v>
+      </c>
+      <c r="K33" s="36"/>
+      <c r="L33" s="111"/>
+      <c r="M33" s="112"/>
+      <c r="N33" s="112"/>
+      <c r="O33" s="113"/>
+      <c r="P33" s="25" t="s">
+        <v>149</v>
+      </c>
+      <c r="Q33" s="37" t="s">
+        <v>130</v>
+      </c>
+      <c r="R33" s="37" t="s">
+        <v>150</v>
+      </c>
+      <c r="S33" s="37" t="s">
+        <v>132</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="38">
-    <mergeCell ref="C20:C21"/>
-    <mergeCell ref="C18:C19"/>
-    <mergeCell ref="G18:G21"/>
-    <mergeCell ref="I16:K16"/>
-    <mergeCell ref="I18:I21"/>
-    <mergeCell ref="K18:K21"/>
-    <mergeCell ref="F18:F21"/>
-    <mergeCell ref="J18:J21"/>
-    <mergeCell ref="L25:O28"/>
+  <mergeCells count="48">
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="C32:G32"/>
+    <mergeCell ref="L32:O32"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="C33:G33"/>
+    <mergeCell ref="L33:O33"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="C31:G31"/>
+    <mergeCell ref="L31:O31"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="C30:G30"/>
+    <mergeCell ref="L30:O30"/>
+    <mergeCell ref="L28:O28"/>
+    <mergeCell ref="A28:B29"/>
+    <mergeCell ref="C28:G29"/>
+    <mergeCell ref="H28:H29"/>
+    <mergeCell ref="I28:I29"/>
+    <mergeCell ref="J28:J29"/>
+    <mergeCell ref="L29:O29"/>
+    <mergeCell ref="A25:B27"/>
+    <mergeCell ref="C25:G27"/>
+    <mergeCell ref="H25:H27"/>
+    <mergeCell ref="I25:I27"/>
+    <mergeCell ref="J25:J27"/>
+    <mergeCell ref="L25:O27"/>
     <mergeCell ref="R23:S23"/>
     <mergeCell ref="L24:O24"/>
     <mergeCell ref="A1:Q1"/>
@@ -4162,21 +4289,16 @@
     <mergeCell ref="B18:B21"/>
     <mergeCell ref="E16:G16"/>
     <mergeCell ref="E18:E21"/>
-    <mergeCell ref="A25:B28"/>
-    <mergeCell ref="C25:G28"/>
-    <mergeCell ref="H25:H28"/>
-    <mergeCell ref="I25:I28"/>
-    <mergeCell ref="J25:J28"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="C32:G32"/>
-    <mergeCell ref="L32:O32"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="C30:G30"/>
-    <mergeCell ref="L30:O30"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="C31:G31"/>
-    <mergeCell ref="L31:O31"/>
+    <mergeCell ref="C20:C21"/>
+    <mergeCell ref="C18:C19"/>
+    <mergeCell ref="G18:G21"/>
+    <mergeCell ref="I16:K16"/>
+    <mergeCell ref="I18:I21"/>
+    <mergeCell ref="K18:K21"/>
+    <mergeCell ref="F18:F21"/>
+    <mergeCell ref="J18:J21"/>
   </mergeCells>
+  <phoneticPr fontId="9" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="A1" location="'Objetos de Dominio'!A1" display="Volver al inicio" xr:uid="{475DC609-B6D5-4D2D-A170-5000DA801120}"/>
     <hyperlink ref="A1:Q1" location="'Listado Objetos de Dominio'!A1" display="&lt;-Volver al inicio" xr:uid="{2CEFD9A1-7256-4CC0-A14B-05D2869A5C81}"/>
@@ -4185,18 +4307,21 @@
     <hyperlink ref="C18" location="Residente!A8" display="tipoDocumento" xr:uid="{54E136A1-DFED-46E9-8B2D-B46752A571BA}"/>
     <hyperlink ref="G18:G21" location="Residente!A11" display="numeroContacto" xr:uid="{822FB009-8280-411A-ABA3-9ECC828AF1D7}"/>
     <hyperlink ref="K18:K21" location="Residente!A12" display="correoElectronico" xr:uid="{6CEB801B-74BD-4ACB-ADC9-1B88A785F9B9}"/>
-    <hyperlink ref="I32" location="'Tipo Relación Institución'!A6" display="'Tipo Relación Institución'!A6" xr:uid="{3F332D65-B743-4C33-8DFA-4072F68B2DBB}"/>
+    <hyperlink ref="I31" location="'Tipo Relación Institución'!A6" display="'Tipo Relación Institución'!A6" xr:uid="{3F332D65-B743-4C33-8DFA-4072F68B2DBB}"/>
     <hyperlink ref="A30:B30" location="Residente!S4" display="Buscar" xr:uid="{ACDDD86B-BF7F-4A39-9668-C238CE60E1B4}"/>
-    <hyperlink ref="A32:B32" location="Residente!U4" display="Eliminar" xr:uid="{7CDD3DA3-7476-4A95-8876-943199D63EA3}"/>
-    <hyperlink ref="A31:B31" location="Residente!T4" display="Modificar" xr:uid="{10406515-93D8-4184-B203-8D732922E6B6}"/>
-    <hyperlink ref="I25:I28" location="Residente!B2" display="Residente!B2" xr:uid="{301FED57-2D15-44DF-AD91-BD00442B7061}"/>
+    <hyperlink ref="A31:B31" location="Residente!U4" display="Eliminar" xr:uid="{7CDD3DA3-7476-4A95-8876-943199D63EA3}"/>
+    <hyperlink ref="I25:I27" location="Residente!B2" display="Residente!B2" xr:uid="{301FED57-2D15-44DF-AD91-BD00442B7061}"/>
     <hyperlink ref="I30" location="Residente!B2" display="Residente!B2" xr:uid="{5A3119CE-AD4B-4D57-88D8-9772937B9648}"/>
-    <hyperlink ref="I31" location="Residente!B2" display="Residente!B2" xr:uid="{7ABB1CDF-640A-4D6A-A4C0-E14A73161812}"/>
-    <hyperlink ref="A25:B28" location="Residente!R4" display="Registrar" xr:uid="{96202AE8-D265-4411-B317-D49A89DD6979}"/>
+    <hyperlink ref="I28" location="Residente!B2" display="Residente!B2" xr:uid="{7ABB1CDF-640A-4D6A-A4C0-E14A73161812}"/>
+    <hyperlink ref="A25:B27" location="Residente!R4" display="Registrar" xr:uid="{96202AE8-D265-4411-B317-D49A89DD6979}"/>
     <hyperlink ref="T4" location="Residente!A30" display="Residente!A30" xr:uid="{5D56BF46-0783-42E4-BCBA-42373B2D338D}"/>
     <hyperlink ref="U4" location="Residente!A31" display="Residente!A31" xr:uid="{1BF78138-4A40-4FEB-9F14-D5CFABAA28FF}"/>
     <hyperlink ref="R4" location="Residente!A25" display="Registrar" xr:uid="{BC21DCA5-C5C3-43EB-BDAE-3B943C74E69A}"/>
     <hyperlink ref="S4" location="Residente!A29" display="Residente!A29" xr:uid="{50909EC4-1171-4363-B829-6AA98DC22077}"/>
+    <hyperlink ref="I32" location="'Tipo Relación Institución'!A6" display="'Tipo Relación Institución'!A6" xr:uid="{0F4FF1C1-0C1C-4525-9FE9-1330D88A37C4}"/>
+    <hyperlink ref="A32:B32" location="Residente!U4" display="Eliminar" xr:uid="{32563D65-E107-4EFB-83C8-D8E6320247E2}"/>
+    <hyperlink ref="I33" location="'Tipo Relación Institución'!A6" display="'Tipo Relación Institución'!A6" xr:uid="{7397B662-9026-4912-9AC6-AEFC024D11F4}"/>
+    <hyperlink ref="A33:B33" location="Residente!U4" display="Eliminar" xr:uid="{2505D7D1-3BE2-464C-B2E7-DF45F3062414}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId2"/>
@@ -4217,12 +4342,12 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE91583B-F698-4020-97FF-1414BFE2C5EB}">
-  <dimension ref="A1:U25"/>
+  <dimension ref="A1:U37"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="23.85546875" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="28.28515625" style="7" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="18.5703125" style="7" customWidth="1"/>
-    <col min="3" max="3" width="18.7109375" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="33.28515625" style="7" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="18.85546875" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11.5703125" style="7" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="19.28515625" style="7" bestFit="1" customWidth="1"/>
@@ -4246,73 +4371,73 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A1" s="124" t="s">
+      <c r="A1" s="77" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="124"/>
-      <c r="C1" s="124"/>
-      <c r="D1" s="124"/>
-      <c r="E1" s="124"/>
-      <c r="F1" s="124"/>
-      <c r="G1" s="124"/>
-      <c r="H1" s="124"/>
-      <c r="I1" s="124"/>
-      <c r="J1" s="124"/>
-      <c r="K1" s="124"/>
-      <c r="L1" s="124"/>
-      <c r="M1" s="124"/>
-      <c r="N1" s="124"/>
-      <c r="O1" s="124"/>
-      <c r="P1" s="124"/>
-      <c r="Q1" s="124"/>
+      <c r="B1" s="77"/>
+      <c r="C1" s="77"/>
+      <c r="D1" s="77"/>
+      <c r="E1" s="77"/>
+      <c r="F1" s="77"/>
+      <c r="G1" s="77"/>
+      <c r="H1" s="77"/>
+      <c r="I1" s="77"/>
+      <c r="J1" s="77"/>
+      <c r="K1" s="77"/>
+      <c r="L1" s="77"/>
+      <c r="M1" s="77"/>
+      <c r="N1" s="77"/>
+      <c r="O1" s="77"/>
+      <c r="P1" s="77"/>
+      <c r="Q1" s="77"/>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A2" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="B2" s="125" t="str">
+      <c r="B2" s="78" t="str">
         <f>'Listado Objetos de Dominio'!A4</f>
         <v>Inmueble</v>
       </c>
-      <c r="C2" s="125"/>
-      <c r="D2" s="125"/>
-      <c r="E2" s="125"/>
-      <c r="F2" s="125"/>
-      <c r="G2" s="125"/>
-      <c r="H2" s="125"/>
-      <c r="I2" s="125"/>
-      <c r="J2" s="125"/>
-      <c r="K2" s="125"/>
-      <c r="L2" s="125"/>
-      <c r="M2" s="125"/>
-      <c r="N2" s="125"/>
-      <c r="O2" s="125"/>
-      <c r="P2" s="125"/>
-      <c r="Q2" s="125"/>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="78"/>
+      <c r="H2" s="78"/>
+      <c r="I2" s="78"/>
+      <c r="J2" s="78"/>
+      <c r="K2" s="78"/>
+      <c r="L2" s="78"/>
+      <c r="M2" s="78"/>
+      <c r="N2" s="78"/>
+      <c r="O2" s="78"/>
+      <c r="P2" s="78"/>
+      <c r="Q2" s="78"/>
     </row>
     <row r="3" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="B3" s="126" t="str">
+      <c r="B3" s="79" t="str">
         <f>'Listado Objetos de Dominio'!B4</f>
         <v xml:space="preserve">Objeto de dominio que representa el inmueble donde vive el residente del conjunto residencial. </v>
       </c>
-      <c r="C3" s="126"/>
-      <c r="D3" s="126"/>
-      <c r="E3" s="126"/>
-      <c r="F3" s="126"/>
-      <c r="G3" s="126"/>
-      <c r="H3" s="126"/>
-      <c r="I3" s="126"/>
-      <c r="J3" s="126"/>
-      <c r="K3" s="126"/>
-      <c r="L3" s="126"/>
-      <c r="M3" s="126"/>
-      <c r="N3" s="126"/>
-      <c r="O3" s="126"/>
-      <c r="P3" s="126"/>
-      <c r="Q3" s="126"/>
+      <c r="C3" s="79"/>
+      <c r="D3" s="79"/>
+      <c r="E3" s="79"/>
+      <c r="F3" s="79"/>
+      <c r="G3" s="79"/>
+      <c r="H3" s="79"/>
+      <c r="I3" s="79"/>
+      <c r="J3" s="79"/>
+      <c r="K3" s="79"/>
+      <c r="L3" s="79"/>
+      <c r="M3" s="79"/>
+      <c r="N3" s="79"/>
+      <c r="O3" s="79"/>
+      <c r="P3" s="79"/>
+      <c r="Q3" s="79"/>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A4" s="15" t="s">
@@ -4367,24 +4492,24 @@
         <v>2</v>
       </c>
       <c r="R4" s="42" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="S4" s="43" t="str">
-        <f>A23</f>
+        <f>A35</f>
         <v>Buscar</v>
       </c>
       <c r="T4" s="44" t="str">
-        <f>A24</f>
+        <f>A36</f>
         <v>Modificar</v>
       </c>
       <c r="U4" s="45" t="str">
-        <f>A25</f>
+        <f>A37</f>
         <v>Eliminar</v>
       </c>
     </row>
     <row r="5" spans="1:21" ht="27" x14ac:dyDescent="0.25">
       <c r="A5" s="18" t="s">
-        <v>39</v>
+        <v>154</v>
       </c>
       <c r="B5" s="19" t="s">
         <v>9</v>
@@ -4420,43 +4545,45 @@
         <v>41</v>
       </c>
       <c r="Q5" s="20" t="s">
+        <v>162</v>
+      </c>
+      <c r="R5" s="46" t="s">
+        <v>99</v>
+      </c>
+      <c r="S5" s="23" t="s">
+        <v>100</v>
+      </c>
+      <c r="T5" s="24" t="s">
         <v>101</v>
       </c>
-      <c r="R5" s="46" t="s">
-        <v>107</v>
-      </c>
-      <c r="S5" s="23" t="s">
-        <v>108</v>
-      </c>
-      <c r="T5" s="24" t="s">
-        <v>109</v>
-      </c>
       <c r="U5" s="25" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="6" spans="1:21" ht="27" x14ac:dyDescent="0.25">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" ht="40.5" x14ac:dyDescent="0.25">
       <c r="A6" s="18" t="s">
-        <v>76</v>
+        <v>155</v>
       </c>
       <c r="B6" s="19" t="s">
         <v>8</v>
       </c>
       <c r="C6" s="19">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D6" s="19">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="E6" s="19"/>
       <c r="F6" s="19"/>
       <c r="G6" s="19"/>
       <c r="H6" s="19"/>
       <c r="I6" s="20" t="s">
-        <v>79</v>
+        <v>44</v>
       </c>
       <c r="J6" s="19"/>
-      <c r="K6" s="21"/>
+      <c r="K6" s="21" t="s">
+        <v>163</v>
+      </c>
       <c r="L6" s="22" t="s">
         <v>42</v>
       </c>
@@ -4473,43 +4600,45 @@
         <v>42</v>
       </c>
       <c r="Q6" s="20" t="s">
+        <v>164</v>
+      </c>
+      <c r="R6" s="46" t="s">
+        <v>99</v>
+      </c>
+      <c r="S6" s="23" t="s">
         <v>102</v>
       </c>
-      <c r="R6" s="46" t="s">
-        <v>107</v>
-      </c>
-      <c r="S6" s="23" t="s">
-        <v>110</v>
-      </c>
       <c r="T6" s="24" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="U6" s="25" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" ht="27" x14ac:dyDescent="0.25">
       <c r="A7" s="18" t="s">
-        <v>77</v>
+        <v>167</v>
       </c>
       <c r="B7" s="19" t="s">
-        <v>80</v>
+        <v>9</v>
       </c>
       <c r="C7" s="19">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="D7" s="19">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="E7" s="19"/>
       <c r="F7" s="19"/>
       <c r="G7" s="19"/>
       <c r="H7" s="19"/>
-      <c r="I7" s="19"/>
+      <c r="I7" s="20" t="s">
+        <v>40</v>
+      </c>
       <c r="J7" s="19"/>
       <c r="K7" s="21"/>
-      <c r="L7" s="19" t="s">
-        <v>42</v>
+      <c r="L7" s="22" t="s">
+        <v>41</v>
       </c>
       <c r="M7" s="19" t="s">
         <v>42</v>
@@ -4521,490 +4650,881 @@
         <v>42</v>
       </c>
       <c r="P7" s="19" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Q7" s="20" t="s">
-        <v>103</v>
+        <v>171</v>
       </c>
       <c r="R7" s="46" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="S7" s="23" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="T7" s="24" t="s">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="U7" s="25" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="8" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" ht="40.5" x14ac:dyDescent="0.25">
       <c r="A8" s="18" t="s">
-        <v>78</v>
+        <v>168</v>
       </c>
       <c r="B8" s="19" t="s">
-        <v>78</v>
-      </c>
-      <c r="C8" s="19"/>
-      <c r="D8" s="19"/>
+        <v>8</v>
+      </c>
+      <c r="C8" s="19">
+        <v>1</v>
+      </c>
+      <c r="D8" s="19">
+        <v>50</v>
+      </c>
       <c r="E8" s="19"/>
       <c r="F8" s="19"/>
       <c r="G8" s="19"/>
       <c r="H8" s="19"/>
       <c r="I8" s="20"/>
       <c r="J8" s="19"/>
-      <c r="K8" s="21"/>
-      <c r="L8" s="22"/>
-      <c r="M8" s="19"/>
-      <c r="N8" s="19"/>
-      <c r="O8" s="19"/>
-      <c r="P8" s="19"/>
+      <c r="K8" s="21" t="s">
+        <v>163</v>
+      </c>
+      <c r="L8" s="22" t="s">
+        <v>42</v>
+      </c>
+      <c r="M8" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="N8" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="O8" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="P8" s="19" t="s">
+        <v>42</v>
+      </c>
       <c r="Q8" s="20" t="s">
-        <v>81</v>
+        <v>166</v>
       </c>
       <c r="R8" s="46" t="s">
-        <v>107</v>
-      </c>
-      <c r="S8" s="31" t="s">
-        <v>113</v>
+        <v>99</v>
+      </c>
+      <c r="S8" s="23" t="s">
+        <v>102</v>
       </c>
       <c r="T8" s="24" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="U8" s="25" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="9" spans="1:21" ht="23.45" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="10" spans="1:21" ht="51" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="127" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" ht="27" x14ac:dyDescent="0.25">
+      <c r="A9" s="18" t="s">
+        <v>169</v>
+      </c>
+      <c r="B9" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="19">
+        <v>32</v>
+      </c>
+      <c r="D9" s="19">
+        <v>32</v>
+      </c>
+      <c r="E9" s="19"/>
+      <c r="F9" s="19"/>
+      <c r="G9" s="19"/>
+      <c r="H9" s="19"/>
+      <c r="I9" s="20" t="s">
+        <v>40</v>
+      </c>
+      <c r="J9" s="19"/>
+      <c r="K9" s="21"/>
+      <c r="L9" s="22" t="s">
+        <v>41</v>
+      </c>
+      <c r="M9" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="N9" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="O9" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="P9" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q9" s="20" t="s">
+        <v>171</v>
+      </c>
+      <c r="R9" s="46" t="s">
+        <v>99</v>
+      </c>
+      <c r="S9" s="23" t="s">
+        <v>100</v>
+      </c>
+      <c r="T9" s="24" t="s">
+        <v>101</v>
+      </c>
+      <c r="U9" s="25" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" ht="40.5" x14ac:dyDescent="0.25">
+      <c r="A10" s="18" t="s">
+        <v>170</v>
+      </c>
+      <c r="B10" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="C10" s="19">
+        <v>1</v>
+      </c>
+      <c r="D10" s="19">
+        <v>20</v>
+      </c>
+      <c r="E10" s="19"/>
+      <c r="F10" s="19"/>
+      <c r="G10" s="19">
+        <v>1</v>
+      </c>
+      <c r="H10" s="19">
+        <v>200</v>
+      </c>
+      <c r="I10" s="20" t="s">
+        <v>172</v>
+      </c>
+      <c r="J10" s="19"/>
+      <c r="K10" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="L10" s="22" t="s">
+        <v>42</v>
+      </c>
+      <c r="M10" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="N10" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="O10" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="P10" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q10" s="20" t="s">
+        <v>174</v>
+      </c>
+      <c r="R10" s="46" t="s">
+        <v>99</v>
+      </c>
+      <c r="S10" s="23" t="s">
+        <v>102</v>
+      </c>
+      <c r="T10" s="24" t="s">
+        <v>103</v>
+      </c>
+      <c r="U10" s="25" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A11" s="18" t="s">
+        <v>156</v>
+      </c>
+      <c r="B11" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="19">
+        <v>32</v>
+      </c>
+      <c r="D11" s="19">
+        <v>32</v>
+      </c>
+      <c r="E11" s="19"/>
+      <c r="F11" s="19"/>
+      <c r="G11" s="19"/>
+      <c r="H11" s="19"/>
+      <c r="I11" s="19" t="s">
+        <v>40</v>
+      </c>
+      <c r="J11" s="19"/>
+      <c r="K11" s="21"/>
+      <c r="L11" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="M11" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="N11" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="O11" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="P11" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q11" s="20" t="s">
+        <v>165</v>
+      </c>
+      <c r="R11" s="46" t="s">
+        <v>99</v>
+      </c>
+      <c r="S11" s="23" t="s">
+        <v>100</v>
+      </c>
+      <c r="T11" s="24" t="s">
+        <v>101</v>
+      </c>
+      <c r="U11" s="25" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21" ht="40.5" x14ac:dyDescent="0.25">
+      <c r="A12" s="18" t="s">
+        <v>157</v>
+      </c>
+      <c r="B12" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" s="19">
+        <v>1</v>
+      </c>
+      <c r="D12" s="19">
+        <v>50</v>
+      </c>
+      <c r="E12" s="19"/>
+      <c r="F12" s="19"/>
+      <c r="G12" s="19"/>
+      <c r="H12" s="19"/>
+      <c r="I12" s="19"/>
+      <c r="J12" s="19"/>
+      <c r="K12" s="21" t="s">
+        <v>163</v>
+      </c>
+      <c r="L12" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="M12" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="N12" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="O12" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="P12" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q12" s="20" t="s">
+        <v>166</v>
+      </c>
+      <c r="R12" s="46" t="s">
+        <v>99</v>
+      </c>
+      <c r="S12" s="23" t="s">
+        <v>102</v>
+      </c>
+      <c r="T12" s="24" t="s">
+        <v>103</v>
+      </c>
+      <c r="U12" s="25" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A13" s="18" t="s">
+        <v>158</v>
+      </c>
+      <c r="B13" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="19">
+        <v>32</v>
+      </c>
+      <c r="D13" s="19">
+        <v>32</v>
+      </c>
+      <c r="E13" s="19"/>
+      <c r="F13" s="19"/>
+      <c r="G13" s="19"/>
+      <c r="H13" s="19"/>
+      <c r="I13" s="19" t="s">
+        <v>40</v>
+      </c>
+      <c r="J13" s="19"/>
+      <c r="K13" s="21"/>
+      <c r="L13" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="M13" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="N13" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="O13" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="P13" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q13" s="20" t="s">
+        <v>96</v>
+      </c>
+      <c r="R13" s="46" t="s">
+        <v>99</v>
+      </c>
+      <c r="S13" s="23" t="s">
+        <v>100</v>
+      </c>
+      <c r="T13" s="24" t="s">
+        <v>101</v>
+      </c>
+      <c r="U13" s="25" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A14" s="18" t="s">
+        <v>159</v>
+      </c>
+      <c r="B14" s="19" t="s">
+        <v>76</v>
+      </c>
+      <c r="C14" s="19">
+        <v>1</v>
+      </c>
+      <c r="D14" s="19">
+        <v>50</v>
+      </c>
+      <c r="E14" s="19"/>
+      <c r="F14" s="19"/>
+      <c r="G14" s="19"/>
+      <c r="H14" s="19"/>
+      <c r="I14" s="20"/>
+      <c r="J14" s="19"/>
+      <c r="K14" s="21"/>
+      <c r="L14" s="22" t="s">
+        <v>42</v>
+      </c>
+      <c r="M14" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="N14" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="O14" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="P14" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q14" s="20" t="s">
+        <v>97</v>
+      </c>
+      <c r="R14" s="46" t="s">
+        <v>99</v>
+      </c>
+      <c r="S14" s="31" t="s">
+        <v>102</v>
+      </c>
+      <c r="T14" s="24" t="s">
+        <v>103</v>
+      </c>
+      <c r="U14" s="25" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" ht="23.45" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16" spans="1:21" ht="51" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="63" t="s">
         <v>47</v>
       </c>
-      <c r="B10" s="127"/>
-      <c r="C10" s="127"/>
-    </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A11" s="26" t="s">
+      <c r="B16" s="63"/>
+      <c r="C16" s="63"/>
+    </row>
+    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A17" s="26" t="s">
         <v>48</v>
       </c>
-      <c r="B11" s="26" t="s">
+      <c r="B17" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="C11" s="26" t="s">
+      <c r="C17" s="26" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="12" spans="1:21" ht="31.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="139" t="s">
-        <v>104</v>
-      </c>
-      <c r="B12" s="139" t="s">
+    <row r="18" spans="1:19" ht="31.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="65" t="s">
+        <v>160</v>
+      </c>
+      <c r="B18" s="65" t="s">
+        <v>161</v>
+      </c>
+      <c r="C18" s="132" t="str">
+        <f>A5</f>
+        <v>identificadorConjuntoResidencial</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19" ht="31.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="65"/>
+      <c r="B19" s="65"/>
+      <c r="C19" s="132" t="str">
+        <f>A6</f>
+        <v>nombreConjuntoResidencial</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19" ht="31.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="65"/>
+      <c r="B20" s="65"/>
+      <c r="C20" s="132" t="str">
+        <f>A7</f>
+        <v>identificadorTipoZonaInmueble</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19" ht="31.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="65"/>
+      <c r="B21" s="65"/>
+      <c r="C21" s="132" t="str">
+        <f>A8</f>
+        <v>nombreTipoZonaInmueble</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19" ht="31.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="65"/>
+      <c r="B22" s="65"/>
+      <c r="C22" s="132" t="str">
+        <f>A9</f>
+        <v>identificadorZonaInmueble</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19" ht="31.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="65"/>
+      <c r="B23" s="65"/>
+      <c r="C23" s="132" t="str">
+        <f>A10</f>
+        <v>numeroZonaInmuebleZonaInmueble</v>
+      </c>
+    </row>
+    <row r="24" spans="1:19" ht="31.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="65"/>
+      <c r="B24" s="65"/>
+      <c r="C24" s="132" t="str">
+        <f>A11</f>
+        <v>identificadorTipoInmueble</v>
+      </c>
+    </row>
+    <row r="25" spans="1:19" ht="31.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="65"/>
+      <c r="B25" s="65"/>
+      <c r="C25" s="132" t="str">
+        <f>A12</f>
+        <v>nombreTipoInmueble</v>
+      </c>
+    </row>
+    <row r="26" spans="1:19" ht="31.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="65"/>
+      <c r="B26" s="65"/>
+      <c r="C26" s="38" t="str">
+        <f>A13</f>
+        <v>identificadorInmueble</v>
+      </c>
+    </row>
+    <row r="27" spans="1:19" ht="31.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="65"/>
+      <c r="B27" s="65"/>
+      <c r="C27" s="38" t="str">
+        <f>A14</f>
+        <v>numeroViviendaInmueble</v>
+      </c>
+    </row>
+    <row r="28" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="29" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A29" s="80" t="s">
+        <v>51</v>
+      </c>
+      <c r="B29" s="81"/>
+      <c r="C29" s="84" t="s">
+        <v>2</v>
+      </c>
+      <c r="D29" s="85"/>
+      <c r="E29" s="85"/>
+      <c r="F29" s="85"/>
+      <c r="G29" s="81"/>
+      <c r="H29" s="72" t="s">
+        <v>52</v>
+      </c>
+      <c r="I29" s="88"/>
+      <c r="J29" s="89"/>
+      <c r="K29" s="72" t="s">
+        <v>53</v>
+      </c>
+      <c r="L29" s="88"/>
+      <c r="M29" s="88"/>
+      <c r="N29" s="88"/>
+      <c r="O29" s="89"/>
+      <c r="P29" s="72" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q29" s="89"/>
+      <c r="R29" s="72" t="s">
+        <v>55</v>
+      </c>
+      <c r="S29" s="73"/>
+    </row>
+    <row r="30" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A30" s="82"/>
+      <c r="B30" s="83"/>
+      <c r="C30" s="86"/>
+      <c r="D30" s="87"/>
+      <c r="E30" s="87"/>
+      <c r="F30" s="87"/>
+      <c r="G30" s="83"/>
+      <c r="H30" s="47" t="s">
+        <v>56</v>
+      </c>
+      <c r="I30" s="27" t="s">
+        <v>57</v>
+      </c>
+      <c r="J30" s="27" t="s">
+        <v>2</v>
+      </c>
+      <c r="K30" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="L30" s="74" t="s">
+        <v>2</v>
+      </c>
+      <c r="M30" s="75"/>
+      <c r="N30" s="75"/>
+      <c r="O30" s="76"/>
+      <c r="P30" s="27" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q30" s="27" t="s">
+        <v>2</v>
+      </c>
+      <c r="R30" s="27" t="s">
+        <v>59</v>
+      </c>
+      <c r="S30" s="28" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="31" spans="1:19" ht="30" x14ac:dyDescent="0.25">
+      <c r="A31" s="90" t="s">
+        <v>98</v>
+      </c>
+      <c r="B31" s="91"/>
+      <c r="C31" s="94" t="s">
         <v>105</v>
       </c>
-      <c r="C12" s="140" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="13" spans="1:21" ht="31.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="139"/>
-      <c r="B13" s="139"/>
-      <c r="C13" s="140"/>
-    </row>
-    <row r="14" spans="1:21" ht="31.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="139"/>
-      <c r="B14" s="139"/>
-      <c r="C14" s="38" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="15" spans="1:21" ht="31.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="139"/>
-      <c r="B15" s="139"/>
-      <c r="C15" s="38" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="16" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A17" s="128" t="s">
-        <v>51</v>
-      </c>
-      <c r="B17" s="129"/>
-      <c r="C17" s="132" t="s">
-        <v>2</v>
-      </c>
-      <c r="D17" s="133"/>
-      <c r="E17" s="133"/>
-      <c r="F17" s="133"/>
-      <c r="G17" s="129"/>
-      <c r="H17" s="119" t="s">
-        <v>52</v>
-      </c>
-      <c r="I17" s="136"/>
-      <c r="J17" s="137"/>
-      <c r="K17" s="119" t="s">
-        <v>53</v>
-      </c>
-      <c r="L17" s="136"/>
-      <c r="M17" s="136"/>
-      <c r="N17" s="136"/>
-      <c r="O17" s="137"/>
-      <c r="P17" s="119" t="s">
-        <v>54</v>
-      </c>
-      <c r="Q17" s="137"/>
-      <c r="R17" s="119" t="s">
-        <v>55</v>
-      </c>
-      <c r="S17" s="120"/>
-    </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A18" s="130"/>
-      <c r="B18" s="131"/>
-      <c r="C18" s="134"/>
-      <c r="D18" s="135"/>
-      <c r="E18" s="135"/>
-      <c r="F18" s="135"/>
-      <c r="G18" s="131"/>
-      <c r="H18" s="47" t="s">
-        <v>56</v>
-      </c>
-      <c r="I18" s="27" t="s">
-        <v>57</v>
-      </c>
-      <c r="J18" s="27" t="s">
-        <v>2</v>
-      </c>
-      <c r="K18" s="27" t="s">
-        <v>24</v>
-      </c>
-      <c r="L18" s="121" t="s">
-        <v>2</v>
-      </c>
-      <c r="M18" s="122"/>
-      <c r="N18" s="122"/>
-      <c r="O18" s="123"/>
-      <c r="P18" s="27" t="s">
-        <v>58</v>
-      </c>
-      <c r="Q18" s="27" t="s">
-        <v>2</v>
-      </c>
-      <c r="R18" s="27" t="s">
-        <v>59</v>
-      </c>
-      <c r="S18" s="28" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="19" spans="1:19" ht="30" x14ac:dyDescent="0.25">
-      <c r="A19" s="97" t="s">
-        <v>106</v>
-      </c>
-      <c r="B19" s="98"/>
-      <c r="C19" s="101" t="s">
-        <v>114</v>
-      </c>
-      <c r="D19" s="102"/>
-      <c r="E19" s="102"/>
-      <c r="F19" s="102"/>
-      <c r="G19" s="103"/>
-      <c r="H19" s="107" t="str">
+      <c r="D31" s="95"/>
+      <c r="E31" s="95"/>
+      <c r="F31" s="95"/>
+      <c r="G31" s="96"/>
+      <c r="H31" s="100" t="str">
         <f>_xlfn.CONCAT("datos",B2)</f>
         <v>datosInmueble</v>
       </c>
-      <c r="I19" s="141" t="str">
+      <c r="I31" s="130" t="str">
         <f>B2</f>
         <v>Inmueble</v>
       </c>
-      <c r="J19" s="111" t="str">
+      <c r="J31" s="104" t="str">
         <f>_xlfn.CONCAT("Corresponde al objeto que internamente contiene los datos necesarios para crear una nueva ",B2,)</f>
         <v>Corresponde al objeto que internamente contiene los datos necesarios para crear una nueva Inmueble</v>
       </c>
-      <c r="K19" s="48"/>
-      <c r="L19" s="113"/>
-      <c r="M19" s="114"/>
-      <c r="N19" s="114"/>
-      <c r="O19" s="115"/>
-      <c r="P19" s="13" t="s">
+      <c r="K31" s="48"/>
+      <c r="L31" s="66"/>
+      <c r="M31" s="67"/>
+      <c r="N31" s="67"/>
+      <c r="O31" s="68"/>
+      <c r="P31" s="13" t="s">
+        <v>106</v>
+      </c>
+      <c r="Q31" s="12" t="s">
+        <v>107</v>
+      </c>
+      <c r="R31" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="S31" s="49" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="32" spans="1:19" ht="45" x14ac:dyDescent="0.25">
+      <c r="A32" s="92"/>
+      <c r="B32" s="93"/>
+      <c r="C32" s="97"/>
+      <c r="D32" s="98"/>
+      <c r="E32" s="98"/>
+      <c r="F32" s="98"/>
+      <c r="G32" s="99"/>
+      <c r="H32" s="101"/>
+      <c r="I32" s="131"/>
+      <c r="J32" s="105"/>
+      <c r="K32" s="50"/>
+      <c r="L32" s="69"/>
+      <c r="M32" s="70"/>
+      <c r="N32" s="70"/>
+      <c r="O32" s="71"/>
+      <c r="P32" s="13" t="s">
+        <v>110</v>
+      </c>
+      <c r="Q32" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="R32" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="S32" s="49" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="33" spans="1:19" ht="30" x14ac:dyDescent="0.25">
+      <c r="A33" s="92"/>
+      <c r="B33" s="93"/>
+      <c r="C33" s="97"/>
+      <c r="D33" s="98"/>
+      <c r="E33" s="98"/>
+      <c r="F33" s="98"/>
+      <c r="G33" s="99"/>
+      <c r="H33" s="101"/>
+      <c r="I33" s="131"/>
+      <c r="J33" s="105"/>
+      <c r="K33" s="50"/>
+      <c r="L33" s="69"/>
+      <c r="M33" s="70"/>
+      <c r="N33" s="70"/>
+      <c r="O33" s="71"/>
+      <c r="P33" s="13" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q33" s="12" t="s">
         <v>115</v>
       </c>
-      <c r="Q19" s="12" t="s">
+      <c r="R33" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="R19" s="12" t="s">
+      <c r="S33" s="49" t="s">
         <v>117</v>
       </c>
-      <c r="S19" s="49" t="s">
+    </row>
+    <row r="34" spans="1:19" ht="45" x14ac:dyDescent="0.25">
+      <c r="A34" s="92"/>
+      <c r="B34" s="93"/>
+      <c r="C34" s="97"/>
+      <c r="D34" s="98"/>
+      <c r="E34" s="98"/>
+      <c r="F34" s="98"/>
+      <c r="G34" s="99"/>
+      <c r="H34" s="101"/>
+      <c r="I34" s="131"/>
+      <c r="J34" s="105"/>
+      <c r="K34" s="50"/>
+      <c r="L34" s="69"/>
+      <c r="M34" s="70"/>
+      <c r="N34" s="70"/>
+      <c r="O34" s="71"/>
+      <c r="P34" s="13" t="s">
         <v>118</v>
       </c>
-    </row>
-    <row r="20" spans="1:19" ht="45" x14ac:dyDescent="0.25">
-      <c r="A20" s="99"/>
-      <c r="B20" s="100"/>
-      <c r="C20" s="104"/>
-      <c r="D20" s="105"/>
-      <c r="E20" s="105"/>
-      <c r="F20" s="105"/>
-      <c r="G20" s="106"/>
-      <c r="H20" s="108"/>
-      <c r="I20" s="142"/>
-      <c r="J20" s="112"/>
-      <c r="K20" s="57"/>
-      <c r="L20" s="116"/>
-      <c r="M20" s="117"/>
-      <c r="N20" s="117"/>
-      <c r="O20" s="118"/>
-      <c r="P20" s="13" t="s">
+      <c r="Q34" s="12" t="s">
         <v>119</v>
       </c>
-      <c r="Q20" s="12" t="s">
+      <c r="R34" s="12" t="s">
         <v>120</v>
       </c>
-      <c r="R20" s="12" t="s">
+      <c r="S34" s="49" t="s">
         <v>121</v>
       </c>
-      <c r="S20" s="49" t="s">
+    </row>
+    <row r="35" spans="1:19" ht="71.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="114" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="21" spans="1:19" ht="30" x14ac:dyDescent="0.25">
-      <c r="A21" s="99"/>
-      <c r="B21" s="100"/>
-      <c r="C21" s="104"/>
-      <c r="D21" s="105"/>
-      <c r="E21" s="105"/>
-      <c r="F21" s="105"/>
-      <c r="G21" s="106"/>
-      <c r="H21" s="108"/>
-      <c r="I21" s="142"/>
-      <c r="J21" s="112"/>
-      <c r="K21" s="57"/>
-      <c r="L21" s="116"/>
-      <c r="M21" s="117"/>
-      <c r="N21" s="117"/>
-      <c r="O21" s="118"/>
-      <c r="P21" s="13" t="s">
+      <c r="B35" s="115"/>
+      <c r="C35" s="116" t="s">
         <v>123</v>
       </c>
-      <c r="Q21" s="12" t="s">
-        <v>124</v>
-      </c>
-      <c r="R21" s="12" t="s">
-        <v>125</v>
-      </c>
-      <c r="S21" s="49" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="22" spans="1:19" ht="45" x14ac:dyDescent="0.25">
-      <c r="A22" s="99"/>
-      <c r="B22" s="100"/>
-      <c r="C22" s="104"/>
-      <c r="D22" s="105"/>
-      <c r="E22" s="105"/>
-      <c r="F22" s="105"/>
-      <c r="G22" s="106"/>
-      <c r="H22" s="108"/>
-      <c r="I22" s="142"/>
-      <c r="J22" s="112"/>
-      <c r="K22" s="57"/>
-      <c r="L22" s="116"/>
-      <c r="M22" s="117"/>
-      <c r="N22" s="117"/>
-      <c r="O22" s="118"/>
-      <c r="P22" s="13" t="s">
-        <v>127</v>
-      </c>
-      <c r="Q22" s="12" t="s">
-        <v>128</v>
-      </c>
-      <c r="R22" s="12" t="s">
-        <v>129</v>
-      </c>
-      <c r="S22" s="49" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="23" spans="1:19" ht="71.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="81" t="s">
-        <v>131</v>
-      </c>
-      <c r="B23" s="82"/>
-      <c r="C23" s="83" t="s">
-        <v>132</v>
-      </c>
-      <c r="D23" s="84"/>
-      <c r="E23" s="84"/>
-      <c r="F23" s="84"/>
-      <c r="G23" s="85"/>
-      <c r="H23" s="30" t="str">
+      <c r="D35" s="117"/>
+      <c r="E35" s="117"/>
+      <c r="F35" s="117"/>
+      <c r="G35" s="118"/>
+      <c r="H35" s="30" t="str">
         <f>_xlfn.CONCAT("datos",B2)</f>
         <v>datosInmueble</v>
       </c>
-      <c r="I23" s="29" t="str">
+      <c r="I35" s="29" t="str">
         <f>B2</f>
         <v>Inmueble</v>
       </c>
-      <c r="J23" s="30" t="str">
+      <c r="J35" s="30" t="str">
         <f>_xlfn.CONCAT("Corresponde a un objeto que contiene los filtros de consulta de ",B2," de un conjunto residencial.")</f>
         <v>Corresponde a un objeto que contiene los filtros de consulta de Inmueble de un conjunto residencial.</v>
       </c>
-      <c r="K23" s="41" t="s">
-        <v>148</v>
-      </c>
-      <c r="L23" s="86" t="s">
-        <v>133</v>
-      </c>
-      <c r="M23" s="87"/>
-      <c r="N23" s="87"/>
-      <c r="O23" s="88"/>
-      <c r="P23" s="23" t="s">
-        <v>134</v>
-      </c>
-      <c r="Q23" s="31" t="s">
-        <v>135</v>
-      </c>
-      <c r="R23" s="31" t="s">
-        <v>117</v>
-      </c>
-      <c r="S23" s="61" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="24" spans="1:19" ht="30" x14ac:dyDescent="0.25">
-      <c r="A24" s="89" t="s">
-        <v>136</v>
-      </c>
-      <c r="B24" s="90"/>
-      <c r="C24" s="91" t="s">
-        <v>137</v>
-      </c>
-      <c r="D24" s="92"/>
-      <c r="E24" s="92"/>
-      <c r="F24" s="92"/>
-      <c r="G24" s="93"/>
-      <c r="H24" s="32" t="str">
+      <c r="K35" s="41" t="s">
+        <v>139</v>
+      </c>
+      <c r="L35" s="119" t="s">
+        <v>124</v>
+      </c>
+      <c r="M35" s="120"/>
+      <c r="N35" s="120"/>
+      <c r="O35" s="121"/>
+      <c r="P35" s="23" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q35" s="31" t="s">
+        <v>126</v>
+      </c>
+      <c r="R35" s="31" t="s">
+        <v>108</v>
+      </c>
+      <c r="S35" s="51" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="36" spans="1:19" ht="30" x14ac:dyDescent="0.25">
+      <c r="A36" s="122" t="s">
+        <v>127</v>
+      </c>
+      <c r="B36" s="123"/>
+      <c r="C36" s="124" t="s">
+        <v>128</v>
+      </c>
+      <c r="D36" s="125"/>
+      <c r="E36" s="125"/>
+      <c r="F36" s="125"/>
+      <c r="G36" s="126"/>
+      <c r="H36" s="32" t="str">
         <f>_xlfn.CONCAT("datos",B2)</f>
         <v>datosInmueble</v>
       </c>
-      <c r="I24" s="33" t="str">
+      <c r="I36" s="33" t="str">
         <f>B2</f>
         <v>Inmueble</v>
       </c>
-      <c r="J24" s="32" t="str">
+      <c r="J36" s="32" t="str">
         <f>_xlfn.CONCAT("Corresponde a los datos que se van a modificar de la ",B2)</f>
         <v>Corresponde a los datos que se van a modificar de la Inmueble</v>
       </c>
-      <c r="K24" s="34"/>
-      <c r="L24" s="94"/>
-      <c r="M24" s="95"/>
-      <c r="N24" s="95"/>
-      <c r="O24" s="96"/>
-      <c r="P24" s="62" t="s">
-        <v>138</v>
-      </c>
-      <c r="Q24" s="63" t="s">
-        <v>139</v>
-      </c>
-      <c r="R24" s="63" t="s">
-        <v>140</v>
-      </c>
-      <c r="S24" s="64" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="25" spans="1:19" ht="30" x14ac:dyDescent="0.25">
-      <c r="A25" s="73" t="s">
-        <v>142</v>
-      </c>
-      <c r="B25" s="74"/>
-      <c r="C25" s="75" t="s">
-        <v>143</v>
-      </c>
-      <c r="D25" s="76"/>
-      <c r="E25" s="76"/>
-      <c r="F25" s="76"/>
-      <c r="G25" s="77"/>
-      <c r="H25" s="35" t="s">
+      <c r="K36" s="34"/>
+      <c r="L36" s="127"/>
+      <c r="M36" s="128"/>
+      <c r="N36" s="128"/>
+      <c r="O36" s="129"/>
+      <c r="P36" s="52" t="s">
+        <v>129</v>
+      </c>
+      <c r="Q36" s="53" t="s">
+        <v>130</v>
+      </c>
+      <c r="R36" s="53" t="s">
+        <v>131</v>
+      </c>
+      <c r="S36" s="54" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="37" spans="1:19" ht="30" x14ac:dyDescent="0.25">
+      <c r="A37" s="106" t="s">
+        <v>133</v>
+      </c>
+      <c r="B37" s="107"/>
+      <c r="C37" s="108" t="s">
+        <v>134</v>
+      </c>
+      <c r="D37" s="109"/>
+      <c r="E37" s="109"/>
+      <c r="F37" s="109"/>
+      <c r="G37" s="110"/>
+      <c r="H37" s="35" t="s">
         <v>39</v>
       </c>
-      <c r="I25" s="25" t="s">
+      <c r="I37" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="J25" s="35" t="str">
+      <c r="J37" s="35" t="str">
         <f>_xlfn.CONCAT("Corresponde al identificador de la ",$B$2,"  que se quiere dar de baja.")</f>
         <v>Corresponde al identificador de la Inmueble  que se quiere dar de baja.</v>
       </c>
-      <c r="K25" s="36"/>
-      <c r="L25" s="78"/>
-      <c r="M25" s="79"/>
-      <c r="N25" s="79"/>
-      <c r="O25" s="80"/>
-      <c r="P25" s="25" t="s">
-        <v>138</v>
-      </c>
-      <c r="Q25" s="37" t="s">
-        <v>139</v>
-      </c>
-      <c r="R25" s="37" t="s">
-        <v>140</v>
-      </c>
-      <c r="S25" s="37" t="s">
-        <v>141</v>
+      <c r="K37" s="36"/>
+      <c r="L37" s="111"/>
+      <c r="M37" s="112"/>
+      <c r="N37" s="112"/>
+      <c r="O37" s="113"/>
+      <c r="P37" s="25" t="s">
+        <v>129</v>
+      </c>
+      <c r="Q37" s="37" t="s">
+        <v>130</v>
+      </c>
+      <c r="R37" s="37" t="s">
+        <v>131</v>
+      </c>
+      <c r="S37" s="37" t="s">
+        <v>132</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="29">
-    <mergeCell ref="L19:O22"/>
-    <mergeCell ref="A19:B22"/>
-    <mergeCell ref="C19:G22"/>
-    <mergeCell ref="H19:H22"/>
-    <mergeCell ref="I19:I22"/>
-    <mergeCell ref="J19:J22"/>
-    <mergeCell ref="P17:Q17"/>
-    <mergeCell ref="R17:S17"/>
-    <mergeCell ref="L18:O18"/>
-    <mergeCell ref="A17:B18"/>
-    <mergeCell ref="C17:G18"/>
-    <mergeCell ref="H17:J17"/>
-    <mergeCell ref="K17:O17"/>
+  <mergeCells count="28">
+    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="C37:G37"/>
+    <mergeCell ref="L37:O37"/>
+    <mergeCell ref="A35:B35"/>
+    <mergeCell ref="C35:G35"/>
+    <mergeCell ref="L35:O35"/>
+    <mergeCell ref="A36:B36"/>
+    <mergeCell ref="C36:G36"/>
+    <mergeCell ref="L36:O36"/>
     <mergeCell ref="A1:Q1"/>
     <mergeCell ref="B2:Q2"/>
     <mergeCell ref="B3:Q3"/>
-    <mergeCell ref="A10:C10"/>
-    <mergeCell ref="A12:A15"/>
-    <mergeCell ref="B12:B15"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="C25:G25"/>
-    <mergeCell ref="L25:O25"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="C23:G23"/>
-    <mergeCell ref="L23:O23"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="C24:G24"/>
-    <mergeCell ref="L24:O24"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="A18:A27"/>
+    <mergeCell ref="B18:B27"/>
+    <mergeCell ref="P29:Q29"/>
+    <mergeCell ref="R29:S29"/>
+    <mergeCell ref="L30:O30"/>
+    <mergeCell ref="A29:B30"/>
+    <mergeCell ref="C29:G30"/>
+    <mergeCell ref="H29:J29"/>
+    <mergeCell ref="K29:O29"/>
+    <mergeCell ref="L31:O34"/>
+    <mergeCell ref="A31:B34"/>
+    <mergeCell ref="C31:G34"/>
+    <mergeCell ref="H31:H34"/>
+    <mergeCell ref="I31:I34"/>
+    <mergeCell ref="J31:J34"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A1" location="'Objetos de Dominio'!A1" display="Volver al inicio" xr:uid="{4C6EA31D-5DD1-42F9-A469-ED5E8CAE0643}"/>
     <hyperlink ref="A1:Q1" location="'Listado Objetos de Dominio'!A1" display="&lt;-Volver al inicio" xr:uid="{68117D6F-3D68-4E53-BDF0-9E2FE69EC82B}"/>
-    <hyperlink ref="C15" location="Inmueble!A8" display="ZonaInmueble" xr:uid="{DB88250A-52A4-46B9-B641-D80D50936AFD}"/>
-    <hyperlink ref="C14" location="Inmueble!A7" display="numeroVivienda" xr:uid="{7C3EDB2F-89BF-494E-90D1-85A6C4411548}"/>
-    <hyperlink ref="C12" location="Inmueble!A6" display="tipoInmueble" xr:uid="{67F5311F-E219-4D10-B08A-00D1F447C35E}"/>
+    <hyperlink ref="C27" location="Inmueble!A8" display="ZonaInmueble" xr:uid="{DB88250A-52A4-46B9-B641-D80D50936AFD}"/>
+    <hyperlink ref="C26" location="Inmueble!A7" display="numeroVivienda" xr:uid="{7C3EDB2F-89BF-494E-90D1-85A6C4411548}"/>
+    <hyperlink ref="C18" location="Inmueble!A6" display="tipoInmueble" xr:uid="{67F5311F-E219-4D10-B08A-00D1F447C35E}"/>
     <hyperlink ref="T4" location="Inmueble!A24" display="Inmueble!A24" xr:uid="{6B85A766-FE98-4E0D-BA4E-307AEF32087B}"/>
     <hyperlink ref="U4" location="Inmueble!A25" display="Inmueble!A25" xr:uid="{0B31C64C-F40D-42E8-B7BB-6F3B28DBA4A9}"/>
     <hyperlink ref="R4" location="Inmueble!A19" display="Registrar" xr:uid="{9CF36FA9-4736-4461-8BC4-6D63275BBB43}"/>
     <hyperlink ref="S4" location="Inmueble!A23" display="Inmueble!A23" xr:uid="{94FC0D47-78FA-4F07-B047-30A115B0B09E}"/>
-    <hyperlink ref="I25" location="'Tipo Relación Institución'!A6" display="'Tipo Relación Institución'!A6" xr:uid="{925BA423-E6A3-4809-A55F-9065ACAC2FA4}"/>
-    <hyperlink ref="A23:B23" location="Residente!S4" display="Buscar" xr:uid="{72BC4EC8-4009-4DCA-90CA-DEE2898E8D75}"/>
-    <hyperlink ref="A25:B25" location="Inmueble!U4" display="Eliminar" xr:uid="{4A22F145-C969-4341-A06C-4D62FAFE1576}"/>
-    <hyperlink ref="A24:B24" location="Inmueble!T4" display="Modificar" xr:uid="{F4439766-D1F3-420B-880B-FDCC00EC4131}"/>
-    <hyperlink ref="I19:I22" location="Inmueble!B2" display="Inmueble!B2" xr:uid="{1A8EFC3A-7FF4-4C4F-AA40-7EC617613E26}"/>
-    <hyperlink ref="I23" location="Inmueble!B2" display="Inmueble!B2" xr:uid="{9D627493-51C8-4318-9769-3833CF76727A}"/>
-    <hyperlink ref="I24" location="Inmueble!B2" display="Inmueble!B2" xr:uid="{FF551B30-67B6-4F91-BA1F-55BDE6DB061F}"/>
-    <hyperlink ref="A19:B22" location="Inmueble!R4" display="Registrar" xr:uid="{9E1F0932-C85E-43D7-9C30-7B740107C30B}"/>
+    <hyperlink ref="I37" location="'Tipo Relación Institución'!A6" display="'Tipo Relación Institución'!A6" xr:uid="{925BA423-E6A3-4809-A55F-9065ACAC2FA4}"/>
+    <hyperlink ref="A35:B35" location="Residente!S4" display="Buscar" xr:uid="{72BC4EC8-4009-4DCA-90CA-DEE2898E8D75}"/>
+    <hyperlink ref="A37:B37" location="Inmueble!U4" display="Eliminar" xr:uid="{4A22F145-C969-4341-A06C-4D62FAFE1576}"/>
+    <hyperlink ref="A36:B36" location="Inmueble!T4" display="Modificar" xr:uid="{F4439766-D1F3-420B-880B-FDCC00EC4131}"/>
+    <hyperlink ref="I31:I34" location="Inmueble!B2" display="Inmueble!B2" xr:uid="{1A8EFC3A-7FF4-4C4F-AA40-7EC617613E26}"/>
+    <hyperlink ref="I35" location="Inmueble!B2" display="Inmueble!B2" xr:uid="{9D627493-51C8-4318-9769-3833CF76727A}"/>
+    <hyperlink ref="I36" location="Inmueble!B2" display="Inmueble!B2" xr:uid="{FF551B30-67B6-4F91-BA1F-55BDE6DB061F}"/>
+    <hyperlink ref="A31:B34" location="Inmueble!R4" display="Registrar" xr:uid="{9E1F0932-C85E-43D7-9C30-7B740107C30B}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>

--- a/Doo-Doc/Nueva Version Victus/Modelos de Dominio Enriquecidos/Modelo De Dominio Enriquecido Residentes.xlsx
+++ b/Doo-Doc/Nueva Version Victus/Modelos de Dominio Enriquecidos/Modelo De Dominio Enriquecido Residentes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andre\Documents\DOO 2024 BD\DOO\victus-doc\Doo-Doc\Nueva Version Victus\Modelos de Dominio Enriquecidos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31D795FA-9C46-48AA-A019-6F77E3828310}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6A621C3-C156-418F-A7A6-E11ABA950670}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="20985" firstSheet="2" activeTab="3" xr2:uid="{007C2ECE-7E90-4717-B1E7-3A143C146FF0}"/>
+    <workbookView minimized="1" xWindow="1050" yWindow="2790" windowWidth="18195" windowHeight="15345" firstSheet="2" activeTab="4" xr2:uid="{007C2ECE-7E90-4717-B1E7-3A143C146FF0}"/>
   </bookViews>
   <sheets>
     <sheet name="Valores" sheetId="1" r:id="rId1"/>
@@ -1591,7 +1591,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="36">
+  <borders count="37">
     <border>
       <left/>
       <right/>
@@ -2022,12 +2022,27 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thick">
+        <color indexed="64"/>
+      </left>
+      <right style="thick">
+        <color indexed="64"/>
+      </right>
+      <top style="thick">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thick">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="147">
+  <cellXfs count="159">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2183,8 +2198,8 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="8" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2204,186 +2219,189 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="34" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="25" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="34" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="25" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="26" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="27" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="30" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="31" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="8" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="26" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="27" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="30" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="31" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="33" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="34" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="25" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="34" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="25" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="34" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2399,65 +2417,98 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="33" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="8" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="36" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="36" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="36" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="30" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="36" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="31" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="9" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="36" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="36" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="36" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="10" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="33" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="12" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3026,7 +3077,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3CD2E3E-2179-4007-8743-BED3F3BF1317}">
-  <dimension ref="A1:U33"/>
+  <dimension ref="A1:U34"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="23.85546875" style="7" bestFit="1" customWidth="1"/>
@@ -3055,73 +3106,73 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A1" s="77" t="s">
+      <c r="A1" s="106" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="77"/>
-      <c r="C1" s="77"/>
-      <c r="D1" s="77"/>
-      <c r="E1" s="77"/>
-      <c r="F1" s="77"/>
-      <c r="G1" s="77"/>
-      <c r="H1" s="77"/>
-      <c r="I1" s="77"/>
-      <c r="J1" s="77"/>
-      <c r="K1" s="77"/>
-      <c r="L1" s="77"/>
-      <c r="M1" s="77"/>
-      <c r="N1" s="77"/>
-      <c r="O1" s="77"/>
-      <c r="P1" s="77"/>
-      <c r="Q1" s="77"/>
+      <c r="B1" s="106"/>
+      <c r="C1" s="106"/>
+      <c r="D1" s="106"/>
+      <c r="E1" s="106"/>
+      <c r="F1" s="106"/>
+      <c r="G1" s="106"/>
+      <c r="H1" s="106"/>
+      <c r="I1" s="106"/>
+      <c r="J1" s="106"/>
+      <c r="K1" s="106"/>
+      <c r="L1" s="106"/>
+      <c r="M1" s="106"/>
+      <c r="N1" s="106"/>
+      <c r="O1" s="106"/>
+      <c r="P1" s="106"/>
+      <c r="Q1" s="106"/>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A2" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="B2" s="78" t="str">
+      <c r="B2" s="107" t="str">
         <f>'Listado Objetos de Dominio'!A3</f>
         <v>Residente</v>
       </c>
-      <c r="C2" s="78"/>
-      <c r="D2" s="78"/>
-      <c r="E2" s="78"/>
-      <c r="F2" s="78"/>
-      <c r="G2" s="78"/>
-      <c r="H2" s="78"/>
-      <c r="I2" s="78"/>
-      <c r="J2" s="78"/>
-      <c r="K2" s="78"/>
-      <c r="L2" s="78"/>
-      <c r="M2" s="78"/>
-      <c r="N2" s="78"/>
-      <c r="O2" s="78"/>
-      <c r="P2" s="78"/>
-      <c r="Q2" s="78"/>
+      <c r="C2" s="107"/>
+      <c r="D2" s="107"/>
+      <c r="E2" s="107"/>
+      <c r="F2" s="107"/>
+      <c r="G2" s="107"/>
+      <c r="H2" s="107"/>
+      <c r="I2" s="107"/>
+      <c r="J2" s="107"/>
+      <c r="K2" s="107"/>
+      <c r="L2" s="107"/>
+      <c r="M2" s="107"/>
+      <c r="N2" s="107"/>
+      <c r="O2" s="107"/>
+      <c r="P2" s="107"/>
+      <c r="Q2" s="107"/>
     </row>
     <row r="3" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="B3" s="79" t="str">
+      <c r="B3" s="108" t="str">
         <f>'Listado Objetos de Dominio'!B3</f>
         <v>Objeto de dominio que representa a un residente que vive dentro de un inmueble en un conjunto residencial</v>
       </c>
-      <c r="C3" s="79"/>
-      <c r="D3" s="79"/>
-      <c r="E3" s="79"/>
-      <c r="F3" s="79"/>
-      <c r="G3" s="79"/>
-      <c r="H3" s="79"/>
-      <c r="I3" s="79"/>
-      <c r="J3" s="79"/>
-      <c r="K3" s="79"/>
-      <c r="L3" s="79"/>
-      <c r="M3" s="79"/>
-      <c r="N3" s="79"/>
-      <c r="O3" s="79"/>
-      <c r="P3" s="79"/>
-      <c r="Q3" s="79"/>
+      <c r="C3" s="108"/>
+      <c r="D3" s="108"/>
+      <c r="E3" s="108"/>
+      <c r="F3" s="108"/>
+      <c r="G3" s="108"/>
+      <c r="H3" s="108"/>
+      <c r="I3" s="108"/>
+      <c r="J3" s="108"/>
+      <c r="K3" s="108"/>
+      <c r="L3" s="108"/>
+      <c r="M3" s="108"/>
+      <c r="N3" s="108"/>
+      <c r="O3" s="108"/>
+      <c r="P3" s="108"/>
+      <c r="Q3" s="108"/>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A4" s="15" t="s">
@@ -3726,21 +3777,21 @@
       </c>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A16" s="63" t="s">
+      <c r="A16" s="109" t="s">
         <v>88</v>
       </c>
-      <c r="B16" s="63"/>
-      <c r="C16" s="63"/>
-      <c r="E16" s="63" t="s">
+      <c r="B16" s="109"/>
+      <c r="C16" s="109"/>
+      <c r="E16" s="109" t="s">
         <v>90</v>
       </c>
-      <c r="F16" s="63"/>
-      <c r="G16" s="63"/>
-      <c r="I16" s="63" t="s">
+      <c r="F16" s="109"/>
+      <c r="G16" s="109"/>
+      <c r="I16" s="109" t="s">
         <v>47</v>
       </c>
-      <c r="J16" s="63"/>
-      <c r="K16" s="63"/>
+      <c r="J16" s="109"/>
+      <c r="K16" s="109"/>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A17" s="26" t="s">
@@ -3772,507 +3823,492 @@
       </c>
     </row>
     <row r="18" spans="1:19" ht="25.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="64" t="s">
+      <c r="A18" s="120" t="s">
         <v>50</v>
       </c>
-      <c r="B18" s="65" t="s">
+      <c r="B18" s="121" t="s">
         <v>89</v>
       </c>
-      <c r="C18" s="62" t="s">
+      <c r="C18" s="122" t="s">
         <v>71</v>
       </c>
-      <c r="E18" s="65" t="s">
+      <c r="E18" s="121" t="s">
         <v>94</v>
       </c>
-      <c r="F18" s="65" t="s">
+      <c r="F18" s="121" t="s">
         <v>91</v>
       </c>
-      <c r="G18" s="62" t="s">
+      <c r="G18" s="122" t="s">
         <v>78</v>
       </c>
       <c r="H18" s="39"/>
-      <c r="I18" s="64" t="s">
+      <c r="I18" s="120" t="s">
         <v>95</v>
       </c>
-      <c r="J18" s="65" t="s">
+      <c r="J18" s="121" t="s">
         <v>92</v>
       </c>
-      <c r="K18" s="62" t="s">
+      <c r="K18" s="122" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="19" spans="1:19" ht="25.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="64"/>
-      <c r="B19" s="65"/>
-      <c r="C19" s="62"/>
-      <c r="E19" s="65"/>
-      <c r="F19" s="65"/>
-      <c r="G19" s="62"/>
+      <c r="A19" s="120"/>
+      <c r="B19" s="121"/>
+      <c r="C19" s="122"/>
+      <c r="E19" s="121"/>
+      <c r="F19" s="121"/>
+      <c r="G19" s="122"/>
       <c r="H19" s="39"/>
-      <c r="I19" s="64"/>
-      <c r="J19" s="65"/>
-      <c r="K19" s="62"/>
+      <c r="I19" s="120"/>
+      <c r="J19" s="121"/>
+      <c r="K19" s="122"/>
     </row>
     <row r="20" spans="1:19" ht="25.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="64"/>
-      <c r="B20" s="65"/>
-      <c r="C20" s="62" t="s">
+      <c r="A20" s="120"/>
+      <c r="B20" s="121"/>
+      <c r="C20" s="122" t="s">
         <v>77</v>
       </c>
-      <c r="E20" s="65"/>
-      <c r="F20" s="65"/>
-      <c r="G20" s="62"/>
-      <c r="I20" s="64"/>
-      <c r="J20" s="65"/>
-      <c r="K20" s="62"/>
+      <c r="E20" s="121"/>
+      <c r="F20" s="121"/>
+      <c r="G20" s="122"/>
+      <c r="I20" s="120"/>
+      <c r="J20" s="121"/>
+      <c r="K20" s="122"/>
     </row>
     <row r="21" spans="1:19" ht="25.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="64"/>
-      <c r="B21" s="65"/>
-      <c r="C21" s="62"/>
-      <c r="E21" s="65"/>
-      <c r="F21" s="65"/>
-      <c r="G21" s="62"/>
-      <c r="I21" s="64"/>
-      <c r="J21" s="65"/>
-      <c r="K21" s="62"/>
+      <c r="A21" s="120"/>
+      <c r="B21" s="121"/>
+      <c r="C21" s="122"/>
+      <c r="E21" s="121"/>
+      <c r="F21" s="121"/>
+      <c r="G21" s="122"/>
+      <c r="I21" s="120"/>
+      <c r="J21" s="121"/>
+      <c r="K21" s="122"/>
     </row>
     <row r="22" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A23" s="80" t="s">
+    <row r="23" spans="1:19" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="130" t="s">
         <v>51</v>
       </c>
-      <c r="B23" s="81"/>
-      <c r="C23" s="84" t="s">
+      <c r="B23" s="130"/>
+      <c r="C23" s="130" t="s">
         <v>2</v>
       </c>
-      <c r="D23" s="85"/>
-      <c r="E23" s="85"/>
-      <c r="F23" s="85"/>
-      <c r="G23" s="81"/>
-      <c r="H23" s="72" t="s">
+      <c r="D23" s="130"/>
+      <c r="E23" s="130"/>
+      <c r="F23" s="130"/>
+      <c r="G23" s="130"/>
+      <c r="H23" s="130" t="s">
         <v>52</v>
       </c>
-      <c r="I23" s="88"/>
-      <c r="J23" s="89"/>
-      <c r="K23" s="72" t="s">
+      <c r="I23" s="130"/>
+      <c r="J23" s="130"/>
+      <c r="K23" s="130" t="s">
         <v>53</v>
       </c>
-      <c r="L23" s="88"/>
-      <c r="M23" s="88"/>
-      <c r="N23" s="88"/>
-      <c r="O23" s="89"/>
-      <c r="P23" s="72" t="s">
+      <c r="L23" s="130"/>
+      <c r="M23" s="130"/>
+      <c r="N23" s="130"/>
+      <c r="O23" s="130"/>
+      <c r="P23" s="130" t="s">
         <v>54</v>
       </c>
-      <c r="Q23" s="89"/>
-      <c r="R23" s="72" t="s">
+      <c r="Q23" s="130"/>
+      <c r="R23" s="130" t="s">
         <v>55</v>
       </c>
-      <c r="S23" s="73"/>
-    </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A24" s="82"/>
-      <c r="B24" s="83"/>
-      <c r="C24" s="86"/>
-      <c r="D24" s="87"/>
-      <c r="E24" s="87"/>
-      <c r="F24" s="87"/>
-      <c r="G24" s="83"/>
-      <c r="H24" s="47" t="s">
+      <c r="S23" s="130"/>
+    </row>
+    <row r="24" spans="1:19" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="130"/>
+      <c r="B24" s="130"/>
+      <c r="C24" s="130"/>
+      <c r="D24" s="130"/>
+      <c r="E24" s="130"/>
+      <c r="F24" s="130"/>
+      <c r="G24" s="130"/>
+      <c r="H24" s="131" t="s">
         <v>56</v>
       </c>
-      <c r="I24" s="27" t="s">
+      <c r="I24" s="132" t="s">
         <v>57</v>
       </c>
-      <c r="J24" s="27" t="s">
+      <c r="J24" s="132" t="s">
         <v>2</v>
       </c>
-      <c r="K24" s="27" t="s">
+      <c r="K24" s="132" t="s">
         <v>24</v>
       </c>
-      <c r="L24" s="74" t="s">
+      <c r="L24" s="130" t="s">
         <v>2</v>
       </c>
-      <c r="M24" s="75"/>
-      <c r="N24" s="75"/>
-      <c r="O24" s="76"/>
-      <c r="P24" s="27" t="s">
+      <c r="M24" s="130"/>
+      <c r="N24" s="130"/>
+      <c r="O24" s="130"/>
+      <c r="P24" s="132" t="s">
         <v>58</v>
       </c>
-      <c r="Q24" s="27" t="s">
+      <c r="Q24" s="132" t="s">
         <v>2</v>
       </c>
-      <c r="R24" s="27" t="s">
+      <c r="R24" s="132" t="s">
         <v>59</v>
       </c>
-      <c r="S24" s="28" t="s">
+      <c r="S24" s="132" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="25" spans="1:19" ht="45" x14ac:dyDescent="0.25">
-      <c r="A25" s="90" t="s">
+    <row r="25" spans="1:19" ht="46.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="133" t="s">
         <v>98</v>
       </c>
-      <c r="B25" s="91"/>
-      <c r="C25" s="94" t="s">
+      <c r="B25" s="133"/>
+      <c r="C25" s="134" t="s">
         <v>135</v>
       </c>
-      <c r="D25" s="95"/>
-      <c r="E25" s="95"/>
-      <c r="F25" s="95"/>
-      <c r="G25" s="96"/>
-      <c r="H25" s="100" t="str">
+      <c r="D25" s="134"/>
+      <c r="E25" s="134"/>
+      <c r="F25" s="134"/>
+      <c r="G25" s="134"/>
+      <c r="H25" s="134" t="str">
         <f>_xlfn.CONCAT("datos",B2)</f>
         <v>datosResidente</v>
       </c>
-      <c r="I25" s="102" t="str">
+      <c r="I25" s="135" t="str">
         <f>B2</f>
         <v>Residente</v>
       </c>
-      <c r="J25" s="104" t="str">
+      <c r="J25" s="136" t="str">
         <f>_xlfn.CONCAT("Corresponde al objeto que internamente contiene los datos necesarios para crear un nuevo ",B2,)</f>
         <v>Corresponde al objeto que internamente contiene los datos necesarios para crear un nuevo Residente</v>
       </c>
-      <c r="K25" s="48"/>
-      <c r="L25" s="66"/>
-      <c r="M25" s="67"/>
-      <c r="N25" s="67"/>
-      <c r="O25" s="68"/>
-      <c r="P25" s="13" t="s">
+      <c r="K25" s="137"/>
+      <c r="L25" s="136"/>
+      <c r="M25" s="136"/>
+      <c r="N25" s="136"/>
+      <c r="O25" s="136"/>
+      <c r="P25" s="138" t="s">
         <v>141</v>
       </c>
-      <c r="Q25" s="12" t="s">
+      <c r="Q25" s="139" t="s">
         <v>146</v>
       </c>
-      <c r="R25" s="12" t="s">
+      <c r="R25" s="139" t="s">
         <v>108</v>
       </c>
-      <c r="S25" s="49" t="s">
+      <c r="S25" s="139" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="26" spans="1:19" ht="30" x14ac:dyDescent="0.25">
-      <c r="A26" s="92"/>
-      <c r="B26" s="93"/>
-      <c r="C26" s="97"/>
-      <c r="D26" s="98"/>
-      <c r="E26" s="98"/>
-      <c r="F26" s="98"/>
-      <c r="G26" s="99"/>
-      <c r="H26" s="101"/>
-      <c r="I26" s="103"/>
-      <c r="J26" s="105"/>
-      <c r="K26" s="50"/>
-      <c r="L26" s="69"/>
-      <c r="M26" s="70"/>
-      <c r="N26" s="70"/>
-      <c r="O26" s="71"/>
-      <c r="P26" s="13" t="s">
+    <row r="26" spans="1:19" ht="31.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="133"/>
+      <c r="B26" s="133"/>
+      <c r="C26" s="134"/>
+      <c r="D26" s="134"/>
+      <c r="E26" s="134"/>
+      <c r="F26" s="134"/>
+      <c r="G26" s="134"/>
+      <c r="H26" s="134"/>
+      <c r="I26" s="135"/>
+      <c r="J26" s="136"/>
+      <c r="K26" s="137"/>
+      <c r="L26" s="136"/>
+      <c r="M26" s="136"/>
+      <c r="N26" s="136"/>
+      <c r="O26" s="136"/>
+      <c r="P26" s="138" t="s">
         <v>142</v>
       </c>
-      <c r="Q26" s="12" t="s">
+      <c r="Q26" s="139" t="s">
         <v>175</v>
       </c>
-      <c r="R26" s="12" t="s">
+      <c r="R26" s="139" t="s">
         <v>177</v>
       </c>
-      <c r="S26" s="49" t="s">
+      <c r="S26" s="139" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="27" spans="1:19" ht="30" x14ac:dyDescent="0.25">
-      <c r="A27" s="92"/>
-      <c r="B27" s="93"/>
-      <c r="C27" s="97"/>
-      <c r="D27" s="98"/>
-      <c r="E27" s="98"/>
-      <c r="F27" s="98"/>
-      <c r="G27" s="99"/>
-      <c r="H27" s="101"/>
-      <c r="I27" s="103"/>
-      <c r="J27" s="105"/>
-      <c r="K27" s="50"/>
-      <c r="L27" s="69"/>
-      <c r="M27" s="70"/>
-      <c r="N27" s="70"/>
-      <c r="O27" s="71"/>
-      <c r="P27" s="13" t="s">
+    <row r="27" spans="1:19" ht="31.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="133"/>
+      <c r="B27" s="133"/>
+      <c r="C27" s="134"/>
+      <c r="D27" s="134"/>
+      <c r="E27" s="134"/>
+      <c r="F27" s="134"/>
+      <c r="G27" s="134"/>
+      <c r="H27" s="134"/>
+      <c r="I27" s="135"/>
+      <c r="J27" s="136"/>
+      <c r="K27" s="137"/>
+      <c r="L27" s="136"/>
+      <c r="M27" s="136"/>
+      <c r="N27" s="136"/>
+      <c r="O27" s="136"/>
+      <c r="P27" s="138" t="s">
         <v>143</v>
       </c>
-      <c r="Q27" s="12" t="s">
+      <c r="Q27" s="139" t="s">
         <v>176</v>
       </c>
-      <c r="R27" s="12" t="s">
+      <c r="R27" s="139" t="s">
         <v>178</v>
       </c>
-      <c r="S27" s="49" t="s">
+      <c r="S27" s="139" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="28" spans="1:19" ht="30" x14ac:dyDescent="0.25">
-      <c r="A28" s="133" t="s">
+    <row r="28" spans="1:19" ht="31.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="140" t="s">
         <v>127</v>
       </c>
-      <c r="B28" s="134"/>
-      <c r="C28" s="137" t="s">
+      <c r="B28" s="140"/>
+      <c r="C28" s="141" t="s">
         <v>137</v>
       </c>
-      <c r="D28" s="138"/>
-      <c r="E28" s="138"/>
-      <c r="F28" s="138"/>
-      <c r="G28" s="139"/>
-      <c r="H28" s="143" t="str">
+      <c r="D28" s="141"/>
+      <c r="E28" s="141"/>
+      <c r="F28" s="141"/>
+      <c r="G28" s="141"/>
+      <c r="H28" s="141" t="str">
         <f>_xlfn.CONCAT("datos",B2)</f>
         <v>datosResidente</v>
       </c>
-      <c r="I28" s="145" t="str">
+      <c r="I28" s="140" t="str">
         <f>B2</f>
         <v>Residente</v>
       </c>
-      <c r="J28" s="143" t="str">
+      <c r="J28" s="141" t="str">
         <f>_xlfn.CONCAT("Corresponde a los datos que se van a modificar del ",B2)</f>
         <v>Corresponde a los datos que se van a modificar del Residente</v>
       </c>
-      <c r="K28" s="34"/>
-      <c r="L28" s="127"/>
-      <c r="M28" s="128"/>
-      <c r="N28" s="128"/>
-      <c r="O28" s="129"/>
-      <c r="P28" s="53" t="s">
+      <c r="K28" s="142"/>
+      <c r="L28" s="141"/>
+      <c r="M28" s="141"/>
+      <c r="N28" s="141"/>
+      <c r="O28" s="141"/>
+      <c r="P28" s="143" t="s">
         <v>144</v>
       </c>
-      <c r="Q28" s="53" t="s">
+      <c r="Q28" s="143" t="s">
         <v>179</v>
       </c>
-      <c r="R28" s="53" t="s">
+      <c r="R28" s="143" t="s">
         <v>181</v>
       </c>
-      <c r="S28" s="53" t="s">
+      <c r="S28" s="143" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="29" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="135"/>
-      <c r="B29" s="136"/>
-      <c r="C29" s="140"/>
+    <row r="29" spans="1:19" ht="30" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="140"/>
+      <c r="B29" s="140"/>
+      <c r="C29" s="141"/>
       <c r="D29" s="141"/>
       <c r="E29" s="141"/>
       <c r="F29" s="141"/>
-      <c r="G29" s="142"/>
-      <c r="H29" s="144"/>
-      <c r="I29" s="146"/>
-      <c r="J29" s="144"/>
-      <c r="K29" s="34"/>
-      <c r="L29" s="127"/>
-      <c r="M29" s="128"/>
-      <c r="N29" s="128"/>
-      <c r="O29" s="129"/>
-      <c r="P29" s="53" t="s">
+      <c r="G29" s="141"/>
+      <c r="H29" s="141"/>
+      <c r="I29" s="140"/>
+      <c r="J29" s="141"/>
+      <c r="K29" s="142"/>
+      <c r="L29" s="141"/>
+      <c r="M29" s="141"/>
+      <c r="N29" s="141"/>
+      <c r="O29" s="141"/>
+      <c r="P29" s="143" t="s">
         <v>145</v>
       </c>
-      <c r="Q29" s="53" t="s">
+      <c r="Q29" s="143" t="s">
         <v>180</v>
       </c>
-      <c r="R29" s="53" t="s">
+      <c r="R29" s="143" t="s">
         <v>183</v>
       </c>
-      <c r="S29" s="54" t="s">
+      <c r="S29" s="143" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="30" spans="1:19" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="114" t="s">
+    <row r="30" spans="1:19" ht="69.599999999999994" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="144" t="s">
         <v>122</v>
       </c>
-      <c r="B30" s="115"/>
-      <c r="C30" s="116" t="s">
+      <c r="B30" s="144"/>
+      <c r="C30" s="145" t="s">
         <v>136</v>
       </c>
-      <c r="D30" s="117"/>
-      <c r="E30" s="117"/>
-      <c r="F30" s="117"/>
-      <c r="G30" s="118"/>
-      <c r="H30" s="30" t="str">
+      <c r="D30" s="145"/>
+      <c r="E30" s="145"/>
+      <c r="F30" s="145"/>
+      <c r="G30" s="145"/>
+      <c r="H30" s="146" t="str">
         <f>_xlfn.CONCAT("datos",B2)</f>
         <v>datosResidente</v>
       </c>
-      <c r="I30" s="55" t="str">
+      <c r="I30" s="147" t="str">
         <f>B2</f>
         <v>Residente</v>
       </c>
-      <c r="J30" s="30" t="str">
+      <c r="J30" s="146" t="str">
         <f>_xlfn.CONCAT("Corresponde a un objeto que contiene los filtros de consulta de un  ",B2," de un conjunto residencial.")</f>
         <v>Corresponde a un objeto que contiene los filtros de consulta de un  Residente de un conjunto residencial.</v>
       </c>
-      <c r="K30" s="41" t="s">
+      <c r="K30" s="148" t="s">
         <v>140</v>
       </c>
-      <c r="L30" s="119" t="s">
+      <c r="L30" s="149" t="s">
         <v>153</v>
       </c>
-      <c r="M30" s="120"/>
-      <c r="N30" s="120"/>
-      <c r="O30" s="121"/>
-      <c r="P30" s="23" t="s">
+      <c r="M30" s="149"/>
+      <c r="N30" s="149"/>
+      <c r="O30" s="149"/>
+      <c r="P30" s="150" t="s">
         <v>148</v>
       </c>
-      <c r="Q30" s="31" t="s">
+      <c r="Q30" s="151" t="s">
         <v>126</v>
       </c>
-      <c r="R30" s="31" t="s">
+      <c r="R30" s="151" t="s">
         <v>108</v>
       </c>
-      <c r="S30" s="51" t="s">
+      <c r="S30" s="151" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="31" spans="1:19" ht="30" x14ac:dyDescent="0.25">
-      <c r="A31" s="106" t="s">
+    <row r="31" spans="1:19" ht="31.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="152" t="s">
         <v>133</v>
       </c>
-      <c r="B31" s="107"/>
-      <c r="C31" s="108" t="s">
+      <c r="B31" s="152"/>
+      <c r="C31" s="153" t="s">
         <v>138</v>
       </c>
-      <c r="D31" s="109"/>
-      <c r="E31" s="109"/>
-      <c r="F31" s="109"/>
-      <c r="G31" s="110"/>
-      <c r="H31" s="35" t="s">
+      <c r="D31" s="153"/>
+      <c r="E31" s="153"/>
+      <c r="F31" s="153"/>
+      <c r="G31" s="153"/>
+      <c r="H31" s="154" t="s">
         <v>39</v>
       </c>
-      <c r="I31" s="25" t="s">
+      <c r="I31" s="155" t="s">
         <v>9</v>
       </c>
-      <c r="J31" s="35" t="str">
+      <c r="J31" s="154" t="str">
         <f>_xlfn.CONCAT("Corresponde al identificador del ",$B$2,"  que se quiere dar de baja.")</f>
         <v>Corresponde al identificador del Residente  que se quiere dar de baja.</v>
       </c>
-      <c r="K31" s="36"/>
-      <c r="L31" s="111"/>
-      <c r="M31" s="112"/>
-      <c r="N31" s="112"/>
-      <c r="O31" s="113"/>
-      <c r="P31" s="25" t="s">
+      <c r="K31" s="156"/>
+      <c r="L31" s="157"/>
+      <c r="M31" s="157"/>
+      <c r="N31" s="157"/>
+      <c r="O31" s="157"/>
+      <c r="P31" s="155" t="s">
         <v>149</v>
       </c>
-      <c r="Q31" s="37" t="s">
+      <c r="Q31" s="158" t="s">
         <v>130</v>
       </c>
-      <c r="R31" s="37" t="s">
+      <c r="R31" s="158" t="s">
         <v>150</v>
       </c>
-      <c r="S31" s="37" t="s">
+      <c r="S31" s="158" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="32" spans="1:19" ht="30" x14ac:dyDescent="0.25">
-      <c r="A32" s="106" t="s">
+    <row r="32" spans="1:19" ht="31.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="152" t="s">
         <v>133</v>
       </c>
-      <c r="B32" s="107"/>
-      <c r="C32" s="108" t="s">
+      <c r="B32" s="152"/>
+      <c r="C32" s="153" t="s">
         <v>138</v>
       </c>
-      <c r="D32" s="109"/>
-      <c r="E32" s="109"/>
-      <c r="F32" s="109"/>
-      <c r="G32" s="110"/>
-      <c r="H32" s="35" t="s">
+      <c r="D32" s="153"/>
+      <c r="E32" s="153"/>
+      <c r="F32" s="153"/>
+      <c r="G32" s="153"/>
+      <c r="H32" s="154" t="s">
         <v>39</v>
       </c>
-      <c r="I32" s="25" t="s">
+      <c r="I32" s="155" t="s">
         <v>9</v>
       </c>
-      <c r="J32" s="35" t="str">
+      <c r="J32" s="154" t="str">
         <f>_xlfn.CONCAT("Corresponde al identificador del ",$B$2,"  que se quiere dar de baja.")</f>
         <v>Corresponde al identificador del Residente  que se quiere dar de baja.</v>
       </c>
-      <c r="K32" s="36"/>
-      <c r="L32" s="111"/>
-      <c r="M32" s="112"/>
-      <c r="N32" s="112"/>
-      <c r="O32" s="113"/>
-      <c r="P32" s="25" t="s">
+      <c r="K32" s="156"/>
+      <c r="L32" s="157"/>
+      <c r="M32" s="157"/>
+      <c r="N32" s="157"/>
+      <c r="O32" s="157"/>
+      <c r="P32" s="155" t="s">
         <v>149</v>
       </c>
-      <c r="Q32" s="37" t="s">
+      <c r="Q32" s="158" t="s">
         <v>130</v>
       </c>
-      <c r="R32" s="37" t="s">
+      <c r="R32" s="158" t="s">
         <v>150</v>
       </c>
-      <c r="S32" s="37" t="s">
+      <c r="S32" s="158" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="33" spans="1:19" ht="30" x14ac:dyDescent="0.25">
-      <c r="A33" s="106" t="s">
+    <row r="33" spans="1:19" ht="31.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="152" t="s">
         <v>133</v>
       </c>
-      <c r="B33" s="107"/>
-      <c r="C33" s="108" t="s">
+      <c r="B33" s="152"/>
+      <c r="C33" s="153" t="s">
         <v>138</v>
       </c>
-      <c r="D33" s="109"/>
-      <c r="E33" s="109"/>
-      <c r="F33" s="109"/>
-      <c r="G33" s="110"/>
-      <c r="H33" s="35" t="s">
+      <c r="D33" s="153"/>
+      <c r="E33" s="153"/>
+      <c r="F33" s="153"/>
+      <c r="G33" s="153"/>
+      <c r="H33" s="154" t="s">
         <v>39</v>
       </c>
-      <c r="I33" s="25" t="s">
+      <c r="I33" s="155" t="s">
         <v>9</v>
       </c>
-      <c r="J33" s="35" t="str">
+      <c r="J33" s="154" t="str">
         <f>_xlfn.CONCAT("Corresponde al identificador del ",$B$2,"  que se quiere dar de baja.")</f>
         <v>Corresponde al identificador del Residente  que se quiere dar de baja.</v>
       </c>
-      <c r="K33" s="36"/>
-      <c r="L33" s="111"/>
-      <c r="M33" s="112"/>
-      <c r="N33" s="112"/>
-      <c r="O33" s="113"/>
-      <c r="P33" s="25" t="s">
+      <c r="K33" s="156"/>
+      <c r="L33" s="157"/>
+      <c r="M33" s="157"/>
+      <c r="N33" s="157"/>
+      <c r="O33" s="157"/>
+      <c r="P33" s="155" t="s">
         <v>149</v>
       </c>
-      <c r="Q33" s="37" t="s">
+      <c r="Q33" s="158" t="s">
         <v>130</v>
       </c>
-      <c r="R33" s="37" t="s">
+      <c r="R33" s="158" t="s">
         <v>150</v>
       </c>
-      <c r="S33" s="37" t="s">
+      <c r="S33" s="158" t="s">
         <v>132</v>
       </c>
     </row>
+    <row r="34" spans="1:19" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="48">
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="C32:G32"/>
-    <mergeCell ref="L32:O32"/>
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="C33:G33"/>
-    <mergeCell ref="L33:O33"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="C31:G31"/>
-    <mergeCell ref="L31:O31"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="C30:G30"/>
-    <mergeCell ref="L30:O30"/>
-    <mergeCell ref="L28:O28"/>
-    <mergeCell ref="A28:B29"/>
-    <mergeCell ref="C28:G29"/>
-    <mergeCell ref="H28:H29"/>
-    <mergeCell ref="I28:I29"/>
-    <mergeCell ref="J28:J29"/>
-    <mergeCell ref="L29:O29"/>
-    <mergeCell ref="A25:B27"/>
-    <mergeCell ref="C25:G27"/>
-    <mergeCell ref="H25:H27"/>
-    <mergeCell ref="I25:I27"/>
-    <mergeCell ref="J25:J27"/>
+    <mergeCell ref="C20:C21"/>
+    <mergeCell ref="C18:C19"/>
+    <mergeCell ref="G18:G21"/>
+    <mergeCell ref="I16:K16"/>
+    <mergeCell ref="I18:I21"/>
+    <mergeCell ref="K18:K21"/>
+    <mergeCell ref="F18:F21"/>
+    <mergeCell ref="J18:J21"/>
     <mergeCell ref="L25:O27"/>
     <mergeCell ref="R23:S23"/>
     <mergeCell ref="L24:O24"/>
@@ -4289,14 +4325,30 @@
     <mergeCell ref="B18:B21"/>
     <mergeCell ref="E16:G16"/>
     <mergeCell ref="E18:E21"/>
-    <mergeCell ref="C20:C21"/>
-    <mergeCell ref="C18:C19"/>
-    <mergeCell ref="G18:G21"/>
-    <mergeCell ref="I16:K16"/>
-    <mergeCell ref="I18:I21"/>
-    <mergeCell ref="K18:K21"/>
-    <mergeCell ref="F18:F21"/>
-    <mergeCell ref="J18:J21"/>
+    <mergeCell ref="A25:B27"/>
+    <mergeCell ref="C25:G27"/>
+    <mergeCell ref="H25:H27"/>
+    <mergeCell ref="I25:I27"/>
+    <mergeCell ref="J25:J27"/>
+    <mergeCell ref="L28:O28"/>
+    <mergeCell ref="A28:B29"/>
+    <mergeCell ref="C28:G29"/>
+    <mergeCell ref="H28:H29"/>
+    <mergeCell ref="I28:I29"/>
+    <mergeCell ref="J28:J29"/>
+    <mergeCell ref="L29:O29"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="C31:G31"/>
+    <mergeCell ref="L31:O31"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="C30:G30"/>
+    <mergeCell ref="L30:O30"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="C32:G32"/>
+    <mergeCell ref="L32:O32"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="C33:G33"/>
+    <mergeCell ref="L33:O33"/>
   </mergeCells>
   <phoneticPr fontId="9" type="noConversion"/>
   <hyperlinks>
@@ -4353,7 +4405,7 @@
     <col min="6" max="6" width="19.28515625" style="7" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="15.28515625" style="7" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="28.5703125" style="7" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="61.28515625" style="7" customWidth="1"/>
+    <col min="9" max="9" width="79.42578125" style="7" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="79.28515625" style="7" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="18.140625" style="7" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="19.28515625" style="7" bestFit="1" customWidth="1"/>
@@ -4371,73 +4423,73 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A1" s="77" t="s">
+      <c r="A1" s="106" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="77"/>
-      <c r="C1" s="77"/>
-      <c r="D1" s="77"/>
-      <c r="E1" s="77"/>
-      <c r="F1" s="77"/>
-      <c r="G1" s="77"/>
-      <c r="H1" s="77"/>
-      <c r="I1" s="77"/>
-      <c r="J1" s="77"/>
-      <c r="K1" s="77"/>
-      <c r="L1" s="77"/>
-      <c r="M1" s="77"/>
-      <c r="N1" s="77"/>
-      <c r="O1" s="77"/>
-      <c r="P1" s="77"/>
-      <c r="Q1" s="77"/>
+      <c r="B1" s="106"/>
+      <c r="C1" s="106"/>
+      <c r="D1" s="106"/>
+      <c r="E1" s="106"/>
+      <c r="F1" s="106"/>
+      <c r="G1" s="106"/>
+      <c r="H1" s="106"/>
+      <c r="I1" s="106"/>
+      <c r="J1" s="106"/>
+      <c r="K1" s="106"/>
+      <c r="L1" s="106"/>
+      <c r="M1" s="106"/>
+      <c r="N1" s="106"/>
+      <c r="O1" s="106"/>
+      <c r="P1" s="106"/>
+      <c r="Q1" s="106"/>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A2" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="B2" s="78" t="str">
+      <c r="B2" s="107" t="str">
         <f>'Listado Objetos de Dominio'!A4</f>
         <v>Inmueble</v>
       </c>
-      <c r="C2" s="78"/>
-      <c r="D2" s="78"/>
-      <c r="E2" s="78"/>
-      <c r="F2" s="78"/>
-      <c r="G2" s="78"/>
-      <c r="H2" s="78"/>
-      <c r="I2" s="78"/>
-      <c r="J2" s="78"/>
-      <c r="K2" s="78"/>
-      <c r="L2" s="78"/>
-      <c r="M2" s="78"/>
-      <c r="N2" s="78"/>
-      <c r="O2" s="78"/>
-      <c r="P2" s="78"/>
-      <c r="Q2" s="78"/>
+      <c r="C2" s="107"/>
+      <c r="D2" s="107"/>
+      <c r="E2" s="107"/>
+      <c r="F2" s="107"/>
+      <c r="G2" s="107"/>
+      <c r="H2" s="107"/>
+      <c r="I2" s="107"/>
+      <c r="J2" s="107"/>
+      <c r="K2" s="107"/>
+      <c r="L2" s="107"/>
+      <c r="M2" s="107"/>
+      <c r="N2" s="107"/>
+      <c r="O2" s="107"/>
+      <c r="P2" s="107"/>
+      <c r="Q2" s="107"/>
     </row>
     <row r="3" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="B3" s="79" t="str">
+      <c r="B3" s="108" t="str">
         <f>'Listado Objetos de Dominio'!B4</f>
         <v xml:space="preserve">Objeto de dominio que representa el inmueble donde vive el residente del conjunto residencial. </v>
       </c>
-      <c r="C3" s="79"/>
-      <c r="D3" s="79"/>
-      <c r="E3" s="79"/>
-      <c r="F3" s="79"/>
-      <c r="G3" s="79"/>
-      <c r="H3" s="79"/>
-      <c r="I3" s="79"/>
-      <c r="J3" s="79"/>
-      <c r="K3" s="79"/>
-      <c r="L3" s="79"/>
-      <c r="M3" s="79"/>
-      <c r="N3" s="79"/>
-      <c r="O3" s="79"/>
-      <c r="P3" s="79"/>
-      <c r="Q3" s="79"/>
+      <c r="C3" s="108"/>
+      <c r="D3" s="108"/>
+      <c r="E3" s="108"/>
+      <c r="F3" s="108"/>
+      <c r="G3" s="108"/>
+      <c r="H3" s="108"/>
+      <c r="I3" s="108"/>
+      <c r="J3" s="108"/>
+      <c r="K3" s="108"/>
+      <c r="L3" s="108"/>
+      <c r="M3" s="108"/>
+      <c r="N3" s="108"/>
+      <c r="O3" s="108"/>
+      <c r="P3" s="108"/>
+      <c r="Q3" s="108"/>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A4" s="15" t="s">
@@ -5045,11 +5097,11 @@
     </row>
     <row r="15" spans="1:21" ht="23.45" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="16" spans="1:21" ht="51" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="63" t="s">
+      <c r="A16" s="109" t="s">
         <v>47</v>
       </c>
-      <c r="B16" s="63"/>
-      <c r="C16" s="63"/>
+      <c r="B16" s="109"/>
+      <c r="C16" s="109"/>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A17" s="26" t="s">
@@ -5063,131 +5115,131 @@
       </c>
     </row>
     <row r="18" spans="1:19" ht="31.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="65" t="s">
+      <c r="A18" s="121" t="s">
         <v>160</v>
       </c>
-      <c r="B18" s="65" t="s">
+      <c r="B18" s="121" t="s">
         <v>161</v>
       </c>
-      <c r="C18" s="132" t="str">
-        <f>A5</f>
+      <c r="C18" s="55" t="str">
+        <f t="shared" ref="C18:C27" si="0">A5</f>
         <v>identificadorConjuntoResidencial</v>
       </c>
     </row>
     <row r="19" spans="1:19" ht="31.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="65"/>
-      <c r="B19" s="65"/>
-      <c r="C19" s="132" t="str">
-        <f>A6</f>
+      <c r="A19" s="121"/>
+      <c r="B19" s="121"/>
+      <c r="C19" s="55" t="str">
+        <f t="shared" si="0"/>
         <v>nombreConjuntoResidencial</v>
       </c>
     </row>
     <row r="20" spans="1:19" ht="31.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="65"/>
-      <c r="B20" s="65"/>
-      <c r="C20" s="132" t="str">
-        <f>A7</f>
+      <c r="A20" s="121"/>
+      <c r="B20" s="121"/>
+      <c r="C20" s="55" t="str">
+        <f t="shared" si="0"/>
         <v>identificadorTipoZonaInmueble</v>
       </c>
     </row>
     <row r="21" spans="1:19" ht="31.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="65"/>
-      <c r="B21" s="65"/>
-      <c r="C21" s="132" t="str">
-        <f>A8</f>
+      <c r="A21" s="121"/>
+      <c r="B21" s="121"/>
+      <c r="C21" s="55" t="str">
+        <f t="shared" si="0"/>
         <v>nombreTipoZonaInmueble</v>
       </c>
     </row>
     <row r="22" spans="1:19" ht="31.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="65"/>
-      <c r="B22" s="65"/>
-      <c r="C22" s="132" t="str">
-        <f>A9</f>
+      <c r="A22" s="121"/>
+      <c r="B22" s="121"/>
+      <c r="C22" s="55" t="str">
+        <f t="shared" si="0"/>
         <v>identificadorZonaInmueble</v>
       </c>
     </row>
     <row r="23" spans="1:19" ht="31.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="65"/>
-      <c r="B23" s="65"/>
-      <c r="C23" s="132" t="str">
-        <f>A10</f>
+      <c r="A23" s="121"/>
+      <c r="B23" s="121"/>
+      <c r="C23" s="55" t="str">
+        <f t="shared" si="0"/>
         <v>numeroZonaInmuebleZonaInmueble</v>
       </c>
     </row>
     <row r="24" spans="1:19" ht="31.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="65"/>
-      <c r="B24" s="65"/>
-      <c r="C24" s="132" t="str">
-        <f>A11</f>
+      <c r="A24" s="121"/>
+      <c r="B24" s="121"/>
+      <c r="C24" s="55" t="str">
+        <f t="shared" si="0"/>
         <v>identificadorTipoInmueble</v>
       </c>
     </row>
     <row r="25" spans="1:19" ht="31.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="65"/>
-      <c r="B25" s="65"/>
-      <c r="C25" s="132" t="str">
-        <f>A12</f>
+      <c r="A25" s="121"/>
+      <c r="B25" s="121"/>
+      <c r="C25" s="55" t="str">
+        <f t="shared" si="0"/>
         <v>nombreTipoInmueble</v>
       </c>
     </row>
     <row r="26" spans="1:19" ht="31.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="65"/>
-      <c r="B26" s="65"/>
+      <c r="A26" s="121"/>
+      <c r="B26" s="121"/>
       <c r="C26" s="38" t="str">
-        <f>A13</f>
+        <f t="shared" si="0"/>
         <v>identificadorInmueble</v>
       </c>
     </row>
     <row r="27" spans="1:19" ht="31.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="65"/>
-      <c r="B27" s="65"/>
+      <c r="A27" s="121"/>
+      <c r="B27" s="121"/>
       <c r="C27" s="38" t="str">
-        <f>A14</f>
+        <f t="shared" si="0"/>
         <v>numeroViviendaInmueble</v>
       </c>
     </row>
     <row r="28" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="29" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A29" s="80" t="s">
+      <c r="A29" s="110" t="s">
         <v>51</v>
       </c>
-      <c r="B29" s="81"/>
-      <c r="C29" s="84" t="s">
+      <c r="B29" s="111"/>
+      <c r="C29" s="114" t="s">
         <v>2</v>
       </c>
-      <c r="D29" s="85"/>
-      <c r="E29" s="85"/>
-      <c r="F29" s="85"/>
-      <c r="G29" s="81"/>
-      <c r="H29" s="72" t="s">
+      <c r="D29" s="115"/>
+      <c r="E29" s="115"/>
+      <c r="F29" s="115"/>
+      <c r="G29" s="111"/>
+      <c r="H29" s="101" t="s">
         <v>52</v>
       </c>
-      <c r="I29" s="88"/>
-      <c r="J29" s="89"/>
-      <c r="K29" s="72" t="s">
+      <c r="I29" s="118"/>
+      <c r="J29" s="119"/>
+      <c r="K29" s="101" t="s">
         <v>53</v>
       </c>
-      <c r="L29" s="88"/>
-      <c r="M29" s="88"/>
-      <c r="N29" s="88"/>
-      <c r="O29" s="89"/>
-      <c r="P29" s="72" t="s">
+      <c r="L29" s="118"/>
+      <c r="M29" s="118"/>
+      <c r="N29" s="118"/>
+      <c r="O29" s="119"/>
+      <c r="P29" s="101" t="s">
         <v>54</v>
       </c>
-      <c r="Q29" s="89"/>
-      <c r="R29" s="72" t="s">
+      <c r="Q29" s="119"/>
+      <c r="R29" s="101" t="s">
         <v>55</v>
       </c>
-      <c r="S29" s="73"/>
+      <c r="S29" s="102"/>
     </row>
     <row r="30" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A30" s="82"/>
-      <c r="B30" s="83"/>
-      <c r="C30" s="86"/>
-      <c r="D30" s="87"/>
-      <c r="E30" s="87"/>
-      <c r="F30" s="87"/>
-      <c r="G30" s="83"/>
+      <c r="A30" s="112"/>
+      <c r="B30" s="113"/>
+      <c r="C30" s="116"/>
+      <c r="D30" s="117"/>
+      <c r="E30" s="117"/>
+      <c r="F30" s="117"/>
+      <c r="G30" s="113"/>
       <c r="H30" s="47" t="s">
         <v>56</v>
       </c>
@@ -5200,12 +5252,12 @@
       <c r="K30" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="L30" s="74" t="s">
+      <c r="L30" s="103" t="s">
         <v>2</v>
       </c>
-      <c r="M30" s="75"/>
-      <c r="N30" s="75"/>
-      <c r="O30" s="76"/>
+      <c r="M30" s="104"/>
+      <c r="N30" s="104"/>
+      <c r="O30" s="105"/>
       <c r="P30" s="27" t="s">
         <v>58</v>
       </c>
@@ -5220,34 +5272,34 @@
       </c>
     </row>
     <row r="31" spans="1:19" ht="30" x14ac:dyDescent="0.25">
-      <c r="A31" s="90" t="s">
+      <c r="A31" s="81" t="s">
         <v>98</v>
       </c>
-      <c r="B31" s="91"/>
-      <c r="C31" s="94" t="s">
+      <c r="B31" s="82"/>
+      <c r="C31" s="85" t="s">
         <v>105</v>
       </c>
-      <c r="D31" s="95"/>
-      <c r="E31" s="95"/>
-      <c r="F31" s="95"/>
-      <c r="G31" s="96"/>
-      <c r="H31" s="100" t="str">
+      <c r="D31" s="86"/>
+      <c r="E31" s="86"/>
+      <c r="F31" s="86"/>
+      <c r="G31" s="87"/>
+      <c r="H31" s="91" t="str">
         <f>_xlfn.CONCAT("datos",B2)</f>
         <v>datosInmueble</v>
       </c>
-      <c r="I31" s="130" t="str">
+      <c r="I31" s="128" t="str">
         <f>B2</f>
         <v>Inmueble</v>
       </c>
-      <c r="J31" s="104" t="str">
+      <c r="J31" s="93" t="str">
         <f>_xlfn.CONCAT("Corresponde al objeto que internamente contiene los datos necesarios para crear una nueva ",B2,)</f>
         <v>Corresponde al objeto que internamente contiene los datos necesarios para crear una nueva Inmueble</v>
       </c>
       <c r="K31" s="48"/>
-      <c r="L31" s="66"/>
-      <c r="M31" s="67"/>
-      <c r="N31" s="67"/>
-      <c r="O31" s="68"/>
+      <c r="L31" s="95"/>
+      <c r="M31" s="96"/>
+      <c r="N31" s="96"/>
+      <c r="O31" s="97"/>
       <c r="P31" s="13" t="s">
         <v>106</v>
       </c>
@@ -5262,21 +5314,21 @@
       </c>
     </row>
     <row r="32" spans="1:19" ht="45" x14ac:dyDescent="0.25">
-      <c r="A32" s="92"/>
-      <c r="B32" s="93"/>
-      <c r="C32" s="97"/>
-      <c r="D32" s="98"/>
-      <c r="E32" s="98"/>
-      <c r="F32" s="98"/>
-      <c r="G32" s="99"/>
-      <c r="H32" s="101"/>
-      <c r="I32" s="131"/>
-      <c r="J32" s="105"/>
+      <c r="A32" s="83"/>
+      <c r="B32" s="84"/>
+      <c r="C32" s="88"/>
+      <c r="D32" s="89"/>
+      <c r="E32" s="89"/>
+      <c r="F32" s="89"/>
+      <c r="G32" s="90"/>
+      <c r="H32" s="92"/>
+      <c r="I32" s="129"/>
+      <c r="J32" s="94"/>
       <c r="K32" s="50"/>
-      <c r="L32" s="69"/>
-      <c r="M32" s="70"/>
-      <c r="N32" s="70"/>
-      <c r="O32" s="71"/>
+      <c r="L32" s="98"/>
+      <c r="M32" s="99"/>
+      <c r="N32" s="99"/>
+      <c r="O32" s="100"/>
       <c r="P32" s="13" t="s">
         <v>110</v>
       </c>
@@ -5291,21 +5343,21 @@
       </c>
     </row>
     <row r="33" spans="1:19" ht="30" x14ac:dyDescent="0.25">
-      <c r="A33" s="92"/>
-      <c r="B33" s="93"/>
-      <c r="C33" s="97"/>
-      <c r="D33" s="98"/>
-      <c r="E33" s="98"/>
-      <c r="F33" s="98"/>
-      <c r="G33" s="99"/>
-      <c r="H33" s="101"/>
-      <c r="I33" s="131"/>
-      <c r="J33" s="105"/>
+      <c r="A33" s="83"/>
+      <c r="B33" s="84"/>
+      <c r="C33" s="88"/>
+      <c r="D33" s="89"/>
+      <c r="E33" s="89"/>
+      <c r="F33" s="89"/>
+      <c r="G33" s="90"/>
+      <c r="H33" s="92"/>
+      <c r="I33" s="129"/>
+      <c r="J33" s="94"/>
       <c r="K33" s="50"/>
-      <c r="L33" s="69"/>
-      <c r="M33" s="70"/>
-      <c r="N33" s="70"/>
-      <c r="O33" s="71"/>
+      <c r="L33" s="98"/>
+      <c r="M33" s="99"/>
+      <c r="N33" s="99"/>
+      <c r="O33" s="100"/>
       <c r="P33" s="13" t="s">
         <v>114</v>
       </c>
@@ -5320,21 +5372,21 @@
       </c>
     </row>
     <row r="34" spans="1:19" ht="45" x14ac:dyDescent="0.25">
-      <c r="A34" s="92"/>
-      <c r="B34" s="93"/>
-      <c r="C34" s="97"/>
-      <c r="D34" s="98"/>
-      <c r="E34" s="98"/>
-      <c r="F34" s="98"/>
-      <c r="G34" s="99"/>
-      <c r="H34" s="101"/>
-      <c r="I34" s="131"/>
-      <c r="J34" s="105"/>
+      <c r="A34" s="83"/>
+      <c r="B34" s="84"/>
+      <c r="C34" s="88"/>
+      <c r="D34" s="89"/>
+      <c r="E34" s="89"/>
+      <c r="F34" s="89"/>
+      <c r="G34" s="90"/>
+      <c r="H34" s="92"/>
+      <c r="I34" s="129"/>
+      <c r="J34" s="94"/>
       <c r="K34" s="50"/>
-      <c r="L34" s="69"/>
-      <c r="M34" s="70"/>
-      <c r="N34" s="70"/>
-      <c r="O34" s="71"/>
+      <c r="L34" s="98"/>
+      <c r="M34" s="99"/>
+      <c r="N34" s="99"/>
+      <c r="O34" s="100"/>
       <c r="P34" s="13" t="s">
         <v>118</v>
       </c>
@@ -5349,17 +5401,17 @@
       </c>
     </row>
     <row r="35" spans="1:19" ht="71.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="114" t="s">
+      <c r="A35" s="70" t="s">
         <v>122</v>
       </c>
-      <c r="B35" s="115"/>
-      <c r="C35" s="116" t="s">
+      <c r="B35" s="71"/>
+      <c r="C35" s="72" t="s">
         <v>123</v>
       </c>
-      <c r="D35" s="117"/>
-      <c r="E35" s="117"/>
-      <c r="F35" s="117"/>
-      <c r="G35" s="118"/>
+      <c r="D35" s="73"/>
+      <c r="E35" s="73"/>
+      <c r="F35" s="73"/>
+      <c r="G35" s="74"/>
       <c r="H35" s="30" t="str">
         <f>_xlfn.CONCAT("datos",B2)</f>
         <v>datosInmueble</v>
@@ -5375,12 +5427,12 @@
       <c r="K35" s="41" t="s">
         <v>139</v>
       </c>
-      <c r="L35" s="119" t="s">
+      <c r="L35" s="75" t="s">
         <v>124</v>
       </c>
-      <c r="M35" s="120"/>
-      <c r="N35" s="120"/>
-      <c r="O35" s="121"/>
+      <c r="M35" s="76"/>
+      <c r="N35" s="76"/>
+      <c r="O35" s="77"/>
       <c r="P35" s="23" t="s">
         <v>125</v>
       </c>
@@ -5395,17 +5447,17 @@
       </c>
     </row>
     <row r="36" spans="1:19" ht="30" x14ac:dyDescent="0.25">
-      <c r="A36" s="122" t="s">
+      <c r="A36" s="123" t="s">
         <v>127</v>
       </c>
-      <c r="B36" s="123"/>
-      <c r="C36" s="124" t="s">
+      <c r="B36" s="124"/>
+      <c r="C36" s="125" t="s">
         <v>128</v>
       </c>
-      <c r="D36" s="125"/>
-      <c r="E36" s="125"/>
-      <c r="F36" s="125"/>
-      <c r="G36" s="126"/>
+      <c r="D36" s="126"/>
+      <c r="E36" s="126"/>
+      <c r="F36" s="126"/>
+      <c r="G36" s="127"/>
       <c r="H36" s="32" t="str">
         <f>_xlfn.CONCAT("datos",B2)</f>
         <v>datosInmueble</v>
@@ -5419,10 +5471,10 @@
         <v>Corresponde a los datos que se van a modificar de la Inmueble</v>
       </c>
       <c r="K36" s="34"/>
-      <c r="L36" s="127"/>
-      <c r="M36" s="128"/>
-      <c r="N36" s="128"/>
-      <c r="O36" s="129"/>
+      <c r="L36" s="78"/>
+      <c r="M36" s="79"/>
+      <c r="N36" s="79"/>
+      <c r="O36" s="80"/>
       <c r="P36" s="52" t="s">
         <v>129</v>
       </c>
@@ -5437,17 +5489,17 @@
       </c>
     </row>
     <row r="37" spans="1:19" ht="30" x14ac:dyDescent="0.25">
-      <c r="A37" s="106" t="s">
+      <c r="A37" s="62" t="s">
         <v>133</v>
       </c>
-      <c r="B37" s="107"/>
-      <c r="C37" s="108" t="s">
+      <c r="B37" s="63"/>
+      <c r="C37" s="64" t="s">
         <v>134</v>
       </c>
-      <c r="D37" s="109"/>
-      <c r="E37" s="109"/>
-      <c r="F37" s="109"/>
-      <c r="G37" s="110"/>
+      <c r="D37" s="65"/>
+      <c r="E37" s="65"/>
+      <c r="F37" s="65"/>
+      <c r="G37" s="66"/>
       <c r="H37" s="35" t="s">
         <v>39</v>
       </c>
@@ -5459,10 +5511,10 @@
         <v>Corresponde al identificador de la Inmueble  que se quiere dar de baja.</v>
       </c>
       <c r="K37" s="36"/>
-      <c r="L37" s="111"/>
-      <c r="M37" s="112"/>
-      <c r="N37" s="112"/>
-      <c r="O37" s="113"/>
+      <c r="L37" s="67"/>
+      <c r="M37" s="68"/>
+      <c r="N37" s="68"/>
+      <c r="O37" s="69"/>
       <c r="P37" s="25" t="s">
         <v>129</v>
       </c>
@@ -5478,6 +5530,25 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="L31:O34"/>
+    <mergeCell ref="A31:B34"/>
+    <mergeCell ref="C31:G34"/>
+    <mergeCell ref="H31:H34"/>
+    <mergeCell ref="I31:I34"/>
+    <mergeCell ref="J31:J34"/>
+    <mergeCell ref="P29:Q29"/>
+    <mergeCell ref="R29:S29"/>
+    <mergeCell ref="L30:O30"/>
+    <mergeCell ref="A29:B30"/>
+    <mergeCell ref="C29:G30"/>
+    <mergeCell ref="H29:J29"/>
+    <mergeCell ref="K29:O29"/>
+    <mergeCell ref="A1:Q1"/>
+    <mergeCell ref="B2:Q2"/>
+    <mergeCell ref="B3:Q3"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="A18:A27"/>
+    <mergeCell ref="B18:B27"/>
     <mergeCell ref="A37:B37"/>
     <mergeCell ref="C37:G37"/>
     <mergeCell ref="L37:O37"/>
@@ -5487,25 +5558,6 @@
     <mergeCell ref="A36:B36"/>
     <mergeCell ref="C36:G36"/>
     <mergeCell ref="L36:O36"/>
-    <mergeCell ref="A1:Q1"/>
-    <mergeCell ref="B2:Q2"/>
-    <mergeCell ref="B3:Q3"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="A18:A27"/>
-    <mergeCell ref="B18:B27"/>
-    <mergeCell ref="P29:Q29"/>
-    <mergeCell ref="R29:S29"/>
-    <mergeCell ref="L30:O30"/>
-    <mergeCell ref="A29:B30"/>
-    <mergeCell ref="C29:G30"/>
-    <mergeCell ref="H29:J29"/>
-    <mergeCell ref="K29:O29"/>
-    <mergeCell ref="L31:O34"/>
-    <mergeCell ref="A31:B34"/>
-    <mergeCell ref="C31:G34"/>
-    <mergeCell ref="H31:H34"/>
-    <mergeCell ref="I31:I34"/>
-    <mergeCell ref="J31:J34"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A1" location="'Objetos de Dominio'!A1" display="Volver al inicio" xr:uid="{4C6EA31D-5DD1-42F9-A469-ED5E8CAE0643}"/>

--- a/Doo-Doc/Nueva Version Victus/Modelos de Dominio Enriquecidos/Modelo De Dominio Enriquecido Residentes.xlsx
+++ b/Doo-Doc/Nueva Version Victus/Modelos de Dominio Enriquecidos/Modelo De Dominio Enriquecido Residentes.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andre\Documents\DOO 2024 BD\DOO\victus-doc\Doo-Doc\Nueva Version Victus\Modelos de Dominio Enriquecidos\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\josez\Documents\Universidad IngeSistemas\Diseño Orientado a Objetos(DOO)\VictusProyect\victus-doc\Doo-Doc\Nueva Version Victus\Modelos de Dominio Enriquecidos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6A621C3-C156-418F-A7A6-E11ABA950670}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{641175AA-DAE8-4FA5-93AB-05A9759D47F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="1050" yWindow="2790" windowWidth="18195" windowHeight="15345" firstSheet="2" activeTab="4" xr2:uid="{007C2ECE-7E90-4717-B1E7-3A143C146FF0}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="3" xr2:uid="{007C2ECE-7E90-4717-B1E7-3A143C146FF0}"/>
   </bookViews>
   <sheets>
     <sheet name="Valores" sheetId="1" r:id="rId1"/>
@@ -2201,6 +2201,54 @@
     <xf numFmtId="0" fontId="2" fillId="9" borderId="8" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="36" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="36" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2219,6 +2267,177 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="8" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="36" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="36" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="36" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="36" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="36" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="26" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="27" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="30" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="31" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="33" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="34" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2267,6 +2486,21 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="34" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="25" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2275,240 +2509,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="26" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="27" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="30" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="31" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="8" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="34" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="25" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="33" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="36" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="36" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="36" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="36" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="36" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="36" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="36" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2895,19 +2895,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8113398C-62AA-4A4A-B9CD-D2552441D379}">
   <dimension ref="A1:B15"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="52.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="52.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="56" t="s">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" s="72" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="57"/>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B1" s="73"/>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -2915,7 +2915,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>3</v>
       </c>
@@ -2923,7 +2923,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="5" t="s">
         <v>5</v>
       </c>
@@ -2931,52 +2931,52 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="5" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="5" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="5" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="5" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="5" t="s">
         <v>15</v>
       </c>
@@ -2992,7 +2992,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7A6ACC7-AE51-45F9-85DD-14DA0E6BE0E5}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -3002,26 +3002,26 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9BB7FA3B-591F-4E21-A008-4E9729EA1949}">
   <dimension ref="A1:D4"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="21.5703125" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="56.28515625" style="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.5703125" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.140625" style="7" bestFit="1" customWidth="1"/>
-    <col min="5" max="16384" width="11.42578125" style="7"/>
+    <col min="1" max="1" width="21.5546875" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="56.33203125" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.5546875" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.109375" style="7" bestFit="1" customWidth="1"/>
+    <col min="5" max="16384" width="11.44140625" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="40" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="58" t="s">
+      <c r="B1" s="74" t="s">
         <v>61</v>
       </c>
-      <c r="C1" s="58"/>
-      <c r="D1" s="59"/>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C1" s="74"/>
+      <c r="D1" s="75"/>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="8" t="s">
         <v>17</v>
       </c>
@@ -3035,7 +3035,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A3" s="11" t="s">
         <v>19</v>
       </c>
@@ -3045,12 +3045,12 @@
       <c r="C3" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="60" t="str">
+      <c r="D3" s="76" t="str">
         <f>$B$1</f>
         <v>Residentes</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A4" s="11" t="s">
         <v>68</v>
       </c>
@@ -3061,7 +3061,7 @@
         <f>Valores!$A$4</f>
         <v>Referenciado</v>
       </c>
-      <c r="D4" s="61"/>
+      <c r="D4" s="77"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -3078,103 +3078,103 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3CD2E3E-2179-4007-8743-BED3F3BF1317}">
   <dimension ref="A1:U34"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="23.85546875" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.5703125" style="7" customWidth="1"/>
-    <col min="3" max="3" width="18.7109375" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.85546875" style="7" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.7109375" style="7" customWidth="1"/>
-    <col min="6" max="6" width="19.28515625" style="7" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.28515625" style="7" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="28.5703125" style="7" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="61.28515625" style="7" customWidth="1"/>
-    <col min="10" max="10" width="79.28515625" style="7" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="18.140625" style="7" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="19.28515625" style="7" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="7" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15.7109375" style="7" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.85546875" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23.88671875" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.5546875" style="7" customWidth="1"/>
+    <col min="3" max="3" width="18.6640625" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.88671875" style="7" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.6640625" style="7" customWidth="1"/>
+    <col min="6" max="6" width="19.33203125" style="7" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.33203125" style="7" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="28.5546875" style="7" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="61.33203125" style="7" customWidth="1"/>
+    <col min="10" max="10" width="79.33203125" style="7" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="18.109375" style="7" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="19.33203125" style="7" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.44140625" style="7" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.6640625" style="7" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.88671875" style="7" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="25" style="7" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="94.42578125" style="7" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="116.7109375" style="7" customWidth="1"/>
-    <col min="19" max="19" width="46.42578125" style="7" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="50.140625" style="7" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="66.85546875" style="7" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="52.28515625" style="7" bestFit="1" customWidth="1"/>
-    <col min="23" max="16384" width="11.42578125" style="7"/>
+    <col min="17" max="17" width="94.44140625" style="7" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="116.6640625" style="7" customWidth="1"/>
+    <col min="19" max="19" width="46.44140625" style="7" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="50.109375" style="7" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="66.88671875" style="7" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="52.33203125" style="7" bestFit="1" customWidth="1"/>
+    <col min="23" max="16384" width="11.44140625" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A1" s="106" t="s">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A1" s="84" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="106"/>
-      <c r="C1" s="106"/>
-      <c r="D1" s="106"/>
-      <c r="E1" s="106"/>
-      <c r="F1" s="106"/>
-      <c r="G1" s="106"/>
-      <c r="H1" s="106"/>
-      <c r="I1" s="106"/>
-      <c r="J1" s="106"/>
-      <c r="K1" s="106"/>
-      <c r="L1" s="106"/>
-      <c r="M1" s="106"/>
-      <c r="N1" s="106"/>
-      <c r="O1" s="106"/>
-      <c r="P1" s="106"/>
-      <c r="Q1" s="106"/>
-    </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="B1" s="84"/>
+      <c r="C1" s="84"/>
+      <c r="D1" s="84"/>
+      <c r="E1" s="84"/>
+      <c r="F1" s="84"/>
+      <c r="G1" s="84"/>
+      <c r="H1" s="84"/>
+      <c r="I1" s="84"/>
+      <c r="J1" s="84"/>
+      <c r="K1" s="84"/>
+      <c r="L1" s="84"/>
+      <c r="M1" s="84"/>
+      <c r="N1" s="84"/>
+      <c r="O1" s="84"/>
+      <c r="P1" s="84"/>
+      <c r="Q1" s="84"/>
+    </row>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A2" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="B2" s="107" t="str">
+      <c r="B2" s="85" t="str">
         <f>'Listado Objetos de Dominio'!A3</f>
         <v>Residente</v>
       </c>
-      <c r="C2" s="107"/>
-      <c r="D2" s="107"/>
-      <c r="E2" s="107"/>
-      <c r="F2" s="107"/>
-      <c r="G2" s="107"/>
-      <c r="H2" s="107"/>
-      <c r="I2" s="107"/>
-      <c r="J2" s="107"/>
-      <c r="K2" s="107"/>
-      <c r="L2" s="107"/>
-      <c r="M2" s="107"/>
-      <c r="N2" s="107"/>
-      <c r="O2" s="107"/>
-      <c r="P2" s="107"/>
-      <c r="Q2" s="107"/>
-    </row>
-    <row r="3" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C2" s="85"/>
+      <c r="D2" s="85"/>
+      <c r="E2" s="85"/>
+      <c r="F2" s="85"/>
+      <c r="G2" s="85"/>
+      <c r="H2" s="85"/>
+      <c r="I2" s="85"/>
+      <c r="J2" s="85"/>
+      <c r="K2" s="85"/>
+      <c r="L2" s="85"/>
+      <c r="M2" s="85"/>
+      <c r="N2" s="85"/>
+      <c r="O2" s="85"/>
+      <c r="P2" s="85"/>
+      <c r="Q2" s="85"/>
+    </row>
+    <row r="3" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="B3" s="108" t="str">
+      <c r="B3" s="86" t="str">
         <f>'Listado Objetos de Dominio'!B3</f>
         <v>Objeto de dominio que representa a un residente que vive dentro de un inmueble en un conjunto residencial</v>
       </c>
-      <c r="C3" s="108"/>
-      <c r="D3" s="108"/>
-      <c r="E3" s="108"/>
-      <c r="F3" s="108"/>
-      <c r="G3" s="108"/>
-      <c r="H3" s="108"/>
-      <c r="I3" s="108"/>
-      <c r="J3" s="108"/>
-      <c r="K3" s="108"/>
-      <c r="L3" s="108"/>
-      <c r="M3" s="108"/>
-      <c r="N3" s="108"/>
-      <c r="O3" s="108"/>
-      <c r="P3" s="108"/>
-      <c r="Q3" s="108"/>
-    </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="C3" s="86"/>
+      <c r="D3" s="86"/>
+      <c r="E3" s="86"/>
+      <c r="F3" s="86"/>
+      <c r="G3" s="86"/>
+      <c r="H3" s="86"/>
+      <c r="I3" s="86"/>
+      <c r="J3" s="86"/>
+      <c r="K3" s="86"/>
+      <c r="L3" s="86"/>
+      <c r="M3" s="86"/>
+      <c r="N3" s="86"/>
+      <c r="O3" s="86"/>
+      <c r="P3" s="86"/>
+      <c r="Q3" s="86"/>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A4" s="15" t="s">
         <v>23</v>
       </c>
@@ -3242,7 +3242,7 @@
         <v>Eliminar</v>
       </c>
     </row>
-    <row r="5" spans="1:21" ht="27" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:21" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A5" s="18" t="s">
         <v>39</v>
       </c>
@@ -3295,7 +3295,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="6" spans="1:21" ht="40.5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:21" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A6" s="18" t="s">
         <v>43</v>
       </c>
@@ -3350,7 +3350,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="7" spans="1:21" ht="40.5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:21" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A7" s="18" t="s">
         <v>63</v>
       </c>
@@ -3405,7 +3405,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="8" spans="1:21" ht="40.5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:21" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A8" s="18" t="s">
         <v>71</v>
       </c>
@@ -3460,7 +3460,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A9" s="18" t="s">
         <v>77</v>
       </c>
@@ -3513,7 +3513,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A10" s="18" t="s">
         <v>64</v>
       </c>
@@ -3562,7 +3562,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="11" spans="1:21" ht="40.5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:21" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A11" s="18" t="s">
         <v>78</v>
       </c>
@@ -3617,7 +3617,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="12" spans="1:21" ht="40.5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:21" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A12" s="18" t="s">
         <v>93</v>
       </c>
@@ -3672,7 +3672,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="13" spans="1:21" ht="67.5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:21" ht="69" x14ac:dyDescent="0.3">
       <c r="A13" s="18" t="s">
         <v>72</v>
       </c>
@@ -3727,7 +3727,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="14" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A14" s="18" t="s">
         <v>65</v>
       </c>
@@ -3776,24 +3776,24 @@
         <v>104</v>
       </c>
     </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A16" s="109" t="s">
+    <row r="16" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A16" s="79" t="s">
         <v>88</v>
       </c>
-      <c r="B16" s="109"/>
-      <c r="C16" s="109"/>
-      <c r="E16" s="109" t="s">
+      <c r="B16" s="79"/>
+      <c r="C16" s="79"/>
+      <c r="E16" s="79" t="s">
         <v>90</v>
       </c>
-      <c r="F16" s="109"/>
-      <c r="G16" s="109"/>
-      <c r="I16" s="109" t="s">
+      <c r="F16" s="79"/>
+      <c r="G16" s="79"/>
+      <c r="I16" s="79" t="s">
         <v>47</v>
       </c>
-      <c r="J16" s="109"/>
-      <c r="K16" s="109"/>
-    </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="J16" s="79"/>
+      <c r="K16" s="79"/>
+    </row>
+    <row r="17" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A17" s="26" t="s">
         <v>48</v>
       </c>
@@ -3822,493 +3822,509 @@
         <v>49</v>
       </c>
     </row>
-    <row r="18" spans="1:19" ht="25.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="120" t="s">
+    <row r="18" spans="1:19" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="80" t="s">
         <v>50</v>
       </c>
-      <c r="B18" s="121" t="s">
+      <c r="B18" s="81" t="s">
         <v>89</v>
       </c>
-      <c r="C18" s="122" t="s">
+      <c r="C18" s="78" t="s">
         <v>71</v>
       </c>
-      <c r="E18" s="121" t="s">
+      <c r="E18" s="81" t="s">
         <v>94</v>
       </c>
-      <c r="F18" s="121" t="s">
+      <c r="F18" s="81" t="s">
         <v>91</v>
       </c>
-      <c r="G18" s="122" t="s">
+      <c r="G18" s="78" t="s">
         <v>78</v>
       </c>
       <c r="H18" s="39"/>
-      <c r="I18" s="120" t="s">
+      <c r="I18" s="80" t="s">
         <v>95</v>
       </c>
-      <c r="J18" s="121" t="s">
+      <c r="J18" s="81" t="s">
         <v>92</v>
       </c>
-      <c r="K18" s="122" t="s">
+      <c r="K18" s="78" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="19" spans="1:19" ht="25.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="120"/>
-      <c r="B19" s="121"/>
-      <c r="C19" s="122"/>
-      <c r="E19" s="121"/>
-      <c r="F19" s="121"/>
-      <c r="G19" s="122"/>
+    <row r="19" spans="1:19" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="80"/>
+      <c r="B19" s="81"/>
+      <c r="C19" s="78"/>
+      <c r="E19" s="81"/>
+      <c r="F19" s="81"/>
+      <c r="G19" s="78"/>
       <c r="H19" s="39"/>
-      <c r="I19" s="120"/>
-      <c r="J19" s="121"/>
-      <c r="K19" s="122"/>
-    </row>
-    <row r="20" spans="1:19" ht="25.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="120"/>
-      <c r="B20" s="121"/>
-      <c r="C20" s="122" t="s">
+      <c r="I19" s="80"/>
+      <c r="J19" s="81"/>
+      <c r="K19" s="78"/>
+    </row>
+    <row r="20" spans="1:19" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="80"/>
+      <c r="B20" s="81"/>
+      <c r="C20" s="78" t="s">
         <v>77</v>
       </c>
-      <c r="E20" s="121"/>
-      <c r="F20" s="121"/>
-      <c r="G20" s="122"/>
-      <c r="I20" s="120"/>
-      <c r="J20" s="121"/>
-      <c r="K20" s="122"/>
-    </row>
-    <row r="21" spans="1:19" ht="25.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="120"/>
-      <c r="B21" s="121"/>
-      <c r="C21" s="122"/>
-      <c r="E21" s="121"/>
-      <c r="F21" s="121"/>
-      <c r="G21" s="122"/>
-      <c r="I21" s="120"/>
-      <c r="J21" s="121"/>
-      <c r="K21" s="122"/>
-    </row>
-    <row r="22" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="23" spans="1:19" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="130" t="s">
+      <c r="E20" s="81"/>
+      <c r="F20" s="81"/>
+      <c r="G20" s="78"/>
+      <c r="I20" s="80"/>
+      <c r="J20" s="81"/>
+      <c r="K20" s="78"/>
+    </row>
+    <row r="21" spans="1:19" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="80"/>
+      <c r="B21" s="81"/>
+      <c r="C21" s="78"/>
+      <c r="E21" s="81"/>
+      <c r="F21" s="81"/>
+      <c r="G21" s="78"/>
+      <c r="I21" s="80"/>
+      <c r="J21" s="81"/>
+      <c r="K21" s="78"/>
+    </row>
+    <row r="22" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="23" spans="1:19" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="83" t="s">
         <v>51</v>
       </c>
-      <c r="B23" s="130"/>
-      <c r="C23" s="130" t="s">
+      <c r="B23" s="83"/>
+      <c r="C23" s="83" t="s">
         <v>2</v>
       </c>
-      <c r="D23" s="130"/>
-      <c r="E23" s="130"/>
-      <c r="F23" s="130"/>
-      <c r="G23" s="130"/>
-      <c r="H23" s="130" t="s">
+      <c r="D23" s="83"/>
+      <c r="E23" s="83"/>
+      <c r="F23" s="83"/>
+      <c r="G23" s="83"/>
+      <c r="H23" s="83" t="s">
         <v>52</v>
       </c>
-      <c r="I23" s="130"/>
-      <c r="J23" s="130"/>
-      <c r="K23" s="130" t="s">
+      <c r="I23" s="83"/>
+      <c r="J23" s="83"/>
+      <c r="K23" s="83" t="s">
         <v>53</v>
       </c>
-      <c r="L23" s="130"/>
-      <c r="M23" s="130"/>
-      <c r="N23" s="130"/>
-      <c r="O23" s="130"/>
-      <c r="P23" s="130" t="s">
+      <c r="L23" s="83"/>
+      <c r="M23" s="83"/>
+      <c r="N23" s="83"/>
+      <c r="O23" s="83"/>
+      <c r="P23" s="83" t="s">
         <v>54</v>
       </c>
-      <c r="Q23" s="130"/>
-      <c r="R23" s="130" t="s">
+      <c r="Q23" s="83"/>
+      <c r="R23" s="83" t="s">
         <v>55</v>
       </c>
-      <c r="S23" s="130"/>
-    </row>
-    <row r="24" spans="1:19" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="130"/>
-      <c r="B24" s="130"/>
-      <c r="C24" s="130"/>
-      <c r="D24" s="130"/>
-      <c r="E24" s="130"/>
-      <c r="F24" s="130"/>
-      <c r="G24" s="130"/>
-      <c r="H24" s="131" t="s">
+      <c r="S23" s="83"/>
+    </row>
+    <row r="24" spans="1:19" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="83"/>
+      <c r="B24" s="83"/>
+      <c r="C24" s="83"/>
+      <c r="D24" s="83"/>
+      <c r="E24" s="83"/>
+      <c r="F24" s="83"/>
+      <c r="G24" s="83"/>
+      <c r="H24" s="57" t="s">
         <v>56</v>
       </c>
-      <c r="I24" s="132" t="s">
+      <c r="I24" s="56" t="s">
         <v>57</v>
       </c>
-      <c r="J24" s="132" t="s">
+      <c r="J24" s="56" t="s">
         <v>2</v>
       </c>
-      <c r="K24" s="132" t="s">
+      <c r="K24" s="56" t="s">
         <v>24</v>
       </c>
-      <c r="L24" s="130" t="s">
+      <c r="L24" s="83" t="s">
         <v>2</v>
       </c>
-      <c r="M24" s="130"/>
-      <c r="N24" s="130"/>
-      <c r="O24" s="130"/>
-      <c r="P24" s="132" t="s">
+      <c r="M24" s="83"/>
+      <c r="N24" s="83"/>
+      <c r="O24" s="83"/>
+      <c r="P24" s="56" t="s">
         <v>58</v>
       </c>
-      <c r="Q24" s="132" t="s">
+      <c r="Q24" s="56" t="s">
         <v>2</v>
       </c>
-      <c r="R24" s="132" t="s">
+      <c r="R24" s="56" t="s">
         <v>59</v>
       </c>
-      <c r="S24" s="132" t="s">
+      <c r="S24" s="56" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="25" spans="1:19" ht="46.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="133" t="s">
+    <row r="25" spans="1:19" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="87" t="s">
         <v>98</v>
       </c>
-      <c r="B25" s="133"/>
-      <c r="C25" s="134" t="s">
+      <c r="B25" s="87"/>
+      <c r="C25" s="88" t="s">
         <v>135</v>
       </c>
-      <c r="D25" s="134"/>
-      <c r="E25" s="134"/>
-      <c r="F25" s="134"/>
-      <c r="G25" s="134"/>
-      <c r="H25" s="134" t="str">
+      <c r="D25" s="88"/>
+      <c r="E25" s="88"/>
+      <c r="F25" s="88"/>
+      <c r="G25" s="88"/>
+      <c r="H25" s="88" t="str">
         <f>_xlfn.CONCAT("datos",B2)</f>
         <v>datosResidente</v>
       </c>
-      <c r="I25" s="135" t="str">
+      <c r="I25" s="89" t="str">
         <f>B2</f>
         <v>Residente</v>
       </c>
-      <c r="J25" s="136" t="str">
+      <c r="J25" s="82" t="str">
         <f>_xlfn.CONCAT("Corresponde al objeto que internamente contiene los datos necesarios para crear un nuevo ",B2,)</f>
         <v>Corresponde al objeto que internamente contiene los datos necesarios para crear un nuevo Residente</v>
       </c>
-      <c r="K25" s="137"/>
-      <c r="L25" s="136"/>
-      <c r="M25" s="136"/>
-      <c r="N25" s="136"/>
-      <c r="O25" s="136"/>
-      <c r="P25" s="138" t="s">
+      <c r="K25" s="58"/>
+      <c r="L25" s="82"/>
+      <c r="M25" s="82"/>
+      <c r="N25" s="82"/>
+      <c r="O25" s="82"/>
+      <c r="P25" s="59" t="s">
         <v>141</v>
       </c>
-      <c r="Q25" s="139" t="s">
+      <c r="Q25" s="60" t="s">
         <v>146</v>
       </c>
-      <c r="R25" s="139" t="s">
+      <c r="R25" s="60" t="s">
         <v>108</v>
       </c>
-      <c r="S25" s="139" t="s">
+      <c r="S25" s="60" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="26" spans="1:19" ht="31.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="133"/>
-      <c r="B26" s="133"/>
-      <c r="C26" s="134"/>
-      <c r="D26" s="134"/>
-      <c r="E26" s="134"/>
-      <c r="F26" s="134"/>
-      <c r="G26" s="134"/>
-      <c r="H26" s="134"/>
-      <c r="I26" s="135"/>
-      <c r="J26" s="136"/>
-      <c r="K26" s="137"/>
-      <c r="L26" s="136"/>
-      <c r="M26" s="136"/>
-      <c r="N26" s="136"/>
-      <c r="O26" s="136"/>
-      <c r="P26" s="138" t="s">
+    <row r="26" spans="1:19" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="87"/>
+      <c r="B26" s="87"/>
+      <c r="C26" s="88"/>
+      <c r="D26" s="88"/>
+      <c r="E26" s="88"/>
+      <c r="F26" s="88"/>
+      <c r="G26" s="88"/>
+      <c r="H26" s="88"/>
+      <c r="I26" s="89"/>
+      <c r="J26" s="82"/>
+      <c r="K26" s="58"/>
+      <c r="L26" s="82"/>
+      <c r="M26" s="82"/>
+      <c r="N26" s="82"/>
+      <c r="O26" s="82"/>
+      <c r="P26" s="59" t="s">
         <v>142</v>
       </c>
-      <c r="Q26" s="139" t="s">
+      <c r="Q26" s="60" t="s">
         <v>175</v>
       </c>
-      <c r="R26" s="139" t="s">
+      <c r="R26" s="60" t="s">
         <v>177</v>
       </c>
-      <c r="S26" s="139" t="s">
+      <c r="S26" s="60" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="27" spans="1:19" ht="31.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="133"/>
-      <c r="B27" s="133"/>
-      <c r="C27" s="134"/>
-      <c r="D27" s="134"/>
-      <c r="E27" s="134"/>
-      <c r="F27" s="134"/>
-      <c r="G27" s="134"/>
-      <c r="H27" s="134"/>
-      <c r="I27" s="135"/>
-      <c r="J27" s="136"/>
-      <c r="K27" s="137"/>
-      <c r="L27" s="136"/>
-      <c r="M27" s="136"/>
-      <c r="N27" s="136"/>
-      <c r="O27" s="136"/>
-      <c r="P27" s="138" t="s">
+    <row r="27" spans="1:19" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="87"/>
+      <c r="B27" s="87"/>
+      <c r="C27" s="88"/>
+      <c r="D27" s="88"/>
+      <c r="E27" s="88"/>
+      <c r="F27" s="88"/>
+      <c r="G27" s="88"/>
+      <c r="H27" s="88"/>
+      <c r="I27" s="89"/>
+      <c r="J27" s="82"/>
+      <c r="K27" s="58"/>
+      <c r="L27" s="82"/>
+      <c r="M27" s="82"/>
+      <c r="N27" s="82"/>
+      <c r="O27" s="82"/>
+      <c r="P27" s="59" t="s">
         <v>143</v>
       </c>
-      <c r="Q27" s="139" t="s">
+      <c r="Q27" s="60" t="s">
         <v>176</v>
       </c>
-      <c r="R27" s="139" t="s">
+      <c r="R27" s="60" t="s">
         <v>178</v>
       </c>
-      <c r="S27" s="139" t="s">
+      <c r="S27" s="60" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="28" spans="1:19" ht="31.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="140" t="s">
+    <row r="28" spans="1:19" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="91" t="s">
         <v>127</v>
       </c>
-      <c r="B28" s="140"/>
-      <c r="C28" s="141" t="s">
+      <c r="B28" s="91"/>
+      <c r="C28" s="90" t="s">
         <v>137</v>
       </c>
-      <c r="D28" s="141"/>
-      <c r="E28" s="141"/>
-      <c r="F28" s="141"/>
-      <c r="G28" s="141"/>
-      <c r="H28" s="141" t="str">
+      <c r="D28" s="90"/>
+      <c r="E28" s="90"/>
+      <c r="F28" s="90"/>
+      <c r="G28" s="90"/>
+      <c r="H28" s="90" t="str">
         <f>_xlfn.CONCAT("datos",B2)</f>
         <v>datosResidente</v>
       </c>
-      <c r="I28" s="140" t="str">
+      <c r="I28" s="91" t="str">
         <f>B2</f>
         <v>Residente</v>
       </c>
-      <c r="J28" s="141" t="str">
+      <c r="J28" s="90" t="str">
         <f>_xlfn.CONCAT("Corresponde a los datos que se van a modificar del ",B2)</f>
         <v>Corresponde a los datos que se van a modificar del Residente</v>
       </c>
-      <c r="K28" s="142"/>
-      <c r="L28" s="141"/>
-      <c r="M28" s="141"/>
-      <c r="N28" s="141"/>
-      <c r="O28" s="141"/>
-      <c r="P28" s="143" t="s">
+      <c r="K28" s="61"/>
+      <c r="L28" s="90"/>
+      <c r="M28" s="90"/>
+      <c r="N28" s="90"/>
+      <c r="O28" s="90"/>
+      <c r="P28" s="62" t="s">
         <v>144</v>
       </c>
-      <c r="Q28" s="143" t="s">
+      <c r="Q28" s="62" t="s">
         <v>179</v>
       </c>
-      <c r="R28" s="143" t="s">
+      <c r="R28" s="62" t="s">
         <v>181</v>
       </c>
-      <c r="S28" s="143" t="s">
+      <c r="S28" s="62" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="29" spans="1:19" ht="30" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="140"/>
-      <c r="B29" s="140"/>
-      <c r="C29" s="141"/>
-      <c r="D29" s="141"/>
-      <c r="E29" s="141"/>
-      <c r="F29" s="141"/>
-      <c r="G29" s="141"/>
-      <c r="H29" s="141"/>
-      <c r="I29" s="140"/>
-      <c r="J29" s="141"/>
-      <c r="K29" s="142"/>
-      <c r="L29" s="141"/>
-      <c r="M29" s="141"/>
-      <c r="N29" s="141"/>
-      <c r="O29" s="141"/>
-      <c r="P29" s="143" t="s">
+    <row r="29" spans="1:19" ht="30" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="91"/>
+      <c r="B29" s="91"/>
+      <c r="C29" s="90"/>
+      <c r="D29" s="90"/>
+      <c r="E29" s="90"/>
+      <c r="F29" s="90"/>
+      <c r="G29" s="90"/>
+      <c r="H29" s="90"/>
+      <c r="I29" s="91"/>
+      <c r="J29" s="90"/>
+      <c r="K29" s="61"/>
+      <c r="L29" s="90"/>
+      <c r="M29" s="90"/>
+      <c r="N29" s="90"/>
+      <c r="O29" s="90"/>
+      <c r="P29" s="62" t="s">
         <v>145</v>
       </c>
-      <c r="Q29" s="143" t="s">
+      <c r="Q29" s="62" t="s">
         <v>180</v>
       </c>
-      <c r="R29" s="143" t="s">
+      <c r="R29" s="62" t="s">
         <v>183</v>
       </c>
-      <c r="S29" s="143" t="s">
+      <c r="S29" s="62" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="30" spans="1:19" ht="69.599999999999994" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="144" t="s">
+    <row r="30" spans="1:19" ht="69.599999999999994" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="95" t="s">
         <v>122</v>
       </c>
-      <c r="B30" s="144"/>
-      <c r="C30" s="145" t="s">
+      <c r="B30" s="95"/>
+      <c r="C30" s="96" t="s">
         <v>136</v>
       </c>
-      <c r="D30" s="145"/>
-      <c r="E30" s="145"/>
-      <c r="F30" s="145"/>
-      <c r="G30" s="145"/>
-      <c r="H30" s="146" t="str">
+      <c r="D30" s="96"/>
+      <c r="E30" s="96"/>
+      <c r="F30" s="96"/>
+      <c r="G30" s="96"/>
+      <c r="H30" s="63" t="str">
         <f>_xlfn.CONCAT("datos",B2)</f>
         <v>datosResidente</v>
       </c>
-      <c r="I30" s="147" t="str">
+      <c r="I30" s="64" t="str">
         <f>B2</f>
         <v>Residente</v>
       </c>
-      <c r="J30" s="146" t="str">
+      <c r="J30" s="63" t="str">
         <f>_xlfn.CONCAT("Corresponde a un objeto que contiene los filtros de consulta de un  ",B2," de un conjunto residencial.")</f>
         <v>Corresponde a un objeto que contiene los filtros de consulta de un  Residente de un conjunto residencial.</v>
       </c>
-      <c r="K30" s="148" t="s">
+      <c r="K30" s="65" t="s">
         <v>140</v>
       </c>
-      <c r="L30" s="149" t="s">
+      <c r="L30" s="97" t="s">
         <v>153</v>
       </c>
-      <c r="M30" s="149"/>
-      <c r="N30" s="149"/>
-      <c r="O30" s="149"/>
-      <c r="P30" s="150" t="s">
+      <c r="M30" s="97"/>
+      <c r="N30" s="97"/>
+      <c r="O30" s="97"/>
+      <c r="P30" s="66" t="s">
         <v>148</v>
       </c>
-      <c r="Q30" s="151" t="s">
+      <c r="Q30" s="67" t="s">
         <v>126</v>
       </c>
-      <c r="R30" s="151" t="s">
+      <c r="R30" s="67" t="s">
         <v>108</v>
       </c>
-      <c r="S30" s="151" t="s">
+      <c r="S30" s="67" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="31" spans="1:19" ht="31.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="152" t="s">
+    <row r="31" spans="1:19" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="92" t="s">
         <v>133</v>
       </c>
-      <c r="B31" s="152"/>
-      <c r="C31" s="153" t="s">
+      <c r="B31" s="92"/>
+      <c r="C31" s="93" t="s">
         <v>138</v>
       </c>
-      <c r="D31" s="153"/>
-      <c r="E31" s="153"/>
-      <c r="F31" s="153"/>
-      <c r="G31" s="153"/>
-      <c r="H31" s="154" t="s">
+      <c r="D31" s="93"/>
+      <c r="E31" s="93"/>
+      <c r="F31" s="93"/>
+      <c r="G31" s="93"/>
+      <c r="H31" s="68" t="s">
         <v>39</v>
       </c>
-      <c r="I31" s="155" t="s">
+      <c r="I31" s="69" t="s">
         <v>9</v>
       </c>
-      <c r="J31" s="154" t="str">
+      <c r="J31" s="68" t="str">
         <f>_xlfn.CONCAT("Corresponde al identificador del ",$B$2,"  que se quiere dar de baja.")</f>
         <v>Corresponde al identificador del Residente  que se quiere dar de baja.</v>
       </c>
-      <c r="K31" s="156"/>
-      <c r="L31" s="157"/>
-      <c r="M31" s="157"/>
-      <c r="N31" s="157"/>
-      <c r="O31" s="157"/>
-      <c r="P31" s="155" t="s">
+      <c r="K31" s="70"/>
+      <c r="L31" s="94"/>
+      <c r="M31" s="94"/>
+      <c r="N31" s="94"/>
+      <c r="O31" s="94"/>
+      <c r="P31" s="69" t="s">
         <v>149</v>
       </c>
-      <c r="Q31" s="158" t="s">
+      <c r="Q31" s="71" t="s">
         <v>130</v>
       </c>
-      <c r="R31" s="158" t="s">
+      <c r="R31" s="71" t="s">
         <v>150</v>
       </c>
-      <c r="S31" s="158" t="s">
+      <c r="S31" s="71" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="32" spans="1:19" ht="31.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="152" t="s">
+    <row r="32" spans="1:19" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="92" t="s">
         <v>133</v>
       </c>
-      <c r="B32" s="152"/>
-      <c r="C32" s="153" t="s">
+      <c r="B32" s="92"/>
+      <c r="C32" s="93" t="s">
         <v>138</v>
       </c>
-      <c r="D32" s="153"/>
-      <c r="E32" s="153"/>
-      <c r="F32" s="153"/>
-      <c r="G32" s="153"/>
-      <c r="H32" s="154" t="s">
+      <c r="D32" s="93"/>
+      <c r="E32" s="93"/>
+      <c r="F32" s="93"/>
+      <c r="G32" s="93"/>
+      <c r="H32" s="68" t="s">
         <v>39</v>
       </c>
-      <c r="I32" s="155" t="s">
+      <c r="I32" s="69" t="s">
         <v>9</v>
       </c>
-      <c r="J32" s="154" t="str">
+      <c r="J32" s="68" t="str">
         <f>_xlfn.CONCAT("Corresponde al identificador del ",$B$2,"  que se quiere dar de baja.")</f>
         <v>Corresponde al identificador del Residente  que se quiere dar de baja.</v>
       </c>
-      <c r="K32" s="156"/>
-      <c r="L32" s="157"/>
-      <c r="M32" s="157"/>
-      <c r="N32" s="157"/>
-      <c r="O32" s="157"/>
-      <c r="P32" s="155" t="s">
+      <c r="K32" s="70"/>
+      <c r="L32" s="94"/>
+      <c r="M32" s="94"/>
+      <c r="N32" s="94"/>
+      <c r="O32" s="94"/>
+      <c r="P32" s="69" t="s">
         <v>149</v>
       </c>
-      <c r="Q32" s="158" t="s">
+      <c r="Q32" s="71" t="s">
         <v>130</v>
       </c>
-      <c r="R32" s="158" t="s">
+      <c r="R32" s="71" t="s">
         <v>150</v>
       </c>
-      <c r="S32" s="158" t="s">
+      <c r="S32" s="71" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="33" spans="1:19" ht="31.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="152" t="s">
+    <row r="33" spans="1:19" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="92" t="s">
         <v>133</v>
       </c>
-      <c r="B33" s="152"/>
-      <c r="C33" s="153" t="s">
+      <c r="B33" s="92"/>
+      <c r="C33" s="93" t="s">
         <v>138</v>
       </c>
-      <c r="D33" s="153"/>
-      <c r="E33" s="153"/>
-      <c r="F33" s="153"/>
-      <c r="G33" s="153"/>
-      <c r="H33" s="154" t="s">
+      <c r="D33" s="93"/>
+      <c r="E33" s="93"/>
+      <c r="F33" s="93"/>
+      <c r="G33" s="93"/>
+      <c r="H33" s="68" t="s">
         <v>39</v>
       </c>
-      <c r="I33" s="155" t="s">
+      <c r="I33" s="69" t="s">
         <v>9</v>
       </c>
-      <c r="J33" s="154" t="str">
+      <c r="J33" s="68" t="str">
         <f>_xlfn.CONCAT("Corresponde al identificador del ",$B$2,"  que se quiere dar de baja.")</f>
         <v>Corresponde al identificador del Residente  que se quiere dar de baja.</v>
       </c>
-      <c r="K33" s="156"/>
-      <c r="L33" s="157"/>
-      <c r="M33" s="157"/>
-      <c r="N33" s="157"/>
-      <c r="O33" s="157"/>
-      <c r="P33" s="155" t="s">
+      <c r="K33" s="70"/>
+      <c r="L33" s="94"/>
+      <c r="M33" s="94"/>
+      <c r="N33" s="94"/>
+      <c r="O33" s="94"/>
+      <c r="P33" s="69" t="s">
         <v>149</v>
       </c>
-      <c r="Q33" s="158" t="s">
+      <c r="Q33" s="71" t="s">
         <v>130</v>
       </c>
-      <c r="R33" s="158" t="s">
+      <c r="R33" s="71" t="s">
         <v>150</v>
       </c>
-      <c r="S33" s="158" t="s">
+      <c r="S33" s="71" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="34" spans="1:19" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
+    <row r="34" spans="1:19" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="48">
-    <mergeCell ref="C20:C21"/>
-    <mergeCell ref="C18:C19"/>
-    <mergeCell ref="G18:G21"/>
-    <mergeCell ref="I16:K16"/>
-    <mergeCell ref="I18:I21"/>
-    <mergeCell ref="K18:K21"/>
-    <mergeCell ref="F18:F21"/>
-    <mergeCell ref="J18:J21"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="C32:G32"/>
+    <mergeCell ref="L32:O32"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="C33:G33"/>
+    <mergeCell ref="L33:O33"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="C31:G31"/>
+    <mergeCell ref="L31:O31"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="C30:G30"/>
+    <mergeCell ref="L30:O30"/>
+    <mergeCell ref="L28:O28"/>
+    <mergeCell ref="A28:B29"/>
+    <mergeCell ref="C28:G29"/>
+    <mergeCell ref="H28:H29"/>
+    <mergeCell ref="I28:I29"/>
+    <mergeCell ref="J28:J29"/>
+    <mergeCell ref="L29:O29"/>
+    <mergeCell ref="A25:B27"/>
+    <mergeCell ref="C25:G27"/>
+    <mergeCell ref="H25:H27"/>
+    <mergeCell ref="I25:I27"/>
+    <mergeCell ref="J25:J27"/>
     <mergeCell ref="L25:O27"/>
     <mergeCell ref="R23:S23"/>
     <mergeCell ref="L24:O24"/>
@@ -4325,30 +4341,14 @@
     <mergeCell ref="B18:B21"/>
     <mergeCell ref="E16:G16"/>
     <mergeCell ref="E18:E21"/>
-    <mergeCell ref="A25:B27"/>
-    <mergeCell ref="C25:G27"/>
-    <mergeCell ref="H25:H27"/>
-    <mergeCell ref="I25:I27"/>
-    <mergeCell ref="J25:J27"/>
-    <mergeCell ref="L28:O28"/>
-    <mergeCell ref="A28:B29"/>
-    <mergeCell ref="C28:G29"/>
-    <mergeCell ref="H28:H29"/>
-    <mergeCell ref="I28:I29"/>
-    <mergeCell ref="J28:J29"/>
-    <mergeCell ref="L29:O29"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="C31:G31"/>
-    <mergeCell ref="L31:O31"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="C30:G30"/>
-    <mergeCell ref="L30:O30"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="C32:G32"/>
-    <mergeCell ref="L32:O32"/>
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="C33:G33"/>
-    <mergeCell ref="L33:O33"/>
+    <mergeCell ref="C20:C21"/>
+    <mergeCell ref="C18:C19"/>
+    <mergeCell ref="G18:G21"/>
+    <mergeCell ref="I16:K16"/>
+    <mergeCell ref="I18:I21"/>
+    <mergeCell ref="K18:K21"/>
+    <mergeCell ref="F18:F21"/>
+    <mergeCell ref="J18:J21"/>
   </mergeCells>
   <phoneticPr fontId="9" type="noConversion"/>
   <hyperlinks>
@@ -4395,103 +4395,103 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE91583B-F698-4020-97FF-1414BFE2C5EB}">
   <dimension ref="A1:U37"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="28.28515625" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.5703125" style="7" customWidth="1"/>
-    <col min="3" max="3" width="33.28515625" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.85546875" style="7" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.5703125" style="7" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="19.28515625" style="7" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.28515625" style="7" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="28.5703125" style="7" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="79.42578125" style="7" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="79.28515625" style="7" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="18.140625" style="7" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="19.28515625" style="7" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="7" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15.7109375" style="7" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.85546875" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="28.33203125" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.5546875" style="7" customWidth="1"/>
+    <col min="3" max="3" width="33.33203125" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.88671875" style="7" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.5546875" style="7" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.33203125" style="7" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.33203125" style="7" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="28.5546875" style="7" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="79.44140625" style="7" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="79.33203125" style="7" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="18.109375" style="7" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="19.33203125" style="7" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.44140625" style="7" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.6640625" style="7" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.88671875" style="7" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="25" style="7" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="94.42578125" style="7" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="132.5703125" style="7" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="46.42578125" style="7" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="50.140625" style="7" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="66.85546875" style="7" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="52.28515625" style="7" bestFit="1" customWidth="1"/>
-    <col min="23" max="16384" width="11.42578125" style="7"/>
+    <col min="17" max="17" width="94.44140625" style="7" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="132.5546875" style="7" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="46.44140625" style="7" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="50.109375" style="7" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="66.88671875" style="7" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="52.33203125" style="7" bestFit="1" customWidth="1"/>
+    <col min="23" max="16384" width="11.44140625" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A1" s="106" t="s">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A1" s="84" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="106"/>
-      <c r="C1" s="106"/>
-      <c r="D1" s="106"/>
-      <c r="E1" s="106"/>
-      <c r="F1" s="106"/>
-      <c r="G1" s="106"/>
-      <c r="H1" s="106"/>
-      <c r="I1" s="106"/>
-      <c r="J1" s="106"/>
-      <c r="K1" s="106"/>
-      <c r="L1" s="106"/>
-      <c r="M1" s="106"/>
-      <c r="N1" s="106"/>
-      <c r="O1" s="106"/>
-      <c r="P1" s="106"/>
-      <c r="Q1" s="106"/>
-    </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="B1" s="84"/>
+      <c r="C1" s="84"/>
+      <c r="D1" s="84"/>
+      <c r="E1" s="84"/>
+      <c r="F1" s="84"/>
+      <c r="G1" s="84"/>
+      <c r="H1" s="84"/>
+      <c r="I1" s="84"/>
+      <c r="J1" s="84"/>
+      <c r="K1" s="84"/>
+      <c r="L1" s="84"/>
+      <c r="M1" s="84"/>
+      <c r="N1" s="84"/>
+      <c r="O1" s="84"/>
+      <c r="P1" s="84"/>
+      <c r="Q1" s="84"/>
+    </row>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A2" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="B2" s="107" t="str">
+      <c r="B2" s="85" t="str">
         <f>'Listado Objetos de Dominio'!A4</f>
         <v>Inmueble</v>
       </c>
-      <c r="C2" s="107"/>
-      <c r="D2" s="107"/>
-      <c r="E2" s="107"/>
-      <c r="F2" s="107"/>
-      <c r="G2" s="107"/>
-      <c r="H2" s="107"/>
-      <c r="I2" s="107"/>
-      <c r="J2" s="107"/>
-      <c r="K2" s="107"/>
-      <c r="L2" s="107"/>
-      <c r="M2" s="107"/>
-      <c r="N2" s="107"/>
-      <c r="O2" s="107"/>
-      <c r="P2" s="107"/>
-      <c r="Q2" s="107"/>
-    </row>
-    <row r="3" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C2" s="85"/>
+      <c r="D2" s="85"/>
+      <c r="E2" s="85"/>
+      <c r="F2" s="85"/>
+      <c r="G2" s="85"/>
+      <c r="H2" s="85"/>
+      <c r="I2" s="85"/>
+      <c r="J2" s="85"/>
+      <c r="K2" s="85"/>
+      <c r="L2" s="85"/>
+      <c r="M2" s="85"/>
+      <c r="N2" s="85"/>
+      <c r="O2" s="85"/>
+      <c r="P2" s="85"/>
+      <c r="Q2" s="85"/>
+    </row>
+    <row r="3" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="B3" s="108" t="str">
+      <c r="B3" s="86" t="str">
         <f>'Listado Objetos de Dominio'!B4</f>
         <v xml:space="preserve">Objeto de dominio que representa el inmueble donde vive el residente del conjunto residencial. </v>
       </c>
-      <c r="C3" s="108"/>
-      <c r="D3" s="108"/>
-      <c r="E3" s="108"/>
-      <c r="F3" s="108"/>
-      <c r="G3" s="108"/>
-      <c r="H3" s="108"/>
-      <c r="I3" s="108"/>
-      <c r="J3" s="108"/>
-      <c r="K3" s="108"/>
-      <c r="L3" s="108"/>
-      <c r="M3" s="108"/>
-      <c r="N3" s="108"/>
-      <c r="O3" s="108"/>
-      <c r="P3" s="108"/>
-      <c r="Q3" s="108"/>
-    </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="C3" s="86"/>
+      <c r="D3" s="86"/>
+      <c r="E3" s="86"/>
+      <c r="F3" s="86"/>
+      <c r="G3" s="86"/>
+      <c r="H3" s="86"/>
+      <c r="I3" s="86"/>
+      <c r="J3" s="86"/>
+      <c r="K3" s="86"/>
+      <c r="L3" s="86"/>
+      <c r="M3" s="86"/>
+      <c r="N3" s="86"/>
+      <c r="O3" s="86"/>
+      <c r="P3" s="86"/>
+      <c r="Q3" s="86"/>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A4" s="15" t="s">
         <v>23</v>
       </c>
@@ -4559,7 +4559,7 @@
         <v>Eliminar</v>
       </c>
     </row>
-    <row r="5" spans="1:21" ht="27" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:21" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A5" s="18" t="s">
         <v>154</v>
       </c>
@@ -4612,7 +4612,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="6" spans="1:21" ht="40.5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:21" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A6" s="18" t="s">
         <v>155</v>
       </c>
@@ -4667,7 +4667,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="7" spans="1:21" ht="27" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:21" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A7" s="18" t="s">
         <v>167</v>
       </c>
@@ -4720,7 +4720,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="8" spans="1:21" ht="40.5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:21" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A8" s="18" t="s">
         <v>168</v>
       </c>
@@ -4773,7 +4773,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="9" spans="1:21" ht="27" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:21" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A9" s="18" t="s">
         <v>169</v>
       </c>
@@ -4826,7 +4826,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="10" spans="1:21" ht="40.5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:21" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A10" s="18" t="s">
         <v>170</v>
       </c>
@@ -4885,7 +4885,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A11" s="18" t="s">
         <v>156</v>
       </c>
@@ -4938,7 +4938,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="12" spans="1:21" ht="40.5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:21" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A12" s="18" t="s">
         <v>157</v>
       </c>
@@ -4991,7 +4991,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A13" s="18" t="s">
         <v>158</v>
       </c>
@@ -5044,7 +5044,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A14" s="18" t="s">
         <v>159</v>
       </c>
@@ -5095,15 +5095,15 @@
         <v>104</v>
       </c>
     </row>
-    <row r="15" spans="1:21" ht="23.45" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="16" spans="1:21" ht="51" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="109" t="s">
+    <row r="15" spans="1:21" ht="23.4" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="16" spans="1:21" ht="51" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="79" t="s">
         <v>47</v>
       </c>
-      <c r="B16" s="109"/>
-      <c r="C16" s="109"/>
-    </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="B16" s="79"/>
+      <c r="C16" s="79"/>
+    </row>
+    <row r="17" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A17" s="26" t="s">
         <v>48</v>
       </c>
@@ -5114,11 +5114,11 @@
         <v>49</v>
       </c>
     </row>
-    <row r="18" spans="1:19" ht="31.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="121" t="s">
+    <row r="18" spans="1:19" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="81" t="s">
         <v>160</v>
       </c>
-      <c r="B18" s="121" t="s">
+      <c r="B18" s="81" t="s">
         <v>161</v>
       </c>
       <c r="C18" s="55" t="str">
@@ -5126,120 +5126,120 @@
         <v>identificadorConjuntoResidencial</v>
       </c>
     </row>
-    <row r="19" spans="1:19" ht="31.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="121"/>
-      <c r="B19" s="121"/>
+    <row r="19" spans="1:19" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="81"/>
+      <c r="B19" s="81"/>
       <c r="C19" s="55" t="str">
         <f t="shared" si="0"/>
         <v>nombreConjuntoResidencial</v>
       </c>
     </row>
-    <row r="20" spans="1:19" ht="31.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="121"/>
-      <c r="B20" s="121"/>
+    <row r="20" spans="1:19" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="81"/>
+      <c r="B20" s="81"/>
       <c r="C20" s="55" t="str">
         <f t="shared" si="0"/>
         <v>identificadorTipoZonaInmueble</v>
       </c>
     </row>
-    <row r="21" spans="1:19" ht="31.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="121"/>
-      <c r="B21" s="121"/>
+    <row r="21" spans="1:19" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="81"/>
+      <c r="B21" s="81"/>
       <c r="C21" s="55" t="str">
         <f t="shared" si="0"/>
         <v>nombreTipoZonaInmueble</v>
       </c>
     </row>
-    <row r="22" spans="1:19" ht="31.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="121"/>
-      <c r="B22" s="121"/>
+    <row r="22" spans="1:19" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="81"/>
+      <c r="B22" s="81"/>
       <c r="C22" s="55" t="str">
         <f t="shared" si="0"/>
         <v>identificadorZonaInmueble</v>
       </c>
     </row>
-    <row r="23" spans="1:19" ht="31.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="121"/>
-      <c r="B23" s="121"/>
+    <row r="23" spans="1:19" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="81"/>
+      <c r="B23" s="81"/>
       <c r="C23" s="55" t="str">
         <f t="shared" si="0"/>
         <v>numeroZonaInmuebleZonaInmueble</v>
       </c>
     </row>
-    <row r="24" spans="1:19" ht="31.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="121"/>
-      <c r="B24" s="121"/>
+    <row r="24" spans="1:19" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="81"/>
+      <c r="B24" s="81"/>
       <c r="C24" s="55" t="str">
         <f t="shared" si="0"/>
         <v>identificadorTipoInmueble</v>
       </c>
     </row>
-    <row r="25" spans="1:19" ht="31.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="121"/>
-      <c r="B25" s="121"/>
+    <row r="25" spans="1:19" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="81"/>
+      <c r="B25" s="81"/>
       <c r="C25" s="55" t="str">
         <f t="shared" si="0"/>
         <v>nombreTipoInmueble</v>
       </c>
     </row>
-    <row r="26" spans="1:19" ht="31.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="121"/>
-      <c r="B26" s="121"/>
+    <row r="26" spans="1:19" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="81"/>
+      <c r="B26" s="81"/>
       <c r="C26" s="38" t="str">
         <f t="shared" si="0"/>
         <v>identificadorInmueble</v>
       </c>
     </row>
-    <row r="27" spans="1:19" ht="31.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="121"/>
-      <c r="B27" s="121"/>
+    <row r="27" spans="1:19" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="81"/>
+      <c r="B27" s="81"/>
       <c r="C27" s="38" t="str">
         <f t="shared" si="0"/>
         <v>numeroViviendaInmueble</v>
       </c>
     </row>
-    <row r="28" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="29" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A29" s="110" t="s">
+    <row r="28" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="29" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A29" s="126" t="s">
         <v>51</v>
       </c>
-      <c r="B29" s="111"/>
-      <c r="C29" s="114" t="s">
+      <c r="B29" s="127"/>
+      <c r="C29" s="130" t="s">
         <v>2</v>
       </c>
-      <c r="D29" s="115"/>
-      <c r="E29" s="115"/>
-      <c r="F29" s="115"/>
-      <c r="G29" s="111"/>
-      <c r="H29" s="101" t="s">
+      <c r="D29" s="131"/>
+      <c r="E29" s="131"/>
+      <c r="F29" s="131"/>
+      <c r="G29" s="127"/>
+      <c r="H29" s="120" t="s">
         <v>52</v>
       </c>
-      <c r="I29" s="118"/>
-      <c r="J29" s="119"/>
-      <c r="K29" s="101" t="s">
+      <c r="I29" s="134"/>
+      <c r="J29" s="121"/>
+      <c r="K29" s="120" t="s">
         <v>53</v>
       </c>
-      <c r="L29" s="118"/>
-      <c r="M29" s="118"/>
-      <c r="N29" s="118"/>
-      <c r="O29" s="119"/>
-      <c r="P29" s="101" t="s">
+      <c r="L29" s="134"/>
+      <c r="M29" s="134"/>
+      <c r="N29" s="134"/>
+      <c r="O29" s="121"/>
+      <c r="P29" s="120" t="s">
         <v>54</v>
       </c>
-      <c r="Q29" s="119"/>
-      <c r="R29" s="101" t="s">
+      <c r="Q29" s="121"/>
+      <c r="R29" s="120" t="s">
         <v>55</v>
       </c>
-      <c r="S29" s="102"/>
-    </row>
-    <row r="30" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A30" s="112"/>
-      <c r="B30" s="113"/>
-      <c r="C30" s="116"/>
-      <c r="D30" s="117"/>
-      <c r="E30" s="117"/>
-      <c r="F30" s="117"/>
-      <c r="G30" s="113"/>
+      <c r="S29" s="122"/>
+    </row>
+    <row r="30" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A30" s="128"/>
+      <c r="B30" s="129"/>
+      <c r="C30" s="132"/>
+      <c r="D30" s="133"/>
+      <c r="E30" s="133"/>
+      <c r="F30" s="133"/>
+      <c r="G30" s="129"/>
       <c r="H30" s="47" t="s">
         <v>56</v>
       </c>
@@ -5252,12 +5252,12 @@
       <c r="K30" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="L30" s="103" t="s">
+      <c r="L30" s="123" t="s">
         <v>2</v>
       </c>
-      <c r="M30" s="104"/>
-      <c r="N30" s="104"/>
-      <c r="O30" s="105"/>
+      <c r="M30" s="124"/>
+      <c r="N30" s="124"/>
+      <c r="O30" s="125"/>
       <c r="P30" s="27" t="s">
         <v>58</v>
       </c>
@@ -5271,35 +5271,35 @@
         <v>60</v>
       </c>
     </row>
-    <row r="31" spans="1:19" ht="30" x14ac:dyDescent="0.25">
-      <c r="A31" s="81" t="s">
+    <row r="31" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A31" s="104" t="s">
         <v>98</v>
       </c>
-      <c r="B31" s="82"/>
-      <c r="C31" s="85" t="s">
+      <c r="B31" s="105"/>
+      <c r="C31" s="108" t="s">
         <v>105</v>
       </c>
-      <c r="D31" s="86"/>
-      <c r="E31" s="86"/>
-      <c r="F31" s="86"/>
-      <c r="G31" s="87"/>
-      <c r="H31" s="91" t="str">
+      <c r="D31" s="109"/>
+      <c r="E31" s="109"/>
+      <c r="F31" s="109"/>
+      <c r="G31" s="110"/>
+      <c r="H31" s="114" t="str">
         <f>_xlfn.CONCAT("datos",B2)</f>
         <v>datosInmueble</v>
       </c>
-      <c r="I31" s="128" t="str">
+      <c r="I31" s="116" t="str">
         <f>B2</f>
         <v>Inmueble</v>
       </c>
-      <c r="J31" s="93" t="str">
+      <c r="J31" s="118" t="str">
         <f>_xlfn.CONCAT("Corresponde al objeto que internamente contiene los datos necesarios para crear una nueva ",B2,)</f>
         <v>Corresponde al objeto que internamente contiene los datos necesarios para crear una nueva Inmueble</v>
       </c>
       <c r="K31" s="48"/>
-      <c r="L31" s="95"/>
-      <c r="M31" s="96"/>
-      <c r="N31" s="96"/>
-      <c r="O31" s="97"/>
+      <c r="L31" s="98"/>
+      <c r="M31" s="99"/>
+      <c r="N31" s="99"/>
+      <c r="O31" s="100"/>
       <c r="P31" s="13" t="s">
         <v>106</v>
       </c>
@@ -5313,22 +5313,22 @@
         <v>109</v>
       </c>
     </row>
-    <row r="32" spans="1:19" ht="45" x14ac:dyDescent="0.25">
-      <c r="A32" s="83"/>
-      <c r="B32" s="84"/>
-      <c r="C32" s="88"/>
-      <c r="D32" s="89"/>
-      <c r="E32" s="89"/>
-      <c r="F32" s="89"/>
-      <c r="G32" s="90"/>
-      <c r="H32" s="92"/>
-      <c r="I32" s="129"/>
-      <c r="J32" s="94"/>
+    <row r="32" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A32" s="106"/>
+      <c r="B32" s="107"/>
+      <c r="C32" s="111"/>
+      <c r="D32" s="112"/>
+      <c r="E32" s="112"/>
+      <c r="F32" s="112"/>
+      <c r="G32" s="113"/>
+      <c r="H32" s="115"/>
+      <c r="I32" s="117"/>
+      <c r="J32" s="119"/>
       <c r="K32" s="50"/>
-      <c r="L32" s="98"/>
-      <c r="M32" s="99"/>
-      <c r="N32" s="99"/>
-      <c r="O32" s="100"/>
+      <c r="L32" s="101"/>
+      <c r="M32" s="102"/>
+      <c r="N32" s="102"/>
+      <c r="O32" s="103"/>
       <c r="P32" s="13" t="s">
         <v>110</v>
       </c>
@@ -5342,22 +5342,22 @@
         <v>113</v>
       </c>
     </row>
-    <row r="33" spans="1:19" ht="30" x14ac:dyDescent="0.25">
-      <c r="A33" s="83"/>
-      <c r="B33" s="84"/>
-      <c r="C33" s="88"/>
-      <c r="D33" s="89"/>
-      <c r="E33" s="89"/>
-      <c r="F33" s="89"/>
-      <c r="G33" s="90"/>
-      <c r="H33" s="92"/>
-      <c r="I33" s="129"/>
-      <c r="J33" s="94"/>
+    <row r="33" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A33" s="106"/>
+      <c r="B33" s="107"/>
+      <c r="C33" s="111"/>
+      <c r="D33" s="112"/>
+      <c r="E33" s="112"/>
+      <c r="F33" s="112"/>
+      <c r="G33" s="113"/>
+      <c r="H33" s="115"/>
+      <c r="I33" s="117"/>
+      <c r="J33" s="119"/>
       <c r="K33" s="50"/>
-      <c r="L33" s="98"/>
-      <c r="M33" s="99"/>
-      <c r="N33" s="99"/>
-      <c r="O33" s="100"/>
+      <c r="L33" s="101"/>
+      <c r="M33" s="102"/>
+      <c r="N33" s="102"/>
+      <c r="O33" s="103"/>
       <c r="P33" s="13" t="s">
         <v>114</v>
       </c>
@@ -5371,22 +5371,22 @@
         <v>117</v>
       </c>
     </row>
-    <row r="34" spans="1:19" ht="45" x14ac:dyDescent="0.25">
-      <c r="A34" s="83"/>
-      <c r="B34" s="84"/>
-      <c r="C34" s="88"/>
-      <c r="D34" s="89"/>
-      <c r="E34" s="89"/>
-      <c r="F34" s="89"/>
-      <c r="G34" s="90"/>
-      <c r="H34" s="92"/>
-      <c r="I34" s="129"/>
-      <c r="J34" s="94"/>
+    <row r="34" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A34" s="106"/>
+      <c r="B34" s="107"/>
+      <c r="C34" s="111"/>
+      <c r="D34" s="112"/>
+      <c r="E34" s="112"/>
+      <c r="F34" s="112"/>
+      <c r="G34" s="113"/>
+      <c r="H34" s="115"/>
+      <c r="I34" s="117"/>
+      <c r="J34" s="119"/>
       <c r="K34" s="50"/>
-      <c r="L34" s="98"/>
-      <c r="M34" s="99"/>
-      <c r="N34" s="99"/>
-      <c r="O34" s="100"/>
+      <c r="L34" s="101"/>
+      <c r="M34" s="102"/>
+      <c r="N34" s="102"/>
+      <c r="O34" s="103"/>
       <c r="P34" s="13" t="s">
         <v>118</v>
       </c>
@@ -5400,18 +5400,18 @@
         <v>121</v>
       </c>
     </row>
-    <row r="35" spans="1:19" ht="71.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="70" t="s">
+    <row r="35" spans="1:19" ht="71.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="143" t="s">
         <v>122</v>
       </c>
-      <c r="B35" s="71"/>
-      <c r="C35" s="72" t="s">
+      <c r="B35" s="144"/>
+      <c r="C35" s="145" t="s">
         <v>123</v>
       </c>
-      <c r="D35" s="73"/>
-      <c r="E35" s="73"/>
-      <c r="F35" s="73"/>
-      <c r="G35" s="74"/>
+      <c r="D35" s="146"/>
+      <c r="E35" s="146"/>
+      <c r="F35" s="146"/>
+      <c r="G35" s="147"/>
       <c r="H35" s="30" t="str">
         <f>_xlfn.CONCAT("datos",B2)</f>
         <v>datosInmueble</v>
@@ -5427,12 +5427,12 @@
       <c r="K35" s="41" t="s">
         <v>139</v>
       </c>
-      <c r="L35" s="75" t="s">
+      <c r="L35" s="148" t="s">
         <v>124</v>
       </c>
-      <c r="M35" s="76"/>
-      <c r="N35" s="76"/>
-      <c r="O35" s="77"/>
+      <c r="M35" s="149"/>
+      <c r="N35" s="149"/>
+      <c r="O35" s="150"/>
       <c r="P35" s="23" t="s">
         <v>125</v>
       </c>
@@ -5446,18 +5446,18 @@
         <v>109</v>
       </c>
     </row>
-    <row r="36" spans="1:19" ht="30" x14ac:dyDescent="0.25">
-      <c r="A36" s="123" t="s">
+    <row r="36" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A36" s="151" t="s">
         <v>127</v>
       </c>
-      <c r="B36" s="124"/>
-      <c r="C36" s="125" t="s">
+      <c r="B36" s="152"/>
+      <c r="C36" s="153" t="s">
         <v>128</v>
       </c>
-      <c r="D36" s="126"/>
-      <c r="E36" s="126"/>
-      <c r="F36" s="126"/>
-      <c r="G36" s="127"/>
+      <c r="D36" s="154"/>
+      <c r="E36" s="154"/>
+      <c r="F36" s="154"/>
+      <c r="G36" s="155"/>
       <c r="H36" s="32" t="str">
         <f>_xlfn.CONCAT("datos",B2)</f>
         <v>datosInmueble</v>
@@ -5471,10 +5471,10 @@
         <v>Corresponde a los datos que se van a modificar de la Inmueble</v>
       </c>
       <c r="K36" s="34"/>
-      <c r="L36" s="78"/>
-      <c r="M36" s="79"/>
-      <c r="N36" s="79"/>
-      <c r="O36" s="80"/>
+      <c r="L36" s="156"/>
+      <c r="M36" s="157"/>
+      <c r="N36" s="157"/>
+      <c r="O36" s="158"/>
       <c r="P36" s="52" t="s">
         <v>129</v>
       </c>
@@ -5488,18 +5488,18 @@
         <v>132</v>
       </c>
     </row>
-    <row r="37" spans="1:19" ht="30" x14ac:dyDescent="0.25">
-      <c r="A37" s="62" t="s">
+    <row r="37" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A37" s="135" t="s">
         <v>133</v>
       </c>
-      <c r="B37" s="63"/>
-      <c r="C37" s="64" t="s">
+      <c r="B37" s="136"/>
+      <c r="C37" s="137" t="s">
         <v>134</v>
       </c>
-      <c r="D37" s="65"/>
-      <c r="E37" s="65"/>
-      <c r="F37" s="65"/>
-      <c r="G37" s="66"/>
+      <c r="D37" s="138"/>
+      <c r="E37" s="138"/>
+      <c r="F37" s="138"/>
+      <c r="G37" s="139"/>
       <c r="H37" s="35" t="s">
         <v>39</v>
       </c>
@@ -5511,10 +5511,10 @@
         <v>Corresponde al identificador de la Inmueble  que se quiere dar de baja.</v>
       </c>
       <c r="K37" s="36"/>
-      <c r="L37" s="67"/>
-      <c r="M37" s="68"/>
-      <c r="N37" s="68"/>
-      <c r="O37" s="69"/>
+      <c r="L37" s="140"/>
+      <c r="M37" s="141"/>
+      <c r="N37" s="141"/>
+      <c r="O37" s="142"/>
       <c r="P37" s="25" t="s">
         <v>129</v>
       </c>
@@ -5530,25 +5530,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="L31:O34"/>
-    <mergeCell ref="A31:B34"/>
-    <mergeCell ref="C31:G34"/>
-    <mergeCell ref="H31:H34"/>
-    <mergeCell ref="I31:I34"/>
-    <mergeCell ref="J31:J34"/>
-    <mergeCell ref="P29:Q29"/>
-    <mergeCell ref="R29:S29"/>
-    <mergeCell ref="L30:O30"/>
-    <mergeCell ref="A29:B30"/>
-    <mergeCell ref="C29:G30"/>
-    <mergeCell ref="H29:J29"/>
-    <mergeCell ref="K29:O29"/>
-    <mergeCell ref="A1:Q1"/>
-    <mergeCell ref="B2:Q2"/>
-    <mergeCell ref="B3:Q3"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="A18:A27"/>
-    <mergeCell ref="B18:B27"/>
     <mergeCell ref="A37:B37"/>
     <mergeCell ref="C37:G37"/>
     <mergeCell ref="L37:O37"/>
@@ -5558,6 +5539,25 @@
     <mergeCell ref="A36:B36"/>
     <mergeCell ref="C36:G36"/>
     <mergeCell ref="L36:O36"/>
+    <mergeCell ref="A1:Q1"/>
+    <mergeCell ref="B2:Q2"/>
+    <mergeCell ref="B3:Q3"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="A18:A27"/>
+    <mergeCell ref="B18:B27"/>
+    <mergeCell ref="P29:Q29"/>
+    <mergeCell ref="R29:S29"/>
+    <mergeCell ref="L30:O30"/>
+    <mergeCell ref="A29:B30"/>
+    <mergeCell ref="C29:G30"/>
+    <mergeCell ref="H29:J29"/>
+    <mergeCell ref="K29:O29"/>
+    <mergeCell ref="L31:O34"/>
+    <mergeCell ref="A31:B34"/>
+    <mergeCell ref="C31:G34"/>
+    <mergeCell ref="H31:H34"/>
+    <mergeCell ref="I31:I34"/>
+    <mergeCell ref="J31:J34"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A1" location="'Objetos de Dominio'!A1" display="Volver al inicio" xr:uid="{4C6EA31D-5DD1-42F9-A469-ED5E8CAE0643}"/>
